--- a/docs/data/jp/xlsx/4644.xlsx
+++ b/docs/data/jp/xlsx/4644.xlsx
@@ -201,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -323,6 +323,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -717,7 +720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC159"/>
+  <dimension ref="A1:AC166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4269,10 +4272,12 @@
     <row r="47">
       <c r="A47" s="20" t="inlineStr">
         <is>
-          <t>현재 주가 ()</t>
-        </is>
-      </c>
-      <c r="B47" s="29" t="n"/>
+          <t>현재 주가 (2026.10.26)</t>
+        </is>
+      </c>
+      <c r="B47" s="29" t="n">
+        <v>1027</v>
+      </c>
       <c r="C47" s="30" t="n"/>
       <c r="D47" s="31" t="n"/>
       <c r="E47" s="31" t="n"/>
@@ -4307,7 +4312,9 @@
           <t>발행주식수 (보통주)</t>
         </is>
       </c>
-      <c r="B48" s="29" t="n"/>
+      <c r="B48" s="29" t="n">
+        <v>10649000</v>
+      </c>
       <c r="C48" s="30" t="n"/>
       <c r="D48" s="31" t="n"/>
       <c r="E48" s="31" t="n"/>
@@ -5506,7 +5513,7 @@
     <row r="74">
       <c r="A74" s="43" t="inlineStr">
         <is>
-          <t>주가: 야후 파이낸스 일봉</t>
+          <t>주가: 야후 파이낸스 일봉 2026.10.26</t>
         </is>
       </c>
       <c r="C74" s="41" t="n"/>
@@ -5758,3611 +5765,3816 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="20" t="inlineStr">
+      <c r="A79" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G79" s="17">
+        <f>IF(OR(G78="",C78=""),"",IF(C78&lt;=0,"",IFERROR(G78/C78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H79" s="17">
+        <f>IF(OR(H78="",D78=""),"",IF(D78&lt;=0,"",IFERROR(H78/D78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I79" s="17">
+        <f>IF(OR(I78="",E78=""),"",IF(E78&lt;=0,"",IFERROR(I78/E78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J79" s="17">
+        <f>IF(OR(J78="",F78=""),"",IF(F78&lt;=0,"",IFERROR(J78/F78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K79" s="17">
+        <f>IF(OR(K78="",G78=""),"",IF(G78&lt;=0,"",IFERROR(K78/G78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L79" s="17">
+        <f>IF(OR(L78="",H78=""),"",IF(H78&lt;=0,"",IFERROR(L78/H78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M79" s="17">
+        <f>IF(OR(M78="",I78=""),"",IF(I78&lt;=0,"",IFERROR(M78/I78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N79" s="17">
+        <f>IF(OR(N78="",J78=""),"",IF(J78&lt;=0,"",IFERROR(N78/J78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T79" s="17">
+        <f>IF(OR(T78="",S78=""),"",IF(S78&lt;=0,"",IFERROR(T78/S78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U79" s="17">
+        <f>IF(OR(U78="",T78=""),"",IF(T78&lt;=0,"",IFERROR(U78/T78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V79" s="17">
+        <f>IF(OR(V78="",U78=""),"",IF(U78&lt;=0,"",IFERROR(V78/U78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W79" s="17">
+        <f>IF(OR(W78="",V78=""),"",IF(V78&lt;=0,"",IFERROR(W78/V78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X79" s="17">
+        <f>IF(OR(X78="",W78=""),"",IF(W78&lt;=0,"",IFERROR(X78/W78-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="20" t="inlineStr">
         <is>
           <t>매출원가</t>
         </is>
       </c>
-      <c r="C79" s="22" t="n">
+      <c r="C80" s="22" t="n">
         <v>526.076</v>
       </c>
-      <c r="D79" s="22" t="n">
+      <c r="D80" s="22" t="n">
         <v>506.067</v>
       </c>
-      <c r="E79" s="22" t="n">
+      <c r="E80" s="22" t="n">
         <v>633.638</v>
       </c>
-      <c r="F79" s="22" t="n">
+      <c r="F80" s="22" t="n">
         <v>578.639</v>
       </c>
-      <c r="G79" s="22" t="n">
+      <c r="G80" s="22" t="n">
         <v>445.816</v>
       </c>
-      <c r="H79" s="22" t="n">
+      <c r="H80" s="22" t="n">
         <v>680.361</v>
       </c>
-      <c r="I79" s="22" t="n">
+      <c r="I80" s="22" t="n">
         <v>684.189</v>
       </c>
-      <c r="J79" s="22" t="n">
+      <c r="J80" s="22" t="n">
         <v>514.466</v>
       </c>
-      <c r="K79" s="22" t="n">
+      <c r="K80" s="22" t="n">
         <v>494.976</v>
       </c>
-      <c r="L79" s="22" t="n">
+      <c r="L80" s="22" t="n">
         <v>598.546</v>
       </c>
-      <c r="M79" s="22" t="n">
+      <c r="M80" s="22" t="n">
         <v>521.6369999999999</v>
       </c>
-      <c r="N79" s="22" t="n">
+      <c r="N80" s="22" t="n">
         <v>475.138</v>
       </c>
-      <c r="T79" s="22" t="n">
+      <c r="T80" s="22" t="n">
         <v>548.34</v>
       </c>
-      <c r="U79" s="22" t="n">
+      <c r="U80" s="22" t="n">
         <v>580.197</v>
       </c>
-      <c r="V79" s="22" t="n">
+      <c r="V80" s="22" t="n">
         <v>633.638</v>
       </c>
-      <c r="W79" s="22" t="n">
+      <c r="W80" s="22" t="n">
         <v>684.189</v>
       </c>
-      <c r="X79" s="22" t="n">
+      <c r="X80" s="22" t="n">
         <v>521.6369999999999</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="9" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr">
         <is>
           <t>매출총이익</t>
         </is>
       </c>
-      <c r="C80" s="12" t="n">
+      <c r="C81" s="12" t="n">
         <v>853.351</v>
       </c>
-      <c r="D80" s="12" t="n">
+      <c r="D81" s="12" t="n">
         <v>962.155</v>
       </c>
-      <c r="E80" s="12" t="n">
+      <c r="E81" s="12" t="n">
         <v>1093.302</v>
       </c>
-      <c r="F80" s="12" t="n">
+      <c r="F81" s="12" t="n">
         <v>812.602</v>
       </c>
-      <c r="G80" s="12" t="n">
+      <c r="G81" s="12" t="n">
         <v>972.809</v>
       </c>
-      <c r="H80" s="12" t="n">
+      <c r="H81" s="12" t="n">
         <v>1309.794</v>
       </c>
-      <c r="I80" s="12" t="n">
+      <c r="I81" s="12" t="n">
         <v>1001.944</v>
       </c>
-      <c r="J80" s="12" t="n">
+      <c r="J81" s="12" t="n">
         <v>790.8200000000001</v>
       </c>
-      <c r="K80" s="12" t="n">
+      <c r="K81" s="12" t="n">
         <v>826.8390000000001</v>
       </c>
-      <c r="L80" s="12" t="n">
+      <c r="L81" s="12" t="n">
         <v>1015.046</v>
       </c>
-      <c r="M80" s="12" t="n">
+      <c r="M81" s="12" t="n">
         <v>928.109</v>
       </c>
-      <c r="N80" s="12" t="n">
+      <c r="N81" s="12" t="n">
         <v>889.956</v>
       </c>
-      <c r="T80" s="12" t="n">
+      <c r="T81" s="12" t="n">
         <v>980.662</v>
       </c>
-      <c r="U80" s="12" t="n">
+      <c r="U81" s="12" t="n">
         <v>939.223</v>
       </c>
-      <c r="V80" s="12" t="n">
+      <c r="V81" s="12" t="n">
         <v>1093.302</v>
       </c>
-      <c r="W80" s="12" t="n">
+      <c r="W81" s="12" t="n">
         <v>1001.944</v>
       </c>
-      <c r="X80" s="12" t="n">
+      <c r="X81" s="12" t="n">
         <v>928.109</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="20" t="inlineStr">
-        <is>
-          <t>판매비와 관리비</t>
-        </is>
-      </c>
-      <c r="C81" s="22" t="n">
-        <v>763.527</v>
-      </c>
-      <c r="D81" s="22" t="n">
-        <v>905.89</v>
-      </c>
-      <c r="E81" s="22" t="n">
-        <v>940.83</v>
-      </c>
-      <c r="F81" s="22" t="n">
-        <v>730.548</v>
-      </c>
-      <c r="G81" s="22" t="n">
-        <v>755.252</v>
-      </c>
-      <c r="H81" s="22" t="n">
-        <v>1201.433</v>
-      </c>
-      <c r="I81" s="22" t="n">
-        <v>951.404</v>
-      </c>
-      <c r="J81" s="22" t="n">
-        <v>827.24</v>
-      </c>
-      <c r="K81" s="22" t="n">
-        <v>920.4160000000001</v>
-      </c>
-      <c r="L81" s="22" t="n">
-        <v>883.373</v>
-      </c>
-      <c r="M81" s="22" t="n">
-        <v>784.657</v>
-      </c>
-      <c r="N81" s="22" t="n">
-        <v>715.963</v>
-      </c>
-      <c r="T81" s="22" t="n">
-        <v>723.556</v>
-      </c>
-      <c r="U81" s="22" t="n">
-        <v>1024.201</v>
-      </c>
-      <c r="V81" s="22" t="n">
-        <v>940.83</v>
-      </c>
-      <c r="W81" s="22" t="n">
-        <v>951.404</v>
-      </c>
-      <c r="X81" s="22" t="n">
-        <v>784.657</v>
-      </c>
-    </row>
     <row r="82">
-      <c r="A82" s="9" t="inlineStr">
-        <is>
-          <t>영업이익(손실)</t>
-        </is>
-      </c>
-      <c r="C82" s="12" t="n">
-        <v>89.825</v>
-      </c>
-      <c r="D82" s="12" t="n">
-        <v>56.265</v>
-      </c>
-      <c r="E82" s="12" t="n">
-        <v>152.471</v>
-      </c>
-      <c r="F82" s="12" t="n">
-        <v>82.054</v>
-      </c>
-      <c r="G82" s="12" t="n">
-        <v>217.557</v>
-      </c>
-      <c r="H82" s="12" t="n">
-        <v>108.36</v>
-      </c>
-      <c r="I82" s="12" t="n">
-        <v>50.54</v>
-      </c>
-      <c r="J82" s="12" t="n">
-        <v>-36.419</v>
-      </c>
-      <c r="K82" s="12" t="n">
-        <v>-93.577</v>
-      </c>
-      <c r="L82" s="12" t="n">
-        <v>131.672</v>
-      </c>
-      <c r="M82" s="12" t="n">
-        <v>143.451</v>
-      </c>
-      <c r="N82" s="12" t="n">
-        <v>173.992</v>
-      </c>
-      <c r="T82" s="12" t="n">
-        <v>257.105</v>
-      </c>
-      <c r="U82" s="12" t="n">
-        <v>-84.979</v>
-      </c>
-      <c r="V82" s="12" t="n">
-        <v>152.471</v>
-      </c>
-      <c r="W82" s="12" t="n">
-        <v>50.54</v>
-      </c>
-      <c r="X82" s="12" t="n">
-        <v>143.451</v>
+      <c r="A82" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G82" s="17">
+        <f>IF(OR(G81="",C81=""),"",IF(C81&lt;=0,"",IFERROR(G81/C81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H82" s="17">
+        <f>IF(OR(H81="",D81=""),"",IF(D81&lt;=0,"",IFERROR(H81/D81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I82" s="17">
+        <f>IF(OR(I81="",E81=""),"",IF(E81&lt;=0,"",IFERROR(I81/E81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J82" s="17">
+        <f>IF(OR(J81="",F81=""),"",IF(F81&lt;=0,"",IFERROR(J81/F81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K82" s="17">
+        <f>IF(OR(K81="",G81=""),"",IF(G81&lt;=0,"",IFERROR(K81/G81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L82" s="17">
+        <f>IF(OR(L81="",H81=""),"",IF(H81&lt;=0,"",IFERROR(L81/H81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M82" s="17">
+        <f>IF(OR(M81="",I81=""),"",IF(I81&lt;=0,"",IFERROR(M81/I81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N82" s="17">
+        <f>IF(OR(N81="",J81=""),"",IF(J81&lt;=0,"",IFERROR(N81/J81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T82" s="17">
+        <f>IF(OR(T81="",S81=""),"",IF(S81&lt;=0,"",IFERROR(T81/S81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U82" s="17">
+        <f>IF(OR(U81="",T81=""),"",IF(T81&lt;=0,"",IFERROR(U81/T81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V82" s="17">
+        <f>IF(OR(V81="",U81=""),"",IF(U81&lt;=0,"",IFERROR(V81/U81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W82" s="17">
+        <f>IF(OR(W81="",V81=""),"",IF(V81&lt;=0,"",IFERROR(W81/V81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X82" s="17">
+        <f>IF(OR(X81="",W81=""),"",IF(W81&lt;=0,"",IFERROR(X81/W81-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 매각이익</t>
+          <t>판매비와 관리비</t>
         </is>
       </c>
       <c r="C83" s="22" t="n">
-        <v>86.327</v>
+        <v>763.527</v>
       </c>
       <c r="D83" s="22" t="n">
-        <v>-3.508</v>
+        <v>905.89</v>
       </c>
       <c r="E83" s="22" t="n">
-        <v>11.744</v>
+        <v>940.83</v>
       </c>
       <c r="F83" s="22" t="n">
-        <v>72.143</v>
+        <v>730.548</v>
       </c>
       <c r="G83" s="22" t="n">
-        <v>92.517</v>
+        <v>755.252</v>
       </c>
       <c r="H83" s="22" t="n">
-        <v>69.042</v>
+        <v>1201.433</v>
       </c>
       <c r="I83" s="22" t="n">
-        <v>262.513</v>
+        <v>951.404</v>
       </c>
       <c r="J83" s="22" t="n">
-        <v>200.054</v>
+        <v>827.24</v>
       </c>
       <c r="K83" s="22" t="n">
-        <v>24.432</v>
+        <v>920.4160000000001</v>
       </c>
       <c r="L83" s="22" t="n">
-        <v>193.867</v>
+        <v>883.373</v>
       </c>
       <c r="M83" s="22" t="n">
-        <v>336.432</v>
+        <v>784.657</v>
       </c>
       <c r="N83" s="22" t="n">
-        <v>278.735</v>
+        <v>715.963</v>
       </c>
       <c r="T83" s="22" t="n">
-        <v>1.367</v>
+        <v>723.556</v>
       </c>
       <c r="U83" s="22" t="n">
-        <v>0</v>
+        <v>1024.201</v>
       </c>
       <c r="V83" s="22" t="n">
-        <v>11.744</v>
+        <v>940.83</v>
       </c>
       <c r="W83" s="22" t="n">
-        <v>262.513</v>
+        <v>951.404</v>
       </c>
       <c r="X83" s="22" t="n">
-        <v>336.432</v>
+        <v>784.657</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="20" t="inlineStr">
-        <is>
-          <t>외환차익</t>
-        </is>
-      </c>
-      <c r="C84" s="22" t="n">
-        <v>45.574</v>
-      </c>
-      <c r="D84" s="22" t="n">
-        <v>-64.874</v>
-      </c>
-      <c r="E84" s="22" t="n">
-        <v>74.001</v>
-      </c>
-      <c r="F84" s="22" t="n">
-        <v>101.458</v>
-      </c>
-      <c r="G84" s="22" t="n">
-        <v>-101.458</v>
-      </c>
-      <c r="J84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T84" s="22" t="n">
-        <v>58.464</v>
-      </c>
-      <c r="U84" s="22" t="n">
-        <v>24.536</v>
-      </c>
-      <c r="V84" s="22" t="n">
-        <v>74.001</v>
+      <c r="A84" s="9" t="inlineStr">
+        <is>
+          <t>영업이익(손실)</t>
+        </is>
+      </c>
+      <c r="C84" s="12" t="n">
+        <v>89.825</v>
+      </c>
+      <c r="D84" s="12" t="n">
+        <v>56.265</v>
+      </c>
+      <c r="E84" s="12" t="n">
+        <v>152.471</v>
+      </c>
+      <c r="F84" s="12" t="n">
+        <v>82.054</v>
+      </c>
+      <c r="G84" s="12" t="n">
+        <v>217.557</v>
+      </c>
+      <c r="H84" s="12" t="n">
+        <v>108.36</v>
+      </c>
+      <c r="I84" s="12" t="n">
+        <v>50.54</v>
+      </c>
+      <c r="J84" s="12" t="n">
+        <v>-36.419</v>
+      </c>
+      <c r="K84" s="12" t="n">
+        <v>-93.577</v>
+      </c>
+      <c r="L84" s="12" t="n">
+        <v>131.672</v>
+      </c>
+      <c r="M84" s="12" t="n">
+        <v>143.451</v>
+      </c>
+      <c r="N84" s="12" t="n">
+        <v>173.992</v>
+      </c>
+      <c r="T84" s="12" t="n">
+        <v>257.105</v>
+      </c>
+      <c r="U84" s="12" t="n">
+        <v>-84.979</v>
+      </c>
+      <c r="V84" s="12" t="n">
+        <v>152.471</v>
+      </c>
+      <c r="W84" s="12" t="n">
+        <v>50.54</v>
+      </c>
+      <c r="X84" s="12" t="n">
+        <v>143.451</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="20" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C85" s="22" t="n">
-        <v>31.953</v>
-      </c>
-      <c r="D85" s="22" t="n">
-        <v>92.54000000000001</v>
-      </c>
-      <c r="E85" s="22" t="n">
-        <v>-118.295</v>
-      </c>
-      <c r="F85" s="22" t="n">
-        <v>44.774</v>
-      </c>
-      <c r="G85" s="22" t="n">
-        <v>64.468</v>
-      </c>
-      <c r="H85" s="22" t="n">
-        <v>67.15000000000001</v>
-      </c>
-      <c r="I85" s="22" t="n">
-        <v>-65.53400000000001</v>
-      </c>
-      <c r="J85" s="22" t="n">
-        <v>13.953</v>
-      </c>
-      <c r="K85" s="22" t="n">
-        <v>27.805</v>
-      </c>
-      <c r="L85" s="22" t="n">
-        <v>76.06699999999999</v>
-      </c>
-      <c r="M85" s="22" t="n">
-        <v>-79.17400000000001</v>
-      </c>
-      <c r="N85" s="22" t="n">
-        <v>41.138</v>
-      </c>
-      <c r="T85" s="22" t="n">
-        <v>9.548999999999999</v>
-      </c>
-      <c r="U85" s="22" t="n">
-        <v>11.891</v>
-      </c>
-      <c r="V85" s="22" t="n">
-        <v>-118.295</v>
-      </c>
-      <c r="W85" s="22" t="n">
-        <v>-65.53400000000001</v>
-      </c>
-      <c r="X85" s="22" t="n">
-        <v>-79.17400000000001</v>
+      <c r="A85" s="45" t="inlineStr">
+        <is>
+          <t>OPM</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>영업이익 ÷ 매출</t>
+        </is>
+      </c>
+      <c r="C85" s="17">
+        <f>IF(OR(C84="",C78=""),"",IF(C78&lt;=0,"",IFERROR(C84/C78,"")))</f>
+        <v/>
+      </c>
+      <c r="D85" s="17">
+        <f>IF(OR(D84="",D78=""),"",IF(D78&lt;=0,"",IFERROR(D84/D78,"")))</f>
+        <v/>
+      </c>
+      <c r="E85" s="17">
+        <f>IF(OR(E84="",E78=""),"",IF(E78&lt;=0,"",IFERROR(E84/E78,"")))</f>
+        <v/>
+      </c>
+      <c r="F85" s="17">
+        <f>IF(OR(F84="",F78=""),"",IF(F78&lt;=0,"",IFERROR(F84/F78,"")))</f>
+        <v/>
+      </c>
+      <c r="G85" s="17">
+        <f>IF(OR(G84="",G78=""),"",IF(G78&lt;=0,"",IFERROR(G84/G78,"")))</f>
+        <v/>
+      </c>
+      <c r="H85" s="17">
+        <f>IF(OR(H84="",H78=""),"",IF(H78&lt;=0,"",IFERROR(H84/H78,"")))</f>
+        <v/>
+      </c>
+      <c r="I85" s="17">
+        <f>IF(OR(I84="",I78=""),"",IF(I78&lt;=0,"",IFERROR(I84/I78,"")))</f>
+        <v/>
+      </c>
+      <c r="J85" s="17">
+        <f>IF(OR(J84="",J78=""),"",IF(J78&lt;=0,"",IFERROR(J84/J78,"")))</f>
+        <v/>
+      </c>
+      <c r="K85" s="17">
+        <f>IF(OR(K84="",K78=""),"",IF(K78&lt;=0,"",IFERROR(K84/K78,"")))</f>
+        <v/>
+      </c>
+      <c r="L85" s="17">
+        <f>IF(OR(L84="",L78=""),"",IF(L78&lt;=0,"",IFERROR(L84/L78,"")))</f>
+        <v/>
+      </c>
+      <c r="M85" s="17">
+        <f>IF(OR(M84="",M78=""),"",IF(M78&lt;=0,"",IFERROR(M84/M78,"")))</f>
+        <v/>
+      </c>
+      <c r="N85" s="17">
+        <f>IF(OR(N84="",N78=""),"",IF(N78&lt;=0,"",IFERROR(N84/N78,"")))</f>
+        <v/>
+      </c>
+      <c r="T85" s="17">
+        <f>IF(OR(T84="",T78=""),"",IF(T78&lt;=0,"",IFERROR(T84/T78,"")))</f>
+        <v/>
+      </c>
+      <c r="U85" s="17">
+        <f>IF(OR(U84="",U78=""),"",IF(U78&lt;=0,"",IFERROR(U84/U78,"")))</f>
+        <v/>
+      </c>
+      <c r="V85" s="17">
+        <f>IF(OR(V84="",V78=""),"",IF(V78&lt;=0,"",IFERROR(V84/V78,"")))</f>
+        <v/>
+      </c>
+      <c r="W85" s="17">
+        <f>IF(OR(W84="",W78=""),"",IF(W78&lt;=0,"",IFERROR(W84/W78,"")))</f>
+        <v/>
+      </c>
+      <c r="X85" s="17">
+        <f>IF(OR(X84="",X78=""),"",IF(X78&lt;=0,"",IFERROR(X84/X78,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="20" t="inlineStr">
-        <is>
-          <t>영업외수익 합계</t>
-        </is>
-      </c>
-      <c r="C86" s="22" t="n">
-        <v>163.855</v>
-      </c>
-      <c r="D86" s="22" t="n">
-        <v>-63.547</v>
-      </c>
-      <c r="E86" s="22" t="n">
-        <v>99.84099999999999</v>
-      </c>
-      <c r="F86" s="22" t="n">
-        <v>218.376</v>
-      </c>
-      <c r="G86" s="22" t="n">
-        <v>55.526</v>
-      </c>
-      <c r="H86" s="22" t="n">
-        <v>136.192</v>
-      </c>
-      <c r="I86" s="22" t="n">
-        <v>248.612</v>
-      </c>
-      <c r="J86" s="22" t="n">
-        <v>214.008</v>
-      </c>
-      <c r="K86" s="22" t="n">
-        <v>52.236</v>
-      </c>
-      <c r="L86" s="22" t="n">
-        <v>269.935</v>
-      </c>
-      <c r="M86" s="22" t="n">
-        <v>478.309</v>
-      </c>
-      <c r="N86" s="22" t="n">
-        <v>319.873</v>
-      </c>
-      <c r="T86" s="22" t="n">
-        <v>88.861</v>
-      </c>
-      <c r="U86" s="22" t="n">
-        <v>36.426</v>
-      </c>
-      <c r="V86" s="22" t="n">
-        <v>99.84099999999999</v>
-      </c>
-      <c r="W86" s="22" t="n">
-        <v>248.612</v>
-      </c>
-      <c r="X86" s="22" t="n">
-        <v>478.309</v>
+      <c r="A86" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G86" s="17">
+        <f>IF(OR(G84="",C84=""),"",IF(C84&lt;=0,"",IFERROR(G84/C84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H86" s="17">
+        <f>IF(OR(H84="",D84=""),"",IF(D84&lt;=0,"",IFERROR(H84/D84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I86" s="17">
+        <f>IF(OR(I84="",E84=""),"",IF(E84&lt;=0,"",IFERROR(I84/E84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J86" s="17">
+        <f>IF(OR(J84="",F84=""),"",IF(F84&lt;=0,"",IFERROR(J84/F84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K86" s="17">
+        <f>IF(OR(K84="",G84=""),"",IF(G84&lt;=0,"",IFERROR(K84/G84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L86" s="17">
+        <f>IF(OR(L84="",H84=""),"",IF(H84&lt;=0,"",IFERROR(L84/H84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M86" s="17">
+        <f>IF(OR(M84="",I84=""),"",IF(I84&lt;=0,"",IFERROR(M84/I84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N86" s="17">
+        <f>IF(OR(N84="",J84=""),"",IF(J84&lt;=0,"",IFERROR(N84/J84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T86" s="17">
+        <f>IF(OR(T84="",S84=""),"",IF(S84&lt;=0,"",IFERROR(T84/S84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U86" s="17">
+        <f>IF(OR(U84="",T84=""),"",IF(T84&lt;=0,"",IFERROR(U84/T84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V86" s="17">
+        <f>IF(OR(V84="",U84=""),"",IF(U84&lt;=0,"",IFERROR(V84/U84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W86" s="17">
+        <f>IF(OR(W84="",V84=""),"",IF(V84&lt;=0,"",IFERROR(W84/V84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X86" s="17">
+        <f>IF(OR(X84="",W84=""),"",IF(W84&lt;=0,"",IFERROR(X84/W84-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 매각손실</t>
+          <t>투자유가증권 매각이익</t>
         </is>
       </c>
       <c r="C87" s="22" t="n">
-        <v>0</v>
+        <v>86.327</v>
       </c>
       <c r="D87" s="22" t="n">
-        <v>0</v>
+        <v>-3.508</v>
       </c>
       <c r="E87" s="22" t="n">
-        <v>0</v>
+        <v>11.744</v>
       </c>
       <c r="F87" s="22" t="n">
-        <v>0</v>
+        <v>72.143</v>
       </c>
       <c r="G87" s="22" t="n">
-        <v>0</v>
+        <v>92.517</v>
       </c>
       <c r="H87" s="22" t="n">
-        <v>20.547</v>
+        <v>69.042</v>
       </c>
       <c r="I87" s="22" t="n">
-        <v>136.157</v>
+        <v>262.513</v>
+      </c>
+      <c r="J87" s="22" t="n">
+        <v>200.054</v>
+      </c>
+      <c r="K87" s="22" t="n">
+        <v>24.432</v>
+      </c>
+      <c r="L87" s="22" t="n">
+        <v>193.867</v>
       </c>
       <c r="M87" s="22" t="n">
-        <v>0</v>
+        <v>336.432</v>
+      </c>
+      <c r="N87" s="22" t="n">
+        <v>278.735</v>
       </c>
       <c r="T87" s="22" t="n">
-        <v>0</v>
+        <v>1.367</v>
       </c>
       <c r="U87" s="22" t="n">
         <v>0</v>
       </c>
       <c r="V87" s="22" t="n">
-        <v>0</v>
+        <v>11.744</v>
       </c>
       <c r="W87" s="22" t="n">
-        <v>136.157</v>
+        <v>262.513</v>
       </c>
       <c r="X87" s="22" t="n">
-        <v>0</v>
+        <v>336.432</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="20" t="inlineStr">
         <is>
-          <t>외환차손</t>
-        </is>
+          <t>외환차익</t>
+        </is>
+      </c>
+      <c r="C88" s="22" t="n">
+        <v>45.574</v>
+      </c>
+      <c r="D88" s="22" t="n">
+        <v>-64.874</v>
+      </c>
+      <c r="E88" s="22" t="n">
+        <v>74.001</v>
       </c>
       <c r="F88" s="22" t="n">
+        <v>101.458</v>
+      </c>
+      <c r="G88" s="22" t="n">
+        <v>-101.458</v>
+      </c>
+      <c r="J88" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="G88" s="22" t="n">
-        <v>69.57599999999999</v>
-      </c>
-      <c r="J88" s="22" t="n">
-        <v>42.152</v>
-      </c>
-      <c r="K88" s="22" t="n">
-        <v>-39.898</v>
+      <c r="T88" s="22" t="n">
+        <v>58.464</v>
+      </c>
+      <c r="U88" s="22" t="n">
+        <v>24.536</v>
+      </c>
+      <c r="V88" s="22" t="n">
+        <v>74.001</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="20" t="inlineStr">
         <is>
-          <t>이자비용</t>
-        </is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="C89" s="22" t="n">
+        <v>31.953</v>
+      </c>
+      <c r="D89" s="22" t="n">
+        <v>92.54000000000001</v>
+      </c>
+      <c r="E89" s="22" t="n">
+        <v>-118.295</v>
       </c>
       <c r="F89" s="22" t="n">
-        <v>0.054</v>
+        <v>44.774</v>
+      </c>
+      <c r="G89" s="22" t="n">
+        <v>64.468</v>
+      </c>
+      <c r="H89" s="22" t="n">
+        <v>67.15000000000001</v>
+      </c>
+      <c r="I89" s="22" t="n">
+        <v>-65.53400000000001</v>
       </c>
       <c r="J89" s="22" t="n">
-        <v>0.034</v>
+        <v>13.953</v>
+      </c>
+      <c r="K89" s="22" t="n">
+        <v>27.805</v>
+      </c>
+      <c r="L89" s="22" t="n">
+        <v>76.06699999999999</v>
+      </c>
+      <c r="M89" s="22" t="n">
+        <v>-79.17400000000001</v>
       </c>
       <c r="N89" s="22" t="n">
-        <v>0.013</v>
+        <v>41.138</v>
+      </c>
+      <c r="T89" s="22" t="n">
+        <v>9.548999999999999</v>
+      </c>
+      <c r="U89" s="22" t="n">
+        <v>11.891</v>
+      </c>
+      <c r="V89" s="22" t="n">
+        <v>-118.295</v>
+      </c>
+      <c r="W89" s="22" t="n">
+        <v>-65.53400000000001</v>
+      </c>
+      <c r="X89" s="22" t="n">
+        <v>-79.17400000000001</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>영업외수익 합계</t>
         </is>
       </c>
       <c r="C90" s="22" t="n">
-        <v>0.015</v>
+        <v>163.855</v>
       </c>
       <c r="D90" s="22" t="n">
-        <v>0.453</v>
+        <v>-63.547</v>
       </c>
       <c r="E90" s="22" t="n">
-        <v>-7.468</v>
+        <v>99.84099999999999</v>
       </c>
       <c r="F90" s="22" t="n">
-        <v>0.07199999999999999</v>
+        <v>218.376</v>
       </c>
       <c r="G90" s="22" t="n">
-        <v>0.049</v>
+        <v>55.526</v>
       </c>
       <c r="H90" s="22" t="n">
-        <v>0.044</v>
+        <v>136.192</v>
       </c>
       <c r="I90" s="22" t="n">
-        <v>0.039</v>
+        <v>248.612</v>
       </c>
       <c r="J90" s="22" t="n">
-        <v>42.309</v>
+        <v>214.008</v>
       </c>
       <c r="K90" s="22" t="n">
-        <v>-42.089</v>
+        <v>52.236</v>
       </c>
       <c r="L90" s="22" t="n">
-        <v>0.024</v>
+        <v>269.935</v>
       </c>
       <c r="M90" s="22" t="n">
-        <v>0.051</v>
+        <v>478.309</v>
       </c>
       <c r="N90" s="22" t="n">
-        <v>0.018</v>
+        <v>319.873</v>
       </c>
       <c r="T90" s="22" t="n">
-        <v>0.051</v>
+        <v>88.861</v>
       </c>
       <c r="U90" s="22" t="n">
-        <v>0.008</v>
+        <v>36.426</v>
       </c>
       <c r="V90" s="22" t="n">
-        <v>-7.468</v>
+        <v>99.84099999999999</v>
       </c>
       <c r="W90" s="22" t="n">
-        <v>0.039</v>
+        <v>248.612</v>
       </c>
       <c r="X90" s="22" t="n">
-        <v>0.051</v>
+        <v>478.309</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="20" t="inlineStr">
         <is>
-          <t>영업외비용 합계</t>
+          <t>투자유가증권 매각손실</t>
         </is>
       </c>
       <c r="C91" s="22" t="n">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="D91" s="22" t="n">
-        <v>0.453</v>
+        <v>0</v>
       </c>
       <c r="E91" s="22" t="n">
-        <v>0.064</v>
+        <v>0</v>
       </c>
       <c r="F91" s="22" t="n">
-        <v>0.07199999999999999</v>
+        <v>0</v>
       </c>
       <c r="G91" s="22" t="n">
-        <v>69.625</v>
+        <v>0</v>
       </c>
       <c r="H91" s="22" t="n">
-        <v>-48.984</v>
+        <v>20.547</v>
       </c>
       <c r="I91" s="22" t="n">
-        <v>172.279</v>
-      </c>
-      <c r="J91" s="22" t="n">
-        <v>42.344</v>
-      </c>
-      <c r="K91" s="22" t="n">
-        <v>-39.87</v>
-      </c>
-      <c r="L91" s="22" t="n">
-        <v>0.38</v>
+        <v>136.157</v>
       </c>
       <c r="M91" s="22" t="n">
-        <v>0.051</v>
-      </c>
-      <c r="N91" s="22" t="n">
-        <v>0.031</v>
+        <v>0</v>
       </c>
       <c r="T91" s="22" t="n">
-        <v>1.863</v>
+        <v>0</v>
       </c>
       <c r="U91" s="22" t="n">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="V91" s="22" t="n">
-        <v>0.064</v>
+        <v>0</v>
       </c>
       <c r="W91" s="22" t="n">
-        <v>172.279</v>
+        <v>136.157</v>
       </c>
       <c r="X91" s="22" t="n">
-        <v>0.051</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="9" t="inlineStr">
-        <is>
-          <t>경상이익</t>
-        </is>
-      </c>
-      <c r="C92" s="12" t="n">
-        <v>253.672</v>
-      </c>
-      <c r="D92" s="12" t="n">
-        <v>-7.734</v>
-      </c>
-      <c r="E92" s="12" t="n">
-        <v>252.248</v>
-      </c>
-      <c r="F92" s="12" t="n">
-        <v>300.359</v>
-      </c>
-      <c r="G92" s="12" t="n">
-        <v>203.457</v>
-      </c>
-      <c r="H92" s="12" t="n">
-        <v>293.537</v>
-      </c>
-      <c r="I92" s="12" t="n">
-        <v>126.872</v>
-      </c>
-      <c r="J92" s="12" t="n">
-        <v>135.244</v>
-      </c>
-      <c r="K92" s="12" t="n">
-        <v>-1.471</v>
-      </c>
-      <c r="L92" s="12" t="n">
-        <v>401.228</v>
-      </c>
-      <c r="M92" s="12" t="n">
-        <v>621.7089999999999</v>
-      </c>
-      <c r="N92" s="12" t="n">
-        <v>493.834</v>
-      </c>
-      <c r="T92" s="12" t="n">
-        <v>344.104</v>
-      </c>
-      <c r="U92" s="12" t="n">
-        <v>-48.56</v>
-      </c>
-      <c r="V92" s="12" t="n">
-        <v>252.248</v>
-      </c>
-      <c r="W92" s="12" t="n">
-        <v>126.872</v>
-      </c>
-      <c r="X92" s="12" t="n">
-        <v>621.7089999999999</v>
+      <c r="A92" s="20" t="inlineStr">
+        <is>
+          <t>외환차손</t>
+        </is>
+      </c>
+      <c r="F92" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" s="22" t="n">
+        <v>69.57599999999999</v>
+      </c>
+      <c r="J92" s="22" t="n">
+        <v>42.152</v>
+      </c>
+      <c r="K92" s="22" t="n">
+        <v>-39.898</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="9" t="inlineStr">
-        <is>
-          <t>법인세차감전 순이익</t>
-        </is>
-      </c>
-      <c r="C93" s="12" t="n">
-        <v>253.672</v>
-      </c>
-      <c r="D93" s="12" t="n">
-        <v>-7.734</v>
-      </c>
-      <c r="E93" s="12" t="n">
-        <v>252.248</v>
-      </c>
-      <c r="F93" s="12" t="n">
-        <v>300.359</v>
-      </c>
-      <c r="G93" s="12" t="n">
-        <v>203.457</v>
-      </c>
-      <c r="H93" s="12" t="n">
-        <v>293.537</v>
-      </c>
-      <c r="I93" s="12" t="n">
-        <v>126.872</v>
-      </c>
-      <c r="J93" s="12" t="n">
-        <v>135.244</v>
-      </c>
-      <c r="K93" s="12" t="n">
-        <v>-1.471</v>
-      </c>
-      <c r="L93" s="12" t="n">
-        <v>401.228</v>
-      </c>
-      <c r="M93" s="12" t="n">
-        <v>621.7089999999999</v>
-      </c>
-      <c r="N93" s="12" t="n">
-        <v>493.834</v>
-      </c>
-      <c r="T93" s="12" t="n">
-        <v>344.104</v>
-      </c>
-      <c r="U93" s="12" t="n">
-        <v>-48.56</v>
-      </c>
-      <c r="V93" s="12" t="n">
-        <v>252.248</v>
-      </c>
-      <c r="W93" s="12" t="n">
-        <v>126.872</v>
-      </c>
-      <c r="X93" s="12" t="n">
-        <v>621.7089999999999</v>
+      <c r="A93" s="20" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="F93" s="22" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="J93" s="22" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="N93" s="22" t="n">
+        <v>0.013</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="20" t="inlineStr">
         <is>
-          <t>법인세·주민세·사업세</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="C94" s="22" t="n">
-        <v>103.526</v>
+        <v>0.015</v>
       </c>
       <c r="D94" s="22" t="n">
-        <v>36.546</v>
+        <v>0.453</v>
       </c>
       <c r="E94" s="22" t="n">
-        <v>139.415</v>
+        <v>-7.468</v>
       </c>
       <c r="F94" s="22" t="n">
-        <v>97.405</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="G94" s="22" t="n">
-        <v>44.355</v>
+        <v>0.049</v>
       </c>
       <c r="H94" s="22" t="n">
-        <v>154.788</v>
+        <v>0.044</v>
       </c>
       <c r="I94" s="22" t="n">
-        <v>108.576</v>
+        <v>0.039</v>
       </c>
       <c r="J94" s="22" t="n">
-        <v>0.666</v>
+        <v>42.309</v>
       </c>
       <c r="K94" s="22" t="n">
-        <v>19.407</v>
+        <v>-42.089</v>
       </c>
       <c r="L94" s="22" t="n">
-        <v>102.47</v>
+        <v>0.024</v>
       </c>
       <c r="M94" s="22" t="n">
-        <v>147.353</v>
+        <v>0.051</v>
       </c>
       <c r="N94" s="22" t="n">
-        <v>103.496</v>
+        <v>0.018</v>
       </c>
       <c r="T94" s="22" t="n">
-        <v>127.138</v>
+        <v>0.051</v>
       </c>
       <c r="U94" s="22" t="n">
-        <v>70.32599999999999</v>
+        <v>0.008</v>
       </c>
       <c r="V94" s="22" t="n">
-        <v>139.415</v>
+        <v>-7.468</v>
       </c>
       <c r="W94" s="22" t="n">
-        <v>108.576</v>
+        <v>0.039</v>
       </c>
       <c r="X94" s="22" t="n">
-        <v>147.353</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="20" t="inlineStr">
         <is>
-          <t>법인세 조정액</t>
+          <t>영업외비용 합계</t>
         </is>
       </c>
       <c r="C95" s="22" t="n">
-        <v>-29.064</v>
+        <v>0.007</v>
       </c>
       <c r="D95" s="22" t="n">
-        <v>-31.751</v>
+        <v>0.453</v>
       </c>
       <c r="E95" s="22" t="n">
-        <v>-38.805</v>
+        <v>0.064</v>
       </c>
       <c r="F95" s="22" t="n">
-        <v>-3.977</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="G95" s="22" t="n">
-        <v>19.78</v>
+        <v>69.625</v>
       </c>
       <c r="H95" s="22" t="n">
-        <v>-62.566</v>
+        <v>-48.984</v>
       </c>
       <c r="I95" s="22" t="n">
-        <v>-65.495</v>
+        <v>172.279</v>
       </c>
       <c r="J95" s="22" t="n">
-        <v>53.003</v>
+        <v>42.344</v>
       </c>
       <c r="K95" s="22" t="n">
-        <v>-39.45</v>
+        <v>-39.87</v>
       </c>
       <c r="L95" s="22" t="n">
-        <v>26.195</v>
+        <v>0.38</v>
       </c>
       <c r="M95" s="22" t="n">
-        <v>66.895</v>
+        <v>0.051</v>
       </c>
       <c r="N95" s="22" t="n">
-        <v>57.334</v>
+        <v>0.031</v>
       </c>
       <c r="T95" s="22" t="n">
-        <v>-22.146</v>
+        <v>1.863</v>
       </c>
       <c r="U95" s="22" t="n">
-        <v>-51.448</v>
+        <v>0.008</v>
       </c>
       <c r="V95" s="22" t="n">
-        <v>-38.805</v>
+        <v>0.064</v>
       </c>
       <c r="W95" s="22" t="n">
-        <v>-65.495</v>
+        <v>172.279</v>
       </c>
       <c r="X95" s="22" t="n">
-        <v>66.895</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="20" t="inlineStr">
-        <is>
-          <t>법인세 등 합계</t>
-        </is>
-      </c>
-      <c r="C96" s="22" t="n">
-        <v>74.461</v>
-      </c>
-      <c r="D96" s="22" t="n">
-        <v>4.796</v>
-      </c>
-      <c r="E96" s="22" t="n">
-        <v>100.61</v>
-      </c>
-      <c r="F96" s="22" t="n">
-        <v>93.428</v>
-      </c>
-      <c r="G96" s="22" t="n">
-        <v>64.13500000000001</v>
-      </c>
-      <c r="H96" s="22" t="n">
-        <v>92.221</v>
-      </c>
-      <c r="I96" s="22" t="n">
-        <v>43.082</v>
-      </c>
-      <c r="J96" s="22" t="n">
-        <v>53.67</v>
-      </c>
-      <c r="K96" s="22" t="n">
-        <v>-20.044</v>
-      </c>
-      <c r="L96" s="22" t="n">
-        <v>128.665</v>
-      </c>
-      <c r="M96" s="22" t="n">
-        <v>214.249</v>
-      </c>
-      <c r="N96" s="22" t="n">
-        <v>160.831</v>
-      </c>
-      <c r="T96" s="22" t="n">
-        <v>104.991</v>
-      </c>
-      <c r="U96" s="22" t="n">
-        <v>18.878</v>
-      </c>
-      <c r="V96" s="22" t="n">
-        <v>100.61</v>
-      </c>
-      <c r="W96" s="22" t="n">
-        <v>43.082</v>
-      </c>
-      <c r="X96" s="22" t="n">
-        <v>214.249</v>
+      <c r="A96" s="9" t="inlineStr">
+        <is>
+          <t>경상이익</t>
+        </is>
+      </c>
+      <c r="C96" s="12" t="n">
+        <v>253.672</v>
+      </c>
+      <c r="D96" s="12" t="n">
+        <v>-7.734</v>
+      </c>
+      <c r="E96" s="12" t="n">
+        <v>252.248</v>
+      </c>
+      <c r="F96" s="12" t="n">
+        <v>300.359</v>
+      </c>
+      <c r="G96" s="12" t="n">
+        <v>203.457</v>
+      </c>
+      <c r="H96" s="12" t="n">
+        <v>293.537</v>
+      </c>
+      <c r="I96" s="12" t="n">
+        <v>126.872</v>
+      </c>
+      <c r="J96" s="12" t="n">
+        <v>135.244</v>
+      </c>
+      <c r="K96" s="12" t="n">
+        <v>-1.471</v>
+      </c>
+      <c r="L96" s="12" t="n">
+        <v>401.228</v>
+      </c>
+      <c r="M96" s="12" t="n">
+        <v>621.7089999999999</v>
+      </c>
+      <c r="N96" s="12" t="n">
+        <v>493.834</v>
+      </c>
+      <c r="T96" s="12" t="n">
+        <v>344.104</v>
+      </c>
+      <c r="U96" s="12" t="n">
+        <v>-48.56</v>
+      </c>
+      <c r="V96" s="12" t="n">
+        <v>252.248</v>
+      </c>
+      <c r="W96" s="12" t="n">
+        <v>126.872</v>
+      </c>
+      <c r="X96" s="12" t="n">
+        <v>621.7089999999999</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="9" t="inlineStr">
-        <is>
-          <t>순이익</t>
-        </is>
-      </c>
-      <c r="C97" s="12" t="n">
-        <v>179.211</v>
-      </c>
-      <c r="D97" s="12" t="n">
-        <v>-12.53</v>
-      </c>
-      <c r="E97" s="12" t="n">
-        <v>151.639</v>
-      </c>
-      <c r="F97" s="12" t="n">
-        <v>206.93</v>
-      </c>
-      <c r="G97" s="12" t="n">
-        <v>139.322</v>
-      </c>
-      <c r="H97" s="12" t="n">
-        <v>201.316</v>
-      </c>
-      <c r="I97" s="12" t="n">
-        <v>83.791</v>
-      </c>
-      <c r="J97" s="12" t="n">
-        <v>81.574</v>
-      </c>
-      <c r="K97" s="12" t="n">
-        <v>18.572</v>
-      </c>
-      <c r="L97" s="12" t="n">
-        <v>272.563</v>
-      </c>
-      <c r="M97" s="12" t="n">
-        <v>407.461</v>
-      </c>
-      <c r="N97" s="12" t="n">
-        <v>333.003</v>
-      </c>
-      <c r="T97" s="12" t="n">
-        <v>239.113</v>
-      </c>
-      <c r="U97" s="12" t="n">
-        <v>-67.438</v>
-      </c>
-      <c r="V97" s="12" t="n">
-        <v>151.639</v>
-      </c>
-      <c r="W97" s="12" t="n">
-        <v>83.791</v>
-      </c>
-      <c r="X97" s="12" t="n">
-        <v>407.461</v>
+      <c r="A97" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G97" s="17">
+        <f>IF(OR(G96="",C96=""),"",IF(C96&lt;=0,"",IFERROR(G96/C96-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H97" s="17">
+        <f>IF(OR(H96="",D96=""),"",IF(D96&lt;=0,"",IFERROR(H96/D96-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I97" s="17">
+        <f>IF(OR(I96="",E96=""),"",IF(E96&lt;=0,"",IFERROR(I96/E96-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J97" s="17">
+        <f>IF(OR(J96="",F96=""),"",IF(F96&lt;=0,"",IFERROR(J96/F96-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K97" s="17">
+        <f>IF(OR(K96="",G96=""),"",IF(G96&lt;=0,"",IFERROR(K96/G96-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L97" s="17">
+        <f>IF(OR(L96="",H96=""),"",IF(H96&lt;=0,"",IFERROR(L96/H96-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M97" s="17">
+        <f>IF(OR(M96="",I96=""),"",IF(I96&lt;=0,"",IFERROR(M96/I96-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N97" s="17">
+        <f>IF(OR(N96="",J96=""),"",IF(J96&lt;=0,"",IFERROR(N96/J96-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T97" s="17">
+        <f>IF(OR(T96="",S96=""),"",IF(S96&lt;=0,"",IFERROR(T96/S96-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U97" s="17">
+        <f>IF(OR(U96="",T96=""),"",IF(T96&lt;=0,"",IFERROR(U96/T96-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V97" s="17">
+        <f>IF(OR(V96="",U96=""),"",IF(U96&lt;=0,"",IFERROR(V96/U96-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W97" s="17">
+        <f>IF(OR(W96="",V96=""),"",IF(V96&lt;=0,"",IFERROR(W96/V96-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X97" s="17">
+        <f>IF(OR(X96="",W96=""),"",IF(W96&lt;=0,"",IFERROR(X96/W96-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="9" t="inlineStr">
         <is>
+          <t>법인세차감전 순이익</t>
+        </is>
+      </c>
+      <c r="C98" s="12" t="n">
+        <v>253.672</v>
+      </c>
+      <c r="D98" s="12" t="n">
+        <v>-7.734</v>
+      </c>
+      <c r="E98" s="12" t="n">
+        <v>252.248</v>
+      </c>
+      <c r="F98" s="12" t="n">
+        <v>300.359</v>
+      </c>
+      <c r="G98" s="12" t="n">
+        <v>203.457</v>
+      </c>
+      <c r="H98" s="12" t="n">
+        <v>293.537</v>
+      </c>
+      <c r="I98" s="12" t="n">
+        <v>126.872</v>
+      </c>
+      <c r="J98" s="12" t="n">
+        <v>135.244</v>
+      </c>
+      <c r="K98" s="12" t="n">
+        <v>-1.471</v>
+      </c>
+      <c r="L98" s="12" t="n">
+        <v>401.228</v>
+      </c>
+      <c r="M98" s="12" t="n">
+        <v>621.7089999999999</v>
+      </c>
+      <c r="N98" s="12" t="n">
+        <v>493.834</v>
+      </c>
+      <c r="T98" s="12" t="n">
+        <v>344.104</v>
+      </c>
+      <c r="U98" s="12" t="n">
+        <v>-48.56</v>
+      </c>
+      <c r="V98" s="12" t="n">
+        <v>252.248</v>
+      </c>
+      <c r="W98" s="12" t="n">
+        <v>126.872</v>
+      </c>
+      <c r="X98" s="12" t="n">
+        <v>621.7089999999999</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="20" t="inlineStr">
+        <is>
+          <t>법인세·주민세·사업세</t>
+        </is>
+      </c>
+      <c r="C99" s="22" t="n">
+        <v>103.526</v>
+      </c>
+      <c r="D99" s="22" t="n">
+        <v>36.546</v>
+      </c>
+      <c r="E99" s="22" t="n">
+        <v>139.415</v>
+      </c>
+      <c r="F99" s="22" t="n">
+        <v>97.405</v>
+      </c>
+      <c r="G99" s="22" t="n">
+        <v>44.355</v>
+      </c>
+      <c r="H99" s="22" t="n">
+        <v>154.788</v>
+      </c>
+      <c r="I99" s="22" t="n">
+        <v>108.576</v>
+      </c>
+      <c r="J99" s="22" t="n">
+        <v>0.666</v>
+      </c>
+      <c r="K99" s="22" t="n">
+        <v>19.407</v>
+      </c>
+      <c r="L99" s="22" t="n">
+        <v>102.47</v>
+      </c>
+      <c r="M99" s="22" t="n">
+        <v>147.353</v>
+      </c>
+      <c r="N99" s="22" t="n">
+        <v>103.496</v>
+      </c>
+      <c r="T99" s="22" t="n">
+        <v>127.138</v>
+      </c>
+      <c r="U99" s="22" t="n">
+        <v>70.32599999999999</v>
+      </c>
+      <c r="V99" s="22" t="n">
+        <v>139.415</v>
+      </c>
+      <c r="W99" s="22" t="n">
+        <v>108.576</v>
+      </c>
+      <c r="X99" s="22" t="n">
+        <v>147.353</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="20" t="inlineStr">
+        <is>
+          <t>법인세 조정액</t>
+        </is>
+      </c>
+      <c r="C100" s="22" t="n">
+        <v>-29.064</v>
+      </c>
+      <c r="D100" s="22" t="n">
+        <v>-31.751</v>
+      </c>
+      <c r="E100" s="22" t="n">
+        <v>-38.805</v>
+      </c>
+      <c r="F100" s="22" t="n">
+        <v>-3.977</v>
+      </c>
+      <c r="G100" s="22" t="n">
+        <v>19.78</v>
+      </c>
+      <c r="H100" s="22" t="n">
+        <v>-62.566</v>
+      </c>
+      <c r="I100" s="22" t="n">
+        <v>-65.495</v>
+      </c>
+      <c r="J100" s="22" t="n">
+        <v>53.003</v>
+      </c>
+      <c r="K100" s="22" t="n">
+        <v>-39.45</v>
+      </c>
+      <c r="L100" s="22" t="n">
+        <v>26.195</v>
+      </c>
+      <c r="M100" s="22" t="n">
+        <v>66.895</v>
+      </c>
+      <c r="N100" s="22" t="n">
+        <v>57.334</v>
+      </c>
+      <c r="T100" s="22" t="n">
+        <v>-22.146</v>
+      </c>
+      <c r="U100" s="22" t="n">
+        <v>-51.448</v>
+      </c>
+      <c r="V100" s="22" t="n">
+        <v>-38.805</v>
+      </c>
+      <c r="W100" s="22" t="n">
+        <v>-65.495</v>
+      </c>
+      <c r="X100" s="22" t="n">
+        <v>66.895</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="20" t="inlineStr">
+        <is>
+          <t>법인세 등 합계</t>
+        </is>
+      </c>
+      <c r="C101" s="22" t="n">
+        <v>74.461</v>
+      </c>
+      <c r="D101" s="22" t="n">
+        <v>4.796</v>
+      </c>
+      <c r="E101" s="22" t="n">
+        <v>100.61</v>
+      </c>
+      <c r="F101" s="22" t="n">
+        <v>93.428</v>
+      </c>
+      <c r="G101" s="22" t="n">
+        <v>64.13500000000001</v>
+      </c>
+      <c r="H101" s="22" t="n">
+        <v>92.221</v>
+      </c>
+      <c r="I101" s="22" t="n">
+        <v>43.082</v>
+      </c>
+      <c r="J101" s="22" t="n">
+        <v>53.67</v>
+      </c>
+      <c r="K101" s="22" t="n">
+        <v>-20.044</v>
+      </c>
+      <c r="L101" s="22" t="n">
+        <v>128.665</v>
+      </c>
+      <c r="M101" s="22" t="n">
+        <v>214.249</v>
+      </c>
+      <c r="N101" s="22" t="n">
+        <v>160.831</v>
+      </c>
+      <c r="T101" s="22" t="n">
+        <v>104.991</v>
+      </c>
+      <c r="U101" s="22" t="n">
+        <v>18.878</v>
+      </c>
+      <c r="V101" s="22" t="n">
+        <v>100.61</v>
+      </c>
+      <c r="W101" s="22" t="n">
+        <v>43.082</v>
+      </c>
+      <c r="X101" s="22" t="n">
+        <v>214.249</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="9" t="inlineStr">
+        <is>
+          <t>순이익</t>
+        </is>
+      </c>
+      <c r="C102" s="12" t="n">
+        <v>179.211</v>
+      </c>
+      <c r="D102" s="12" t="n">
+        <v>-12.53</v>
+      </c>
+      <c r="E102" s="12" t="n">
+        <v>151.639</v>
+      </c>
+      <c r="F102" s="12" t="n">
+        <v>206.93</v>
+      </c>
+      <c r="G102" s="12" t="n">
+        <v>139.322</v>
+      </c>
+      <c r="H102" s="12" t="n">
+        <v>201.316</v>
+      </c>
+      <c r="I102" s="12" t="n">
+        <v>83.791</v>
+      </c>
+      <c r="J102" s="12" t="n">
+        <v>81.574</v>
+      </c>
+      <c r="K102" s="12" t="n">
+        <v>18.572</v>
+      </c>
+      <c r="L102" s="12" t="n">
+        <v>272.563</v>
+      </c>
+      <c r="M102" s="12" t="n">
+        <v>407.461</v>
+      </c>
+      <c r="N102" s="12" t="n">
+        <v>333.003</v>
+      </c>
+      <c r="T102" s="12" t="n">
+        <v>239.113</v>
+      </c>
+      <c r="U102" s="12" t="n">
+        <v>-67.438</v>
+      </c>
+      <c r="V102" s="12" t="n">
+        <v>151.639</v>
+      </c>
+      <c r="W102" s="12" t="n">
+        <v>83.791</v>
+      </c>
+      <c r="X102" s="12" t="n">
+        <v>407.461</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G103" s="17">
+        <f>IF(OR(G102="",C102=""),"",IF(C102&lt;=0,"",IFERROR(G102/C102-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H103" s="17">
+        <f>IF(OR(H102="",D102=""),"",IF(D102&lt;=0,"",IFERROR(H102/D102-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I103" s="17">
+        <f>IF(OR(I102="",E102=""),"",IF(E102&lt;=0,"",IFERROR(I102/E102-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J103" s="17">
+        <f>IF(OR(J102="",F102=""),"",IF(F102&lt;=0,"",IFERROR(J102/F102-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K103" s="17">
+        <f>IF(OR(K102="",G102=""),"",IF(G102&lt;=0,"",IFERROR(K102/G102-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L103" s="17">
+        <f>IF(OR(L102="",H102=""),"",IF(H102&lt;=0,"",IFERROR(L102/H102-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M103" s="17">
+        <f>IF(OR(M102="",I102=""),"",IF(I102&lt;=0,"",IFERROR(M102/I102-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N103" s="17">
+        <f>IF(OR(N102="",J102=""),"",IF(J102&lt;=0,"",IFERROR(N102/J102-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T103" s="17">
+        <f>IF(OR(T102="",S102=""),"",IF(S102&lt;=0,"",IFERROR(T102/S102-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U103" s="17">
+        <f>IF(OR(U102="",T102=""),"",IF(T102&lt;=0,"",IFERROR(U102/T102-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V103" s="17">
+        <f>IF(OR(V102="",U102=""),"",IF(U102&lt;=0,"",IFERROR(V102/U102-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W103" s="17">
+        <f>IF(OR(W102="",V102=""),"",IF(V102&lt;=0,"",IFERROR(W102/V102-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X103" s="17">
+        <f>IF(OR(X102="",W102=""),"",IF(W102&lt;=0,"",IFERROR(X102/W102-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="9" t="inlineStr">
+        <is>
           <t>비지배주주 순이익</t>
         </is>
       </c>
-      <c r="C98" s="12" t="n">
+      <c r="C104" s="12" t="n">
         <v>2.409</v>
       </c>
-      <c r="D98" s="12" t="n">
+      <c r="D104" s="12" t="n">
         <v>3.275</v>
       </c>
-      <c r="E98" s="12" t="n">
+      <c r="E104" s="12" t="n">
         <v>3.478</v>
       </c>
-      <c r="F98" s="12" t="n">
+      <c r="F104" s="12" t="n">
         <v>10.409</v>
       </c>
-      <c r="G98" s="12" t="n">
+      <c r="G104" s="12" t="n">
         <v>2.991</v>
       </c>
-      <c r="H98" s="12" t="n">
+      <c r="H104" s="12" t="n">
         <v>4.42</v>
       </c>
-      <c r="I98" s="12" t="n">
+      <c r="I104" s="12" t="n">
         <v>10.512</v>
       </c>
-      <c r="J98" s="12" t="n">
+      <c r="J104" s="12" t="n">
         <v>3.913</v>
       </c>
-      <c r="K98" s="12" t="n">
+      <c r="K104" s="12" t="n">
         <v>13.518</v>
       </c>
-      <c r="L98" s="12" t="n">
+      <c r="L104" s="12" t="n">
         <v>1.471</v>
       </c>
-      <c r="M98" s="12" t="n">
+      <c r="M104" s="12" t="n">
         <v>15.018</v>
       </c>
-      <c r="N98" s="12" t="n">
+      <c r="N104" s="12" t="n">
         <v>14.751</v>
       </c>
-      <c r="T98" s="12" t="n">
+      <c r="T104" s="12" t="n">
         <v>2.186</v>
       </c>
-      <c r="U98" s="12" t="n">
+      <c r="U104" s="12" t="n">
         <v>-1.317</v>
       </c>
-      <c r="V98" s="12" t="n">
+      <c r="V104" s="12" t="n">
         <v>3.478</v>
       </c>
-      <c r="W98" s="12" t="n">
+      <c r="W104" s="12" t="n">
         <v>10.512</v>
       </c>
-      <c r="X98" s="12" t="n">
+      <c r="X104" s="12" t="n">
         <v>15.018</v>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="9" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="9" t="inlineStr">
         <is>
           <t>지배주주 순이익</t>
         </is>
       </c>
-      <c r="C99" s="12" t="n">
+      <c r="C105" s="12" t="n">
         <v>176.803</v>
       </c>
-      <c r="D99" s="12" t="n">
+      <c r="D105" s="12" t="n">
         <v>-15.806</v>
       </c>
-      <c r="E99" s="12" t="n">
+      <c r="E105" s="12" t="n">
         <v>148.16</v>
       </c>
-      <c r="F99" s="12" t="n">
+      <c r="F105" s="12" t="n">
         <v>196.52</v>
       </c>
-      <c r="G99" s="12" t="n">
+      <c r="G105" s="12" t="n">
         <v>136.332</v>
       </c>
-      <c r="H99" s="12" t="n">
+      <c r="H105" s="12" t="n">
         <v>196.896</v>
       </c>
-      <c r="I99" s="12" t="n">
+      <c r="I105" s="12" t="n">
         <v>73.27800000000001</v>
       </c>
-      <c r="J99" s="12" t="n">
+      <c r="J105" s="12" t="n">
         <v>77.66</v>
       </c>
-      <c r="K99" s="12" t="n">
+      <c r="K105" s="12" t="n">
         <v>5.054</v>
       </c>
-      <c r="L99" s="12" t="n">
+      <c r="L105" s="12" t="n">
         <v>271.093</v>
       </c>
-      <c r="M99" s="12" t="n">
+      <c r="M105" s="12" t="n">
         <v>392.443</v>
       </c>
-      <c r="N99" s="12" t="n">
+      <c r="N105" s="12" t="n">
         <v>318.251</v>
       </c>
-      <c r="T99" s="12" t="n">
+      <c r="T105" s="12" t="n">
         <v>236.926</v>
       </c>
-      <c r="U99" s="12" t="n">
+      <c r="U105" s="12" t="n">
         <v>-66.121</v>
       </c>
-      <c r="V99" s="12" t="n">
+      <c r="V105" s="12" t="n">
         <v>148.16</v>
       </c>
-      <c r="W99" s="12" t="n">
+      <c r="W105" s="12" t="n">
         <v>73.27800000000001</v>
       </c>
-      <c r="X99" s="12" t="n">
+      <c r="X105" s="12" t="n">
         <v>392.443</v>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="18" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G106" s="17">
+        <f>IF(OR(G105="",C105=""),"",IF(C105&lt;=0,"",IFERROR(G105/C105-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H106" s="17">
+        <f>IF(OR(H105="",D105=""),"",IF(D105&lt;=0,"",IFERROR(H105/D105-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I106" s="17">
+        <f>IF(OR(I105="",E105=""),"",IF(E105&lt;=0,"",IFERROR(I105/E105-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J106" s="17">
+        <f>IF(OR(J105="",F105=""),"",IF(F105&lt;=0,"",IFERROR(J105/F105-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K106" s="17">
+        <f>IF(OR(K105="",G105=""),"",IF(G105&lt;=0,"",IFERROR(K105/G105-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L106" s="17">
+        <f>IF(OR(L105="",H105=""),"",IF(H105&lt;=0,"",IFERROR(L105/H105-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M106" s="17">
+        <f>IF(OR(M105="",I105=""),"",IF(I105&lt;=0,"",IFERROR(M105/I105-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N106" s="17">
+        <f>IF(OR(N105="",J105=""),"",IF(J105&lt;=0,"",IFERROR(N105/J105-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T106" s="17">
+        <f>IF(OR(T105="",S105=""),"",IF(S105&lt;=0,"",IFERROR(T105/S105-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U106" s="17">
+        <f>IF(OR(U105="",T105=""),"",IF(T105&lt;=0,"",IFERROR(U105/T105-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V106" s="17">
+        <f>IF(OR(V105="",U105=""),"",IF(U105&lt;=0,"",IFERROR(V105/U105-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W106" s="17">
+        <f>IF(OR(W105="",V105=""),"",IF(V105&lt;=0,"",IFERROR(W105/V105-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X106" s="17">
+        <f>IF(OR(X105="",W105=""),"",IF(W105&lt;=0,"",IFERROR(X105/W105-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="18" t="inlineStr">
         <is>
           <t>포괄손익 · 전 항목</t>
         </is>
       </c>
-      <c r="B101" s="44" t="inlineStr">
+      <c r="B108" s="44" t="inlineStr">
         <is>
           <t>분기 = 3개월 단독</t>
         </is>
       </c>
-      <c r="C101" s="18" t="n"/>
-      <c r="D101" s="18" t="n"/>
-      <c r="E101" s="18" t="n"/>
-      <c r="F101" s="18" t="n"/>
-      <c r="G101" s="18" t="n"/>
-      <c r="H101" s="18" t="n"/>
-      <c r="I101" s="18" t="n"/>
-      <c r="J101" s="18" t="n"/>
-      <c r="K101" s="18" t="n"/>
-      <c r="L101" s="18" t="n"/>
-      <c r="M101" s="18" t="n"/>
-      <c r="N101" s="18" t="n"/>
-      <c r="O101" s="18" t="n"/>
-      <c r="P101" s="18" t="n"/>
-      <c r="Q101" s="18" t="n"/>
-      <c r="R101" s="18" t="n"/>
-      <c r="S101" s="18" t="n"/>
-      <c r="T101" s="18" t="n"/>
-      <c r="U101" s="18" t="n"/>
-      <c r="V101" s="18" t="n"/>
-      <c r="W101" s="18" t="n"/>
-      <c r="X101" s="18" t="n"/>
-      <c r="Y101" s="18" t="n"/>
-      <c r="Z101" s="18" t="n"/>
-      <c r="AA101" s="18" t="n"/>
-      <c r="AB101" s="18" t="n"/>
-      <c r="AC101" s="18" t="n"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="5" t="inlineStr">
+      <c r="C108" s="18" t="n"/>
+      <c r="D108" s="18" t="n"/>
+      <c r="E108" s="18" t="n"/>
+      <c r="F108" s="18" t="n"/>
+      <c r="G108" s="18" t="n"/>
+      <c r="H108" s="18" t="n"/>
+      <c r="I108" s="18" t="n"/>
+      <c r="J108" s="18" t="n"/>
+      <c r="K108" s="18" t="n"/>
+      <c r="L108" s="18" t="n"/>
+      <c r="M108" s="18" t="n"/>
+      <c r="N108" s="18" t="n"/>
+      <c r="O108" s="18" t="n"/>
+      <c r="P108" s="18" t="n"/>
+      <c r="Q108" s="18" t="n"/>
+      <c r="R108" s="18" t="n"/>
+      <c r="S108" s="18" t="n"/>
+      <c r="T108" s="18" t="n"/>
+      <c r="U108" s="18" t="n"/>
+      <c r="V108" s="18" t="n"/>
+      <c r="W108" s="18" t="n"/>
+      <c r="X108" s="18" t="n"/>
+      <c r="Y108" s="18" t="n"/>
+      <c r="Z108" s="18" t="n"/>
+      <c r="AA108" s="18" t="n"/>
+      <c r="AB108" s="18" t="n"/>
+      <c r="AC108" s="18" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B102" s="5" t="inlineStr">
+      <c r="B109" s="5" t="inlineStr">
         <is>
           <t>참고</t>
         </is>
       </c>
-      <c r="C102" s="5" t="inlineStr">
+      <c r="C109" s="5" t="inlineStr">
         <is>
           <t>2024.2Q</t>
         </is>
       </c>
-      <c r="D102" s="5" t="inlineStr">
+      <c r="D109" s="5" t="inlineStr">
         <is>
           <t>2024.3Q</t>
         </is>
       </c>
-      <c r="E102" s="5" t="inlineStr">
+      <c r="E109" s="5" t="inlineStr">
         <is>
           <t>2024.4Q</t>
         </is>
       </c>
-      <c r="F102" s="5" t="inlineStr">
+      <c r="F109" s="5" t="inlineStr">
         <is>
           <t>2025.1Q</t>
         </is>
       </c>
-      <c r="G102" s="5" t="inlineStr">
+      <c r="G109" s="5" t="inlineStr">
         <is>
           <t>2025.2Q</t>
         </is>
       </c>
-      <c r="H102" s="5" t="inlineStr">
+      <c r="H109" s="5" t="inlineStr">
         <is>
           <t>2025.3Q</t>
         </is>
       </c>
-      <c r="I102" s="5" t="inlineStr">
+      <c r="I109" s="5" t="inlineStr">
         <is>
           <t>2025.4Q</t>
         </is>
       </c>
-      <c r="J102" s="5" t="inlineStr">
+      <c r="J109" s="5" t="inlineStr">
         <is>
           <t>2026.1Q</t>
         </is>
       </c>
-      <c r="K102" s="5" t="inlineStr">
+      <c r="K109" s="5" t="inlineStr">
         <is>
           <t>2026.2Q</t>
         </is>
       </c>
-      <c r="L102" s="5" t="inlineStr">
+      <c r="L109" s="5" t="inlineStr">
         <is>
           <t>2026.3Q</t>
         </is>
       </c>
-      <c r="M102" s="5" t="inlineStr">
+      <c r="M109" s="5" t="inlineStr">
         <is>
           <t>2026.4Q</t>
         </is>
       </c>
-      <c r="N102" s="5" t="inlineStr">
+      <c r="N109" s="5" t="inlineStr">
         <is>
           <t>2027.1Q</t>
         </is>
       </c>
-      <c r="O102" s="5" t="inlineStr">
+      <c r="O109" s="5" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="P102" s="5" t="inlineStr">
+      <c r="P109" s="5" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="Q102" s="5" t="inlineStr">
+      <c r="Q109" s="5" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="R102" s="5" t="inlineStr">
+      <c r="R109" s="5" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="S102" s="5" t="inlineStr">
+      <c r="S109" s="5" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="T102" s="5" t="inlineStr">
+      <c r="T109" s="5" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="U102" s="5" t="inlineStr">
+      <c r="U109" s="5" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="V102" s="5" t="inlineStr">
+      <c r="V109" s="5" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="W102" s="5" t="inlineStr">
+      <c r="W109" s="5" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="X102" s="5" t="inlineStr">
+      <c r="X109" s="5" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="Y102" s="5" t="inlineStr">
+      <c r="Y109" s="5" t="inlineStr">
         <is>
           <t>2027(MW)</t>
         </is>
       </c>
-      <c r="Z102" s="5" t="inlineStr">
+      <c r="Z109" s="5" t="inlineStr">
         <is>
           <t>2028(MW)</t>
         </is>
       </c>
-      <c r="AA102" s="5" t="inlineStr">
+      <c r="AA109" s="5" t="inlineStr">
         <is>
           <t>2029(MW)</t>
         </is>
       </c>
-      <c r="AB102" s="5" t="inlineStr">
+      <c r="AB109" s="5" t="inlineStr">
         <is>
           <t>2030(MW)</t>
         </is>
       </c>
-      <c r="AC102" s="5" t="inlineStr">
+      <c r="AC109" s="5" t="inlineStr">
         <is>
           <t>2031(MW)</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="9" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="9" t="inlineStr">
         <is>
           <t>순이익</t>
         </is>
       </c>
-      <c r="C103" s="12" t="n">
+      <c r="C110" s="12" t="n">
         <v>179.211</v>
       </c>
-      <c r="D103" s="12" t="n">
+      <c r="D110" s="12" t="n">
         <v>-12.53</v>
       </c>
-      <c r="E103" s="12" t="n">
+      <c r="E110" s="12" t="n">
         <v>151.639</v>
       </c>
-      <c r="F103" s="12" t="n">
+      <c r="F110" s="12" t="n">
         <v>206.93</v>
       </c>
-      <c r="G103" s="12" t="n">
+      <c r="G110" s="12" t="n">
         <v>139.322</v>
       </c>
-      <c r="H103" s="12" t="n">
+      <c r="H110" s="12" t="n">
         <v>201.316</v>
       </c>
-      <c r="I103" s="12" t="n">
+      <c r="I110" s="12" t="n">
         <v>83.791</v>
       </c>
-      <c r="J103" s="12" t="n">
+      <c r="J110" s="12" t="n">
         <v>81.574</v>
       </c>
-      <c r="K103" s="12" t="n">
+      <c r="K110" s="12" t="n">
         <v>18.572</v>
       </c>
-      <c r="L103" s="12" t="n">
+      <c r="L110" s="12" t="n">
         <v>272.563</v>
       </c>
-      <c r="M103" s="12" t="n">
+      <c r="M110" s="12" t="n">
         <v>407.461</v>
       </c>
-      <c r="N103" s="12" t="n">
+      <c r="N110" s="12" t="n">
         <v>333.003</v>
       </c>
-      <c r="T103" s="12" t="n">
+      <c r="T110" s="12" t="n">
         <v>239.113</v>
       </c>
-      <c r="U103" s="12" t="n">
+      <c r="U110" s="12" t="n">
         <v>-67.438</v>
       </c>
-      <c r="V103" s="12" t="n">
+      <c r="V110" s="12" t="n">
         <v>151.639</v>
       </c>
-      <c r="W103" s="12" t="n">
+      <c r="W110" s="12" t="n">
         <v>83.791</v>
       </c>
-      <c r="X103" s="12" t="n">
+      <c r="X110" s="12" t="n">
         <v>407.461</v>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="20" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="20" t="inlineStr">
         <is>
           <t>기타유가증권 평가차액</t>
         </is>
       </c>
-      <c r="C104" s="22" t="n">
+      <c r="C111" s="22" t="n">
         <v>-22.436</v>
       </c>
-      <c r="D104" s="22" t="n">
+      <c r="D111" s="22" t="n">
         <v>0.06</v>
       </c>
-      <c r="E104" s="22" t="n">
+      <c r="E111" s="22" t="n">
         <v>30.321</v>
       </c>
-      <c r="F104" s="22" t="n">
+      <c r="F111" s="22" t="n">
         <v>65.057</v>
       </c>
-      <c r="G104" s="22" t="n">
+      <c r="G111" s="22" t="n">
         <v>-420.405</v>
       </c>
-      <c r="H104" s="22" t="n">
+      <c r="H111" s="22" t="n">
         <v>306.737</v>
       </c>
-      <c r="I104" s="22" t="n">
+      <c r="I111" s="22" t="n">
         <v>-8.237</v>
       </c>
-      <c r="J104" s="22" t="n">
+      <c r="J111" s="22" t="n">
         <v>-4.871</v>
       </c>
-      <c r="K104" s="22" t="n">
+      <c r="K111" s="22" t="n">
         <v>31.359</v>
       </c>
-      <c r="L104" s="22" t="n">
+      <c r="L111" s="22" t="n">
         <v>21.829</v>
       </c>
-      <c r="M104" s="22" t="n">
+      <c r="M111" s="22" t="n">
         <v>-355.269</v>
       </c>
-      <c r="N104" s="22" t="n">
+      <c r="N111" s="22" t="n">
         <v>346.623</v>
       </c>
-      <c r="T104" s="22" t="n">
+      <c r="T111" s="22" t="n">
         <v>90.54900000000001</v>
       </c>
-      <c r="U104" s="22" t="n">
+      <c r="U111" s="22" t="n">
         <v>-7.835</v>
       </c>
-      <c r="V104" s="22" t="n">
+      <c r="V111" s="22" t="n">
         <v>30.321</v>
       </c>
-      <c r="W104" s="22" t="n">
+      <c r="W111" s="22" t="n">
         <v>-8.237</v>
       </c>
-      <c r="X104" s="22" t="n">
+      <c r="X111" s="22" t="n">
         <v>-355.269</v>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="20" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="20" t="inlineStr">
         <is>
           <t>기타포괄손익 합계</t>
         </is>
       </c>
-      <c r="C105" s="22" t="n">
+      <c r="C112" s="22" t="n">
         <v>-22.436</v>
       </c>
-      <c r="D105" s="22" t="n">
+      <c r="D112" s="22" t="n">
         <v>0.06</v>
       </c>
-      <c r="E105" s="22" t="n">
+      <c r="E112" s="22" t="n">
         <v>30.321</v>
       </c>
-      <c r="F105" s="22" t="n">
+      <c r="F112" s="22" t="n">
         <v>65.057</v>
       </c>
-      <c r="G105" s="22" t="n">
+      <c r="G112" s="22" t="n">
         <v>-420.405</v>
       </c>
-      <c r="H105" s="22" t="n">
+      <c r="H112" s="22" t="n">
         <v>306.737</v>
       </c>
-      <c r="I105" s="22" t="n">
+      <c r="I112" s="22" t="n">
         <v>-8.237</v>
       </c>
-      <c r="J105" s="22" t="n">
+      <c r="J112" s="22" t="n">
         <v>-4.871</v>
       </c>
-      <c r="K105" s="22" t="n">
+      <c r="K112" s="22" t="n">
         <v>31.359</v>
       </c>
-      <c r="L105" s="22" t="n">
+      <c r="L112" s="22" t="n">
         <v>21.829</v>
       </c>
-      <c r="M105" s="22" t="n">
+      <c r="M112" s="22" t="n">
         <v>-355.269</v>
       </c>
-      <c r="N105" s="22" t="n">
+      <c r="N112" s="22" t="n">
         <v>346.623</v>
       </c>
-      <c r="T105" s="22" t="n">
+      <c r="T112" s="22" t="n">
         <v>90.54900000000001</v>
       </c>
-      <c r="U105" s="22" t="n">
+      <c r="U112" s="22" t="n">
         <v>-7.835</v>
       </c>
-      <c r="V105" s="22" t="n">
+      <c r="V112" s="22" t="n">
         <v>30.321</v>
       </c>
-      <c r="W105" s="22" t="n">
+      <c r="W112" s="22" t="n">
         <v>-8.237</v>
       </c>
-      <c r="X105" s="22" t="n">
+      <c r="X112" s="22" t="n">
         <v>-355.269</v>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="9" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="9" t="inlineStr">
         <is>
           <t>포괄이익</t>
         </is>
       </c>
-      <c r="C106" s="12" t="n">
+      <c r="C113" s="12" t="n">
         <v>156.776</v>
       </c>
-      <c r="D106" s="12" t="n">
+      <c r="D113" s="12" t="n">
         <v>-12.47</v>
       </c>
-      <c r="E106" s="12" t="n">
+      <c r="E113" s="12" t="n">
         <v>181.96</v>
       </c>
-      <c r="F106" s="12" t="n">
+      <c r="F113" s="12" t="n">
         <v>271.988</v>
       </c>
-      <c r="G106" s="12" t="n">
+      <c r="G113" s="12" t="n">
         <v>-281.083</v>
       </c>
-      <c r="H106" s="12" t="n">
+      <c r="H113" s="12" t="n">
         <v>508.052</v>
       </c>
-      <c r="I106" s="12" t="n">
+      <c r="I113" s="12" t="n">
         <v>75.553</v>
       </c>
-      <c r="J106" s="12" t="n">
+      <c r="J113" s="12" t="n">
         <v>76.703</v>
       </c>
-      <c r="K106" s="12" t="n">
+      <c r="K113" s="12" t="n">
         <v>49.932</v>
       </c>
-      <c r="L106" s="12" t="n">
+      <c r="L113" s="12" t="n">
         <v>294.391</v>
       </c>
-      <c r="M106" s="12" t="n">
+      <c r="M113" s="12" t="n">
         <v>52.192</v>
       </c>
-      <c r="N106" s="12" t="n">
+      <c r="N113" s="12" t="n">
         <v>679.626</v>
       </c>
-      <c r="T106" s="12" t="n">
+      <c r="T113" s="12" t="n">
         <v>329.661</v>
       </c>
-      <c r="U106" s="12" t="n">
+      <c r="U113" s="12" t="n">
         <v>-75.273</v>
       </c>
-      <c r="V106" s="12" t="n">
+      <c r="V113" s="12" t="n">
         <v>181.96</v>
       </c>
-      <c r="W106" s="12" t="n">
+      <c r="W113" s="12" t="n">
         <v>75.553</v>
       </c>
-      <c r="X106" s="12" t="n">
+      <c r="X113" s="12" t="n">
         <v>52.192</v>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="9" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="9" t="inlineStr">
         <is>
           <t>지배주주 포괄이익</t>
         </is>
       </c>
-      <c r="C107" s="12" t="n">
+      <c r="C114" s="12" t="n">
         <v>154.367</v>
       </c>
-      <c r="D107" s="12" t="n">
+      <c r="D114" s="12" t="n">
         <v>-15.746</v>
       </c>
-      <c r="E107" s="12" t="n">
+      <c r="E114" s="12" t="n">
         <v>178.482</v>
       </c>
-      <c r="F107" s="12" t="n">
+      <c r="F114" s="12" t="n">
         <v>261.578</v>
       </c>
-      <c r="G107" s="12" t="n">
+      <c r="G114" s="12" t="n">
         <v>-284.074</v>
       </c>
-      <c r="H107" s="12" t="n">
+      <c r="H114" s="12" t="n">
         <v>503.632</v>
       </c>
-      <c r="I107" s="12" t="n">
+      <c r="I114" s="12" t="n">
         <v>65.042</v>
       </c>
-      <c r="J107" s="12" t="n">
+      <c r="J114" s="12" t="n">
         <v>72.789</v>
       </c>
-      <c r="K107" s="12" t="n">
+      <c r="K114" s="12" t="n">
         <v>36.414</v>
       </c>
-      <c r="L107" s="12" t="n">
+      <c r="L114" s="12" t="n">
         <v>292.921</v>
       </c>
-      <c r="M107" s="12" t="n">
+      <c r="M114" s="12" t="n">
         <v>37.173</v>
       </c>
-      <c r="N107" s="12" t="n">
+      <c r="N114" s="12" t="n">
         <v>664.874</v>
       </c>
-      <c r="T107" s="12" t="n">
+      <c r="T114" s="12" t="n">
         <v>327.475</v>
       </c>
-      <c r="U107" s="12" t="n">
+      <c r="U114" s="12" t="n">
         <v>-73.956</v>
       </c>
-      <c r="V107" s="12" t="n">
+      <c r="V114" s="12" t="n">
         <v>178.482</v>
       </c>
-      <c r="W107" s="12" t="n">
+      <c r="W114" s="12" t="n">
         <v>65.042</v>
       </c>
-      <c r="X107" s="12" t="n">
+      <c r="X114" s="12" t="n">
         <v>37.173</v>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="9" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="9" t="inlineStr">
         <is>
           <t>비지배주주 포괄이익</t>
         </is>
       </c>
-      <c r="C108" s="12" t="n">
+      <c r="C115" s="12" t="n">
         <v>2.409</v>
       </c>
-      <c r="D108" s="12" t="n">
+      <c r="D115" s="12" t="n">
         <v>3.275</v>
       </c>
-      <c r="E108" s="12" t="n">
+      <c r="E115" s="12" t="n">
         <v>3.478</v>
       </c>
-      <c r="F108" s="12" t="n">
+      <c r="F115" s="12" t="n">
         <v>10.409</v>
       </c>
-      <c r="G108" s="12" t="n">
+      <c r="G115" s="12" t="n">
         <v>2.991</v>
       </c>
-      <c r="H108" s="12" t="n">
+      <c r="H115" s="12" t="n">
         <v>4.42</v>
       </c>
-      <c r="I108" s="12" t="n">
+      <c r="I115" s="12" t="n">
         <v>10.512</v>
       </c>
-      <c r="J108" s="12" t="n">
+      <c r="J115" s="12" t="n">
         <v>3.913</v>
       </c>
-      <c r="K108" s="12" t="n">
+      <c r="K115" s="12" t="n">
         <v>13.518</v>
       </c>
-      <c r="L108" s="12" t="n">
+      <c r="L115" s="12" t="n">
         <v>1.471</v>
       </c>
-      <c r="M108" s="12" t="n">
+      <c r="M115" s="12" t="n">
         <v>15.018</v>
       </c>
-      <c r="N108" s="12" t="n">
+      <c r="N115" s="12" t="n">
         <v>14.751</v>
       </c>
-      <c r="T108" s="12" t="n">
+      <c r="T115" s="12" t="n">
         <v>2.186</v>
       </c>
-      <c r="U108" s="12" t="n">
+      <c r="U115" s="12" t="n">
         <v>-1.317</v>
       </c>
-      <c r="V108" s="12" t="n">
+      <c r="V115" s="12" t="n">
         <v>3.478</v>
       </c>
-      <c r="W108" s="12" t="n">
+      <c r="W115" s="12" t="n">
         <v>10.512</v>
       </c>
-      <c r="X108" s="12" t="n">
+      <c r="X115" s="12" t="n">
         <v>15.018</v>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="18" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="18" t="inlineStr">
         <is>
           <t>현금흐름표 · 전 항목</t>
         </is>
       </c>
-      <c r="B110" s="44" t="inlineStr">
+      <c r="B117" s="44" t="inlineStr">
         <is>
           <t>분기 = 결산기 첫날부터 누계(공시 그대로)</t>
         </is>
       </c>
-      <c r="C110" s="18" t="n"/>
-      <c r="D110" s="18" t="n"/>
-      <c r="E110" s="18" t="n"/>
-      <c r="F110" s="18" t="n"/>
-      <c r="G110" s="18" t="n"/>
-      <c r="H110" s="18" t="n"/>
-      <c r="I110" s="18" t="n"/>
-      <c r="J110" s="18" t="n"/>
-      <c r="K110" s="18" t="n"/>
-      <c r="L110" s="18" t="n"/>
-      <c r="M110" s="18" t="n"/>
-      <c r="N110" s="18" t="n"/>
-      <c r="O110" s="18" t="n"/>
-      <c r="P110" s="18" t="n"/>
-      <c r="Q110" s="18" t="n"/>
-      <c r="R110" s="18" t="n"/>
-      <c r="S110" s="18" t="n"/>
-      <c r="T110" s="18" t="n"/>
-      <c r="U110" s="18" t="n"/>
-      <c r="V110" s="18" t="n"/>
-      <c r="W110" s="18" t="n"/>
-      <c r="X110" s="18" t="n"/>
-      <c r="Y110" s="18" t="n"/>
-      <c r="Z110" s="18" t="n"/>
-      <c r="AA110" s="18" t="n"/>
-      <c r="AB110" s="18" t="n"/>
-      <c r="AC110" s="18" t="n"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="5" t="inlineStr">
+      <c r="C117" s="18" t="n"/>
+      <c r="D117" s="18" t="n"/>
+      <c r="E117" s="18" t="n"/>
+      <c r="F117" s="18" t="n"/>
+      <c r="G117" s="18" t="n"/>
+      <c r="H117" s="18" t="n"/>
+      <c r="I117" s="18" t="n"/>
+      <c r="J117" s="18" t="n"/>
+      <c r="K117" s="18" t="n"/>
+      <c r="L117" s="18" t="n"/>
+      <c r="M117" s="18" t="n"/>
+      <c r="N117" s="18" t="n"/>
+      <c r="O117" s="18" t="n"/>
+      <c r="P117" s="18" t="n"/>
+      <c r="Q117" s="18" t="n"/>
+      <c r="R117" s="18" t="n"/>
+      <c r="S117" s="18" t="n"/>
+      <c r="T117" s="18" t="n"/>
+      <c r="U117" s="18" t="n"/>
+      <c r="V117" s="18" t="n"/>
+      <c r="W117" s="18" t="n"/>
+      <c r="X117" s="18" t="n"/>
+      <c r="Y117" s="18" t="n"/>
+      <c r="Z117" s="18" t="n"/>
+      <c r="AA117" s="18" t="n"/>
+      <c r="AB117" s="18" t="n"/>
+      <c r="AC117" s="18" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B111" s="5" t="inlineStr">
+      <c r="B118" s="5" t="inlineStr">
         <is>
           <t>참고</t>
         </is>
       </c>
-      <c r="C111" s="5" t="inlineStr">
+      <c r="C118" s="5" t="inlineStr">
         <is>
           <t>2024.2Q</t>
         </is>
       </c>
-      <c r="D111" s="5" t="inlineStr">
+      <c r="D118" s="5" t="inlineStr">
         <is>
           <t>2024.3Q</t>
         </is>
       </c>
-      <c r="E111" s="5" t="inlineStr">
+      <c r="E118" s="5" t="inlineStr">
         <is>
           <t>2024.4Q</t>
         </is>
       </c>
-      <c r="F111" s="5" t="inlineStr">
+      <c r="F118" s="5" t="inlineStr">
         <is>
           <t>2025.1Q</t>
         </is>
       </c>
-      <c r="G111" s="5" t="inlineStr">
+      <c r="G118" s="5" t="inlineStr">
         <is>
           <t>2025.2Q</t>
         </is>
       </c>
-      <c r="H111" s="5" t="inlineStr">
+      <c r="H118" s="5" t="inlineStr">
         <is>
           <t>2025.3Q</t>
         </is>
       </c>
-      <c r="I111" s="5" t="inlineStr">
+      <c r="I118" s="5" t="inlineStr">
         <is>
           <t>2025.4Q</t>
         </is>
       </c>
-      <c r="J111" s="5" t="inlineStr">
+      <c r="J118" s="5" t="inlineStr">
         <is>
           <t>2026.1Q</t>
         </is>
       </c>
-      <c r="K111" s="5" t="inlineStr">
+      <c r="K118" s="5" t="inlineStr">
         <is>
           <t>2026.2Q</t>
         </is>
       </c>
-      <c r="L111" s="5" t="inlineStr">
+      <c r="L118" s="5" t="inlineStr">
         <is>
           <t>2026.3Q</t>
         </is>
       </c>
-      <c r="M111" s="5" t="inlineStr">
+      <c r="M118" s="5" t="inlineStr">
         <is>
           <t>2026.4Q</t>
         </is>
       </c>
-      <c r="N111" s="5" t="inlineStr">
+      <c r="N118" s="5" t="inlineStr">
         <is>
           <t>2027.1Q</t>
         </is>
       </c>
-      <c r="O111" s="5" t="inlineStr">
+      <c r="O118" s="5" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="P111" s="5" t="inlineStr">
+      <c r="P118" s="5" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="Q111" s="5" t="inlineStr">
+      <c r="Q118" s="5" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="R111" s="5" t="inlineStr">
+      <c r="R118" s="5" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="S111" s="5" t="inlineStr">
+      <c r="S118" s="5" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="T111" s="5" t="inlineStr">
+      <c r="T118" s="5" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="U111" s="5" t="inlineStr">
+      <c r="U118" s="5" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="V111" s="5" t="inlineStr">
+      <c r="V118" s="5" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="W111" s="5" t="inlineStr">
+      <c r="W118" s="5" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="X111" s="5" t="inlineStr">
+      <c r="X118" s="5" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="Y111" s="5" t="inlineStr">
+      <c r="Y118" s="5" t="inlineStr">
         <is>
           <t>2027(MW)</t>
         </is>
       </c>
-      <c r="Z111" s="5" t="inlineStr">
+      <c r="Z118" s="5" t="inlineStr">
         <is>
           <t>2028(MW)</t>
         </is>
       </c>
-      <c r="AA111" s="5" t="inlineStr">
+      <c r="AA118" s="5" t="inlineStr">
         <is>
           <t>2029(MW)</t>
         </is>
       </c>
-      <c r="AB111" s="5" t="inlineStr">
+      <c r="AB118" s="5" t="inlineStr">
         <is>
           <t>2030(MW)</t>
         </is>
       </c>
-      <c r="AC111" s="5" t="inlineStr">
+      <c r="AC118" s="5" t="inlineStr">
         <is>
           <t>2031(MW)</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="9" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="9" t="inlineStr">
         <is>
           <t>법인세차감전 순이익</t>
         </is>
       </c>
-      <c r="C112" s="12" t="n">
+      <c r="C119" s="12" t="n">
         <v>412.344</v>
       </c>
-      <c r="E112" s="12" t="n">
+      <c r="E119" s="12" t="n">
         <v>656.8579999999999</v>
       </c>
-      <c r="G112" s="12" t="n">
+      <c r="G119" s="12" t="n">
         <v>503.816</v>
       </c>
-      <c r="I112" s="12" t="n">
+      <c r="I119" s="12" t="n">
         <v>924.225</v>
       </c>
-      <c r="K112" s="12" t="n">
+      <c r="K119" s="12" t="n">
         <v>133.773</v>
       </c>
-      <c r="M112" s="12" t="n">
+      <c r="M119" s="12" t="n">
         <v>1156.71</v>
       </c>
-      <c r="O112" s="12" t="n">
+      <c r="O119" s="12" t="n">
         <v>664.744</v>
       </c>
-      <c r="P112" s="12" t="n">
+      <c r="P119" s="12" t="n">
         <v>742.524</v>
       </c>
-      <c r="Q112" s="12" t="n">
+      <c r="Q119" s="12" t="n">
         <v>724.336</v>
       </c>
-      <c r="R112" s="12" t="n">
+      <c r="R119" s="12" t="n">
         <v>1132.109</v>
       </c>
-      <c r="S112" s="12" t="n">
+      <c r="S119" s="12" t="n">
         <v>1524.051</v>
       </c>
-      <c r="T112" s="12" t="n">
+      <c r="T119" s="12" t="n">
         <v>1337.287</v>
       </c>
-      <c r="U112" s="12" t="n">
+      <c r="U119" s="12" t="n">
         <v>932.689</v>
       </c>
-      <c r="V112" s="12" t="n">
+      <c r="V119" s="12" t="n">
         <v>656.8579999999999</v>
       </c>
-      <c r="W112" s="12" t="n">
+      <c r="W119" s="12" t="n">
         <v>924.225</v>
       </c>
-      <c r="X112" s="12" t="n">
+      <c r="X119" s="12" t="n">
         <v>1156.71</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="20" t="inlineStr">
-        <is>
-          <t>감가상각비</t>
-        </is>
-      </c>
-      <c r="C113" s="22" t="n">
-        <v>8.012</v>
-      </c>
-      <c r="E113" s="22" t="n">
-        <v>18.428</v>
-      </c>
-      <c r="G113" s="22" t="n">
-        <v>10.703</v>
-      </c>
-      <c r="I113" s="22" t="n">
-        <v>21.434</v>
-      </c>
-      <c r="K113" s="22" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="M113" s="22" t="n">
-        <v>13.793</v>
-      </c>
-      <c r="O113" s="22" t="n">
-        <v>25.618</v>
-      </c>
-      <c r="P113" s="22" t="n">
-        <v>20.805</v>
-      </c>
-      <c r="Q113" s="22" t="n">
-        <v>16.172</v>
-      </c>
-      <c r="R113" s="22" t="n">
-        <v>13.721</v>
-      </c>
-      <c r="S113" s="22" t="n">
-        <v>19.334</v>
-      </c>
-      <c r="T113" s="22" t="n">
-        <v>20.131</v>
-      </c>
-      <c r="U113" s="22" t="n">
-        <v>19.326</v>
-      </c>
-      <c r="V113" s="22" t="n">
-        <v>18.428</v>
-      </c>
-      <c r="W113" s="22" t="n">
-        <v>21.434</v>
-      </c>
-      <c r="X113" s="22" t="n">
-        <v>13.793</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="20" t="inlineStr">
-        <is>
-          <t>손상차손</t>
-        </is>
-      </c>
-      <c r="P114" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q114" s="22" t="n">
-        <v>26.655</v>
-      </c>
-      <c r="R114" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="20" t="inlineStr">
-        <is>
-          <t>대손충당금 증감</t>
-        </is>
-      </c>
-      <c r="C115" s="22" t="n">
-        <v>17.401</v>
-      </c>
-      <c r="E115" s="22" t="n">
-        <v>19.323</v>
-      </c>
-      <c r="G115" s="22" t="n">
-        <v>-9.336</v>
-      </c>
-      <c r="I115" s="22" t="n">
-        <v>-2.051</v>
-      </c>
-      <c r="K115" s="22" t="n">
-        <v>-0.634</v>
-      </c>
-      <c r="M115" s="22" t="n">
-        <v>11.203</v>
-      </c>
-      <c r="O115" s="22" t="n">
-        <v>-3.28</v>
-      </c>
-      <c r="P115" s="22" t="n">
-        <v>114.452</v>
-      </c>
-      <c r="Q115" s="22" t="n">
-        <v>5.021</v>
-      </c>
-      <c r="R115" s="22" t="n">
-        <v>-2.623</v>
-      </c>
-      <c r="S115" s="22" t="n">
-        <v>6.022</v>
-      </c>
-      <c r="T115" s="22" t="n">
-        <v>10.328</v>
-      </c>
-      <c r="U115" s="22" t="n">
-        <v>11.686</v>
-      </c>
-      <c r="V115" s="22" t="n">
-        <v>19.323</v>
-      </c>
-      <c r="W115" s="22" t="n">
-        <v>-2.051</v>
-      </c>
-      <c r="X115" s="22" t="n">
-        <v>11.203</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="20" t="inlineStr">
-        <is>
-          <t>상여충당금 증감</t>
-        </is>
-      </c>
-      <c r="C116" s="22" t="n">
-        <v>9.02</v>
-      </c>
-      <c r="E116" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G116" s="22" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="I116" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K116" s="22" t="n">
-        <v>15.25</v>
-      </c>
-      <c r="S116" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T116" s="22" t="n">
-        <v>7.95</v>
-      </c>
-      <c r="U116" s="22" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="V116" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W116" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="20" t="inlineStr">
-        <is>
-          <t>반품조정 충당금 증감</t>
-        </is>
-      </c>
-      <c r="O117" s="22" t="n">
-        <v>1.566</v>
-      </c>
-      <c r="P117" s="22" t="n">
-        <v>-1.566</v>
-      </c>
-      <c r="Q117" s="22" t="n">
-        <v>1.488</v>
-      </c>
-      <c r="R117" s="22" t="n">
-        <v>-1.488</v>
-      </c>
-      <c r="S117" s="22" t="n">
-        <v>1.141</v>
-      </c>
-      <c r="T117" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="20" t="inlineStr">
-        <is>
-          <t>이자·배당금 수익</t>
-        </is>
-      </c>
-      <c r="C118" s="22" t="n">
-        <v>-47.968</v>
-      </c>
-      <c r="E118" s="22" t="n">
-        <v>-64.014</v>
-      </c>
-      <c r="G118" s="22" t="n">
-        <v>-84.09099999999999</v>
-      </c>
-      <c r="I118" s="22" t="n">
-        <v>-133.625</v>
-      </c>
-      <c r="K118" s="22" t="n">
-        <v>-35.938</v>
-      </c>
-      <c r="M118" s="22" t="n">
-        <v>-147.103</v>
-      </c>
-      <c r="O118" s="22" t="n">
-        <v>-164.141</v>
-      </c>
-      <c r="P118" s="22" t="n">
-        <v>-178.961</v>
-      </c>
-      <c r="Q118" s="22" t="n">
-        <v>-182.623</v>
-      </c>
-      <c r="R118" s="22" t="n">
-        <v>-85.39400000000001</v>
-      </c>
-      <c r="S118" s="22" t="n">
-        <v>-85.961</v>
-      </c>
-      <c r="T118" s="22" t="n">
-        <v>-50.337</v>
-      </c>
-      <c r="U118" s="22" t="n">
-        <v>-3.995</v>
-      </c>
-      <c r="V118" s="22" t="n">
-        <v>-64.014</v>
-      </c>
-      <c r="W118" s="22" t="n">
-        <v>-133.625</v>
-      </c>
-      <c r="X118" s="22" t="n">
-        <v>-147.103</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="20" t="inlineStr">
-        <is>
-          <t>외환차손익</t>
-        </is>
-      </c>
-      <c r="C119" s="22" t="n">
-        <v>-12.511</v>
-      </c>
-      <c r="E119" s="22" t="n">
-        <v>-13.345</v>
-      </c>
-      <c r="G119" s="22" t="n">
-        <v>-3.371</v>
-      </c>
-      <c r="I119" s="22" t="n">
-        <v>-8.218</v>
-      </c>
-      <c r="K119" s="22" t="n">
-        <v>-2.125</v>
-      </c>
-      <c r="M119" s="22" t="n">
-        <v>-17.813</v>
-      </c>
-      <c r="O119" s="22" t="n">
-        <v>29.863</v>
-      </c>
-      <c r="P119" s="22" t="n">
-        <v>18.766</v>
-      </c>
-      <c r="Q119" s="22" t="n">
-        <v>4.086</v>
-      </c>
-      <c r="R119" s="22" t="n">
-        <v>6.511</v>
-      </c>
-      <c r="S119" s="22" t="n">
-        <v>1.511</v>
-      </c>
-      <c r="T119" s="22" t="n">
-        <v>-21.446</v>
-      </c>
-      <c r="U119" s="22" t="n">
-        <v>-19.185</v>
-      </c>
-      <c r="V119" s="22" t="n">
-        <v>-13.345</v>
-      </c>
-      <c r="W119" s="22" t="n">
-        <v>-8.218</v>
-      </c>
-      <c r="X119" s="22" t="n">
-        <v>-17.813</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 매각손익</t>
+          <t>감가상각비</t>
         </is>
       </c>
       <c r="C120" s="22" t="n">
-        <v>-76.38500000000001</v>
+        <v>8.012</v>
       </c>
       <c r="E120" s="22" t="n">
-        <v>-85.11799999999999</v>
+        <v>18.428</v>
       </c>
       <c r="G120" s="22" t="n">
-        <v>-164.66</v>
+        <v>10.703</v>
       </c>
       <c r="I120" s="22" t="n">
-        <v>-339.511</v>
+        <v>21.434</v>
       </c>
       <c r="K120" s="22" t="n">
-        <v>-224.486</v>
+        <v>6.55</v>
       </c>
       <c r="M120" s="22" t="n">
-        <v>-752.175</v>
+        <v>13.793</v>
       </c>
       <c r="O120" s="22" t="n">
-        <v>-93.337</v>
+        <v>25.618</v>
       </c>
       <c r="P120" s="22" t="n">
-        <v>-3.42</v>
+        <v>20.805</v>
       </c>
       <c r="Q120" s="22" t="n">
-        <v>170.356</v>
+        <v>16.172</v>
       </c>
       <c r="R120" s="22" t="n">
-        <v>112.124</v>
+        <v>13.721</v>
       </c>
       <c r="S120" s="22" t="n">
-        <v>0</v>
+        <v>19.334</v>
       </c>
       <c r="T120" s="22" t="n">
-        <v>-1.367</v>
+        <v>20.131</v>
       </c>
       <c r="U120" s="22" t="n">
-        <v>-166.298</v>
+        <v>19.326</v>
       </c>
       <c r="V120" s="22" t="n">
-        <v>-85.11799999999999</v>
+        <v>18.428</v>
       </c>
       <c r="W120" s="22" t="n">
-        <v>-339.511</v>
+        <v>21.434</v>
       </c>
       <c r="X120" s="22" t="n">
-        <v>-752.175</v>
+        <v>13.793</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 평가손익</t>
-        </is>
-      </c>
-      <c r="O121" s="22" t="n">
-        <v>0.391</v>
+          <t>손상차손</t>
+        </is>
       </c>
       <c r="P121" s="22" t="n">
-        <v>17.701</v>
+        <v>0</v>
       </c>
       <c r="Q121" s="22" t="n">
+        <v>26.655</v>
+      </c>
+      <c r="R121" s="22" t="n">
         <v>0</v>
-      </c>
-      <c r="R121" s="22" t="n">
-        <v>0.152</v>
-      </c>
-      <c r="S121" s="22" t="n">
-        <v>15.705</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="20" t="inlineStr">
         <is>
-          <t>Loss Gain On Investments In Partnership Ope CF</t>
-        </is>
+          <t>대손충당금 증감</t>
+        </is>
+      </c>
+      <c r="C122" s="22" t="n">
+        <v>17.401</v>
+      </c>
+      <c r="E122" s="22" t="n">
+        <v>19.323</v>
+      </c>
+      <c r="G122" s="22" t="n">
+        <v>-9.336</v>
+      </c>
+      <c r="I122" s="22" t="n">
+        <v>-2.051</v>
+      </c>
+      <c r="K122" s="22" t="n">
+        <v>-0.634</v>
+      </c>
+      <c r="M122" s="22" t="n">
+        <v>11.203</v>
       </c>
       <c r="O122" s="22" t="n">
-        <v>-55.475</v>
+        <v>-3.28</v>
       </c>
       <c r="P122" s="22" t="n">
-        <v>-83.093</v>
+        <v>114.452</v>
       </c>
       <c r="Q122" s="22" t="n">
-        <v>-1.777</v>
+        <v>5.021</v>
+      </c>
+      <c r="R122" s="22" t="n">
+        <v>-2.623</v>
+      </c>
+      <c r="S122" s="22" t="n">
+        <v>6.022</v>
+      </c>
+      <c r="T122" s="22" t="n">
+        <v>10.328</v>
+      </c>
+      <c r="U122" s="22" t="n">
+        <v>11.686</v>
+      </c>
+      <c r="V122" s="22" t="n">
+        <v>19.323</v>
+      </c>
+      <c r="W122" s="22" t="n">
+        <v>-2.051</v>
+      </c>
+      <c r="X122" s="22" t="n">
+        <v>11.203</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="20" t="inlineStr">
         <is>
-          <t>출자금 운용손익</t>
+          <t>상여충당금 증감</t>
         </is>
       </c>
       <c r="C123" s="22" t="n">
-        <v>-2.268</v>
+        <v>9.02</v>
       </c>
       <c r="E123" s="22" t="n">
-        <v>-3.689</v>
+        <v>0</v>
       </c>
       <c r="G123" s="22" t="n">
-        <v>-23.78</v>
+        <v>16.5</v>
       </c>
       <c r="I123" s="22" t="n">
-        <v>-26.104</v>
+        <v>0</v>
       </c>
       <c r="K123" s="22" t="n">
-        <v>-1.381</v>
-      </c>
-      <c r="M123" s="22" t="n">
-        <v>-2.613</v>
-      </c>
-      <c r="Q123" s="22" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="S123" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="R123" s="22" t="n">
-        <v>-43.192</v>
-      </c>
-      <c r="S123" s="22" t="n">
-        <v>-10.842</v>
-      </c>
       <c r="T123" s="22" t="n">
-        <v>-19.48</v>
+        <v>7.95</v>
       </c>
       <c r="U123" s="22" t="n">
-        <v>-40.138</v>
+        <v>-0.04</v>
       </c>
       <c r="V123" s="22" t="n">
-        <v>-3.689</v>
+        <v>0</v>
       </c>
       <c r="W123" s="22" t="n">
-        <v>-26.104</v>
-      </c>
-      <c r="X123" s="22" t="n">
-        <v>-2.613</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="20" t="inlineStr">
         <is>
-          <t>지분법손익</t>
+          <t>반품조정 충당금 증감</t>
         </is>
       </c>
       <c r="O124" s="22" t="n">
-        <v>-5.467</v>
+        <v>1.566</v>
       </c>
       <c r="P124" s="22" t="n">
-        <v>-10.855</v>
+        <v>-1.566</v>
       </c>
       <c r="Q124" s="22" t="n">
-        <v>-1.464</v>
+        <v>1.488</v>
       </c>
       <c r="R124" s="22" t="n">
-        <v>1.039</v>
+        <v>-1.488</v>
       </c>
       <c r="S124" s="22" t="n">
+        <v>1.141</v>
+      </c>
+      <c r="T124" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="20" t="inlineStr">
         <is>
-          <t>매출채권 증감</t>
+          <t>이자·배당금 수익</t>
         </is>
       </c>
       <c r="C125" s="22" t="n">
-        <v>59.075</v>
+        <v>-47.968</v>
       </c>
       <c r="E125" s="22" t="n">
-        <v>-325.805</v>
+        <v>-64.014</v>
       </c>
       <c r="G125" s="22" t="n">
-        <v>151.89</v>
+        <v>-84.09099999999999</v>
       </c>
       <c r="I125" s="22" t="n">
-        <v>-52.498</v>
+        <v>-133.625</v>
       </c>
       <c r="K125" s="22" t="n">
-        <v>337.369</v>
+        <v>-35.938</v>
       </c>
       <c r="M125" s="22" t="n">
-        <v>150.059</v>
+        <v>-147.103</v>
       </c>
       <c r="O125" s="22" t="n">
-        <v>-260.236</v>
+        <v>-164.141</v>
       </c>
       <c r="P125" s="22" t="n">
-        <v>322.295</v>
+        <v>-178.961</v>
       </c>
       <c r="Q125" s="22" t="n">
-        <v>42.955</v>
+        <v>-182.623</v>
       </c>
       <c r="R125" s="22" t="n">
-        <v>-586.182</v>
+        <v>-85.39400000000001</v>
       </c>
       <c r="S125" s="22" t="n">
-        <v>227.97</v>
+        <v>-85.961</v>
       </c>
       <c r="T125" s="22" t="n">
-        <v>59.055</v>
+        <v>-50.337</v>
       </c>
       <c r="U125" s="22" t="n">
-        <v>-495.64</v>
+        <v>-3.995</v>
       </c>
       <c r="V125" s="22" t="n">
-        <v>-325.805</v>
+        <v>-64.014</v>
       </c>
       <c r="W125" s="22" t="n">
-        <v>-52.498</v>
+        <v>-133.625</v>
       </c>
       <c r="X125" s="22" t="n">
-        <v>150.059</v>
+        <v>-147.103</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="20" t="inlineStr">
         <is>
-          <t>선급금 증감</t>
+          <t>외환차손익</t>
         </is>
       </c>
       <c r="C126" s="22" t="n">
-        <v>-2.228</v>
+        <v>-12.511</v>
+      </c>
+      <c r="E126" s="22" t="n">
+        <v>-13.345</v>
       </c>
       <c r="G126" s="22" t="n">
-        <v>-225.664</v>
+        <v>-3.371</v>
       </c>
       <c r="I126" s="22" t="n">
-        <v>19.341</v>
+        <v>-8.218</v>
       </c>
       <c r="K126" s="22" t="n">
-        <v>-114.212</v>
+        <v>-2.125</v>
       </c>
       <c r="M126" s="22" t="n">
-        <v>-104.377</v>
+        <v>-17.813</v>
+      </c>
+      <c r="O126" s="22" t="n">
+        <v>29.863</v>
+      </c>
+      <c r="P126" s="22" t="n">
+        <v>18.766</v>
+      </c>
+      <c r="Q126" s="22" t="n">
+        <v>4.086</v>
+      </c>
+      <c r="R126" s="22" t="n">
+        <v>6.511</v>
+      </c>
+      <c r="S126" s="22" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="T126" s="22" t="n">
+        <v>-21.446</v>
+      </c>
+      <c r="U126" s="22" t="n">
+        <v>-19.185</v>
+      </c>
+      <c r="V126" s="22" t="n">
+        <v>-13.345</v>
       </c>
       <c r="W126" s="22" t="n">
-        <v>19.341</v>
+        <v>-8.218</v>
       </c>
       <c r="X126" s="22" t="n">
-        <v>-104.377</v>
+        <v>-17.813</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="20" t="inlineStr">
         <is>
-          <t>Decrease Increase In Advance Expense Payments Other Ope CF</t>
+          <t>투자유가증권 매각손익</t>
         </is>
       </c>
       <c r="C127" s="22" t="n">
-        <v>84.432</v>
+        <v>-76.38500000000001</v>
       </c>
       <c r="E127" s="22" t="n">
-        <v>100.312</v>
+        <v>-85.11799999999999</v>
       </c>
       <c r="G127" s="22" t="n">
-        <v>28.585</v>
+        <v>-164.66</v>
       </c>
       <c r="I127" s="22" t="n">
-        <v>-6.616</v>
+        <v>-339.511</v>
       </c>
       <c r="K127" s="22" t="n">
-        <v>20.485</v>
+        <v>-224.486</v>
       </c>
       <c r="M127" s="22" t="n">
-        <v>23.477</v>
+        <v>-752.175</v>
       </c>
       <c r="O127" s="22" t="n">
-        <v>-161.692</v>
+        <v>-93.337</v>
       </c>
       <c r="P127" s="22" t="n">
-        <v>46.833</v>
+        <v>-3.42</v>
       </c>
       <c r="Q127" s="22" t="n">
-        <v>121.746</v>
+        <v>170.356</v>
       </c>
       <c r="R127" s="22" t="n">
-        <v>-15.432</v>
+        <v>112.124</v>
       </c>
       <c r="S127" s="22" t="n">
-        <v>-228.306</v>
+        <v>0</v>
       </c>
       <c r="T127" s="22" t="n">
-        <v>-100.362</v>
+        <v>-1.367</v>
       </c>
       <c r="U127" s="22" t="n">
-        <v>51.069</v>
+        <v>-166.298</v>
       </c>
       <c r="V127" s="22" t="n">
-        <v>100.312</v>
+        <v>-85.11799999999999</v>
       </c>
       <c r="W127" s="22" t="n">
-        <v>-6.616</v>
+        <v>-339.511</v>
       </c>
       <c r="X127" s="22" t="n">
-        <v>23.477</v>
+        <v>-752.175</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="20" t="inlineStr">
         <is>
-          <t>파산갱생채권 증감</t>
+          <t>투자유가증권 평가손익</t>
         </is>
       </c>
       <c r="O128" s="22" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="P128" s="22" t="n">
+        <v>17.701</v>
+      </c>
+      <c r="Q128" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="P128" s="22" t="n">
-        <v>-115.164</v>
-      </c>
-      <c r="Q128" s="22" t="n">
-        <v>-5.149</v>
-      </c>
       <c r="R128" s="22" t="n">
-        <v>2.341</v>
+        <v>0.152</v>
       </c>
       <c r="S128" s="22" t="n">
-        <v>-2.037</v>
-      </c>
-      <c r="T128" s="22" t="n">
-        <v>-12.661</v>
+        <v>15.705</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="20" t="inlineStr">
         <is>
-          <t>매입채무 증감</t>
-        </is>
-      </c>
-      <c r="C129" s="22" t="n">
-        <v>-12.77</v>
-      </c>
-      <c r="E129" s="22" t="n">
-        <v>-7.945</v>
-      </c>
-      <c r="G129" s="22" t="n">
-        <v>-7.778</v>
-      </c>
-      <c r="I129" s="22" t="n">
-        <v>-8.042999999999999</v>
-      </c>
-      <c r="K129" s="22" t="n">
-        <v>4.715</v>
-      </c>
-      <c r="M129" s="22" t="n">
-        <v>5.373</v>
+          <t>투자사업조합 운용 손익(△는 이익)</t>
+        </is>
       </c>
       <c r="O129" s="22" t="n">
-        <v>-43.891</v>
+        <v>-55.475</v>
       </c>
       <c r="P129" s="22" t="n">
-        <v>5.024</v>
+        <v>-83.093</v>
       </c>
       <c r="Q129" s="22" t="n">
-        <v>4.144</v>
-      </c>
-      <c r="R129" s="22" t="n">
-        <v>5.454</v>
-      </c>
-      <c r="S129" s="22" t="n">
-        <v>0.5629999999999999</v>
-      </c>
-      <c r="T129" s="22" t="n">
-        <v>-10.598</v>
-      </c>
-      <c r="U129" s="22" t="n">
-        <v>6.517</v>
-      </c>
-      <c r="V129" s="22" t="n">
-        <v>-7.945</v>
-      </c>
-      <c r="W129" s="22" t="n">
-        <v>-8.042999999999999</v>
-      </c>
-      <c r="X129" s="22" t="n">
-        <v>5.373</v>
+        <v>-1.777</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="20" t="inlineStr">
         <is>
-          <t>Increase Decrease In Accounts Payable Ope CF</t>
+          <t>출자금 운용손익</t>
         </is>
       </c>
       <c r="C130" s="22" t="n">
-        <v>-78.399</v>
+        <v>-2.268</v>
       </c>
       <c r="E130" s="22" t="n">
-        <v>162.167</v>
+        <v>-3.689</v>
       </c>
       <c r="G130" s="22" t="n">
-        <v>-399.452</v>
+        <v>-23.78</v>
       </c>
       <c r="I130" s="22" t="n">
-        <v>-277.226</v>
+        <v>-26.104</v>
       </c>
       <c r="K130" s="22" t="n">
-        <v>-117.036</v>
+        <v>-1.381</v>
       </c>
       <c r="M130" s="22" t="n">
-        <v>-86.407</v>
-      </c>
-      <c r="O130" s="22" t="n">
-        <v>-1.955</v>
-      </c>
-      <c r="P130" s="22" t="n">
-        <v>155.865</v>
+        <v>-2.613</v>
       </c>
       <c r="Q130" s="22" t="n">
-        <v>70.248</v>
+        <v>0</v>
       </c>
       <c r="R130" s="22" t="n">
-        <v>-81.962</v>
+        <v>-43.192</v>
       </c>
       <c r="S130" s="22" t="n">
-        <v>184.89</v>
+        <v>-10.842</v>
       </c>
       <c r="T130" s="22" t="n">
-        <v>-182.405</v>
+        <v>-19.48</v>
       </c>
       <c r="U130" s="22" t="n">
-        <v>113.511</v>
+        <v>-40.138</v>
       </c>
       <c r="V130" s="22" t="n">
-        <v>162.167</v>
+        <v>-3.689</v>
       </c>
       <c r="W130" s="22" t="n">
-        <v>-277.226</v>
+        <v>-26.104</v>
       </c>
       <c r="X130" s="22" t="n">
-        <v>-86.407</v>
+        <v>-2.613</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="20" t="inlineStr">
         <is>
-          <t>미지급금 증감</t>
-        </is>
-      </c>
-      <c r="C131" s="22" t="n">
-        <v>42.502</v>
-      </c>
-      <c r="E131" s="22" t="n">
-        <v>116.314</v>
-      </c>
-      <c r="G131" s="22" t="n">
-        <v>-104.93</v>
-      </c>
-      <c r="I131" s="22" t="n">
-        <v>-18.073</v>
-      </c>
-      <c r="K131" s="22" t="n">
-        <v>-69.61199999999999</v>
-      </c>
-      <c r="M131" s="22" t="n">
-        <v>-58.46</v>
+          <t>지분법손익</t>
+        </is>
       </c>
       <c r="O131" s="22" t="n">
-        <v>-65.98</v>
+        <v>-5.467</v>
       </c>
       <c r="P131" s="22" t="n">
-        <v>110.384</v>
+        <v>-10.855</v>
       </c>
       <c r="Q131" s="22" t="n">
-        <v>-9.08</v>
+        <v>-1.464</v>
       </c>
       <c r="R131" s="22" t="n">
-        <v>430.492</v>
+        <v>1.039</v>
       </c>
       <c r="S131" s="22" t="n">
-        <v>-149.054</v>
-      </c>
-      <c r="T131" s="22" t="n">
-        <v>-276.782</v>
-      </c>
-      <c r="U131" s="22" t="n">
-        <v>5.361</v>
-      </c>
-      <c r="V131" s="22" t="n">
-        <v>116.314</v>
-      </c>
-      <c r="W131" s="22" t="n">
-        <v>-18.073</v>
-      </c>
-      <c r="X131" s="22" t="n">
-        <v>-58.46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="20" t="inlineStr">
         <is>
-          <t>선수금 증감</t>
+          <t>매출채권 증감</t>
         </is>
       </c>
       <c r="C132" s="22" t="n">
-        <v>30.537</v>
+        <v>59.075</v>
       </c>
       <c r="E132" s="22" t="n">
-        <v>40.281</v>
+        <v>-325.805</v>
+      </c>
+      <c r="G132" s="22" t="n">
+        <v>151.89</v>
       </c>
       <c r="I132" s="22" t="n">
-        <v>32.612</v>
+        <v>-52.498</v>
+      </c>
+      <c r="K132" s="22" t="n">
+        <v>337.369</v>
+      </c>
+      <c r="M132" s="22" t="n">
+        <v>150.059</v>
+      </c>
+      <c r="O132" s="22" t="n">
+        <v>-260.236</v>
+      </c>
+      <c r="P132" s="22" t="n">
+        <v>322.295</v>
       </c>
       <c r="Q132" s="22" t="n">
-        <v>9.042999999999999</v>
+        <v>42.955</v>
       </c>
       <c r="R132" s="22" t="n">
-        <v>-24.19</v>
+        <v>-586.182</v>
       </c>
       <c r="S132" s="22" t="n">
-        <v>21.358</v>
+        <v>227.97</v>
       </c>
       <c r="T132" s="22" t="n">
-        <v>98.92100000000001</v>
+        <v>59.055</v>
       </c>
       <c r="U132" s="22" t="n">
-        <v>4.466</v>
+        <v>-495.64</v>
       </c>
       <c r="V132" s="22" t="n">
-        <v>40.281</v>
+        <v>-325.805</v>
       </c>
       <c r="W132" s="22" t="n">
-        <v>32.612</v>
+        <v>-52.498</v>
+      </c>
+      <c r="X132" s="22" t="n">
+        <v>150.059</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="20" t="inlineStr">
         <is>
-          <t>미지급 소비세 증감</t>
+          <t>선급금 증감</t>
         </is>
       </c>
       <c r="C133" s="22" t="n">
-        <v>43.236</v>
+        <v>-2.228</v>
       </c>
       <c r="G133" s="22" t="n">
-        <v>-8.868</v>
+        <v>-225.664</v>
+      </c>
+      <c r="I133" s="22" t="n">
+        <v>19.341</v>
       </c>
       <c r="K133" s="22" t="n">
-        <v>-85.542</v>
-      </c>
-      <c r="O133" s="22" t="n">
-        <v>64.339</v>
-      </c>
-      <c r="P133" s="22" t="n">
-        <v>36.476</v>
-      </c>
-      <c r="Q133" s="22" t="n">
-        <v>-14.969</v>
-      </c>
-      <c r="R133" s="22" t="n">
-        <v>115.237</v>
-      </c>
-      <c r="S133" s="22" t="n">
-        <v>-152.579</v>
+        <v>-114.212</v>
+      </c>
+      <c r="M133" s="22" t="n">
+        <v>-104.377</v>
+      </c>
+      <c r="W133" s="22" t="n">
+        <v>19.341</v>
+      </c>
+      <c r="X133" s="22" t="n">
+        <v>-104.377</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="20" t="inlineStr">
         <is>
-          <t>Decrease Increase In Consumption Taxes Receivable Payable Ope CF</t>
-        </is>
+          <t>Decrease Increase In Advance Expense Payments Other Ope CF</t>
+        </is>
+      </c>
+      <c r="C134" s="22" t="n">
+        <v>84.432</v>
       </c>
       <c r="E134" s="22" t="n">
-        <v>78.678</v>
+        <v>100.312</v>
+      </c>
+      <c r="G134" s="22" t="n">
+        <v>28.585</v>
       </c>
       <c r="I134" s="22" t="n">
-        <v>25.042</v>
+        <v>-6.616</v>
+      </c>
+      <c r="K134" s="22" t="n">
+        <v>20.485</v>
       </c>
       <c r="M134" s="22" t="n">
-        <v>-90.486</v>
+        <v>23.477</v>
+      </c>
+      <c r="O134" s="22" t="n">
+        <v>-161.692</v>
+      </c>
+      <c r="P134" s="22" t="n">
+        <v>46.833</v>
+      </c>
+      <c r="Q134" s="22" t="n">
+        <v>121.746</v>
+      </c>
+      <c r="R134" s="22" t="n">
+        <v>-15.432</v>
       </c>
       <c r="S134" s="22" t="n">
-        <v>-152.579</v>
+        <v>-228.306</v>
       </c>
       <c r="T134" s="22" t="n">
-        <v>7.094</v>
+        <v>-100.362</v>
       </c>
       <c r="U134" s="22" t="n">
-        <v>-21.012</v>
+        <v>51.069</v>
       </c>
       <c r="V134" s="22" t="n">
-        <v>78.678</v>
+        <v>100.312</v>
       </c>
       <c r="W134" s="22" t="n">
-        <v>25.042</v>
+        <v>-6.616</v>
       </c>
       <c r="X134" s="22" t="n">
-        <v>-90.486</v>
+        <v>23.477</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C135" s="22" t="n">
-        <v>21.988</v>
-      </c>
-      <c r="E135" s="22" t="n">
-        <v>-49.188</v>
-      </c>
-      <c r="G135" s="22" t="n">
-        <v>-35.233</v>
-      </c>
-      <c r="I135" s="22" t="n">
-        <v>-45.974</v>
-      </c>
-      <c r="K135" s="22" t="n">
-        <v>63.836</v>
-      </c>
-      <c r="M135" s="22" t="n">
-        <v>22.763</v>
+          <t>파산갱생채권 증감</t>
+        </is>
       </c>
       <c r="O135" s="22" t="n">
-        <v>286.011</v>
+        <v>0</v>
       </c>
       <c r="P135" s="22" t="n">
-        <v>8.210000000000001</v>
+        <v>-115.164</v>
       </c>
       <c r="Q135" s="22" t="n">
-        <v>-3.428</v>
+        <v>-5.149</v>
       </c>
       <c r="R135" s="22" t="n">
-        <v>-3.084</v>
+        <v>2.341</v>
       </c>
       <c r="S135" s="22" t="n">
-        <v>-3.625</v>
+        <v>-2.037</v>
       </c>
       <c r="T135" s="22" t="n">
-        <v>-53.921</v>
-      </c>
-      <c r="U135" s="22" t="n">
-        <v>13.43</v>
-      </c>
-      <c r="V135" s="22" t="n">
-        <v>-49.188</v>
-      </c>
-      <c r="W135" s="22" t="n">
-        <v>-45.974</v>
-      </c>
-      <c r="X135" s="22" t="n">
-        <v>22.763</v>
+        <v>-12.661</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="20" t="inlineStr">
         <is>
-          <t>소계</t>
+          <t>매입채무 증감</t>
         </is>
       </c>
       <c r="C136" s="22" t="n">
-        <v>465.48</v>
+        <v>-12.77</v>
       </c>
       <c r="E136" s="22" t="n">
-        <v>643.256</v>
+        <v>-7.945</v>
       </c>
       <c r="G136" s="22" t="n">
-        <v>-355.672</v>
+        <v>-7.778</v>
       </c>
       <c r="I136" s="22" t="n">
-        <v>72.102</v>
+        <v>-8.042999999999999</v>
       </c>
       <c r="K136" s="22" t="n">
-        <v>-68.98999999999999</v>
+        <v>4.715</v>
       </c>
       <c r="M136" s="22" t="n">
-        <v>123.943</v>
+        <v>5.373</v>
       </c>
       <c r="O136" s="22" t="n">
-        <v>217.076</v>
+        <v>-43.891</v>
       </c>
       <c r="P136" s="22" t="n">
-        <v>1206.279</v>
+        <v>5.024</v>
       </c>
       <c r="Q136" s="22" t="n">
-        <v>979.542</v>
+        <v>4.144</v>
       </c>
       <c r="R136" s="22" t="n">
-        <v>975.633</v>
+        <v>5.454</v>
       </c>
       <c r="S136" s="22" t="n">
-        <v>1354.437</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="T136" s="22" t="n">
-        <v>824.066</v>
+        <v>-10.598</v>
       </c>
       <c r="U136" s="22" t="n">
-        <v>411.748</v>
+        <v>6.517</v>
       </c>
       <c r="V136" s="22" t="n">
-        <v>643.256</v>
+        <v>-7.945</v>
       </c>
       <c r="W136" s="22" t="n">
-        <v>72.102</v>
+        <v>-8.042999999999999</v>
       </c>
       <c r="X136" s="22" t="n">
-        <v>123.943</v>
+        <v>5.373</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="20" t="inlineStr">
         <is>
-          <t>이자·배당금 수취</t>
+          <t>Increase Decrease In Accounts Payable Ope CF</t>
         </is>
       </c>
       <c r="C137" s="22" t="n">
-        <v>23.769</v>
+        <v>-78.399</v>
       </c>
       <c r="E137" s="22" t="n">
-        <v>28.194</v>
+        <v>162.167</v>
       </c>
       <c r="G137" s="22" t="n">
-        <v>32.973</v>
+        <v>-399.452</v>
       </c>
       <c r="I137" s="22" t="n">
-        <v>116.91</v>
+        <v>-277.226</v>
       </c>
       <c r="K137" s="22" t="n">
-        <v>17.429</v>
+        <v>-117.036</v>
       </c>
       <c r="M137" s="22" t="n">
-        <v>45.005</v>
+        <v>-86.407</v>
       </c>
       <c r="O137" s="22" t="n">
-        <v>79.813</v>
+        <v>-1.955</v>
       </c>
       <c r="P137" s="22" t="n">
-        <v>191.725</v>
+        <v>155.865</v>
       </c>
       <c r="Q137" s="22" t="n">
-        <v>151.248</v>
+        <v>70.248</v>
       </c>
       <c r="R137" s="22" t="n">
-        <v>70.011</v>
+        <v>-81.962</v>
       </c>
       <c r="S137" s="22" t="n">
-        <v>61.799</v>
+        <v>184.89</v>
       </c>
       <c r="T137" s="22" t="n">
-        <v>19.351</v>
+        <v>-182.405</v>
       </c>
       <c r="U137" s="22" t="n">
-        <v>0.73</v>
+        <v>113.511</v>
       </c>
       <c r="V137" s="22" t="n">
-        <v>28.194</v>
+        <v>162.167</v>
       </c>
       <c r="W137" s="22" t="n">
-        <v>116.91</v>
+        <v>-277.226</v>
       </c>
       <c r="X137" s="22" t="n">
-        <v>45.005</v>
+        <v>-86.407</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="20" t="inlineStr">
         <is>
-          <t>이자 지급</t>
+          <t>미지급금 증감</t>
         </is>
       </c>
       <c r="C138" s="22" t="n">
-        <v>-0.015</v>
+        <v>42.502</v>
       </c>
       <c r="E138" s="22" t="n">
-        <v>-0.081</v>
+        <v>116.314</v>
       </c>
       <c r="G138" s="22" t="n">
-        <v>-0.103</v>
+        <v>-104.93</v>
       </c>
       <c r="I138" s="22" t="n">
-        <v>-0.186</v>
+        <v>-18.073</v>
       </c>
       <c r="K138" s="22" t="n">
-        <v>-0.063</v>
+        <v>-69.61199999999999</v>
       </c>
       <c r="M138" s="22" t="n">
-        <v>-0.106</v>
+        <v>-58.46</v>
       </c>
       <c r="O138" s="22" t="n">
-        <v>-0.041</v>
+        <v>-65.98</v>
       </c>
       <c r="P138" s="22" t="n">
-        <v>-0.101</v>
+        <v>110.384</v>
       </c>
       <c r="Q138" s="22" t="n">
-        <v>-0.059</v>
+        <v>-9.08</v>
       </c>
       <c r="R138" s="22" t="n">
-        <v>-0.048</v>
+        <v>430.492</v>
       </c>
       <c r="S138" s="22" t="n">
-        <v>-0.102</v>
+        <v>-149.054</v>
       </c>
       <c r="T138" s="22" t="n">
-        <v>-0.057</v>
+        <v>-276.782</v>
       </c>
       <c r="U138" s="22" t="n">
-        <v>-0.057</v>
+        <v>5.361</v>
       </c>
       <c r="V138" s="22" t="n">
-        <v>-0.081</v>
+        <v>116.314</v>
       </c>
       <c r="W138" s="22" t="n">
-        <v>-0.186</v>
+        <v>-18.073</v>
       </c>
       <c r="X138" s="22" t="n">
-        <v>-0.106</v>
+        <v>-58.46</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="20" t="inlineStr">
         <is>
-          <t>법인세 환급</t>
+          <t>선수금 증감</t>
         </is>
       </c>
       <c r="C139" s="22" t="n">
-        <v>2.544</v>
+        <v>30.537</v>
       </c>
       <c r="E139" s="22" t="n">
-        <v>2.544</v>
-      </c>
-      <c r="G139" s="22" t="n">
-        <v>0.467</v>
+        <v>40.281</v>
       </c>
       <c r="I139" s="22" t="n">
-        <v>0.699</v>
-      </c>
-      <c r="K139" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M139" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O139" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P139" s="22" t="n">
-        <v>3.457</v>
+        <v>32.612</v>
       </c>
       <c r="Q139" s="22" t="n">
-        <v>0</v>
+        <v>9.042999999999999</v>
       </c>
       <c r="R139" s="22" t="n">
-        <v>0</v>
+        <v>-24.19</v>
       </c>
       <c r="S139" s="22" t="n">
-        <v>0.075</v>
+        <v>21.358</v>
       </c>
       <c r="T139" s="22" t="n">
-        <v>0.075</v>
+        <v>98.92100000000001</v>
       </c>
       <c r="U139" s="22" t="n">
-        <v>1.208</v>
+        <v>4.466</v>
       </c>
       <c r="V139" s="22" t="n">
-        <v>2.544</v>
+        <v>40.281</v>
       </c>
       <c r="W139" s="22" t="n">
-        <v>0.699</v>
-      </c>
-      <c r="X139" s="22" t="n">
-        <v>0</v>
+        <v>32.612</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="20" t="inlineStr">
         <is>
-          <t>법인세 납부</t>
+          <t>미지급 소비세 증감</t>
         </is>
       </c>
       <c r="C140" s="22" t="n">
-        <v>-277.182</v>
-      </c>
-      <c r="E140" s="22" t="n">
-        <v>-498.689</v>
+        <v>43.236</v>
       </c>
       <c r="G140" s="22" t="n">
-        <v>-76.54600000000001</v>
-      </c>
-      <c r="I140" s="22" t="n">
-        <v>-232.071</v>
+        <v>-8.868</v>
       </c>
       <c r="K140" s="22" t="n">
-        <v>-246.661</v>
-      </c>
-      <c r="M140" s="22" t="n">
-        <v>-438.937</v>
+        <v>-85.542</v>
       </c>
       <c r="O140" s="22" t="n">
-        <v>-280.481</v>
+        <v>64.339</v>
       </c>
       <c r="P140" s="22" t="n">
-        <v>-203.572</v>
+        <v>36.476</v>
       </c>
       <c r="Q140" s="22" t="n">
-        <v>-249.826</v>
+        <v>-14.969</v>
       </c>
       <c r="R140" s="22" t="n">
-        <v>-111.168</v>
+        <v>115.237</v>
       </c>
       <c r="S140" s="22" t="n">
-        <v>-597.553</v>
-      </c>
-      <c r="T140" s="22" t="n">
-        <v>-532.301</v>
-      </c>
-      <c r="U140" s="22" t="n">
-        <v>-346.203</v>
-      </c>
-      <c r="V140" s="22" t="n">
-        <v>-498.689</v>
-      </c>
-      <c r="W140" s="22" t="n">
-        <v>-232.071</v>
-      </c>
-      <c r="X140" s="22" t="n">
-        <v>-438.937</v>
+        <v>-152.579</v>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="9" t="inlineStr">
-        <is>
-          <t>영업활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="C141" s="12" t="n">
-        <v>214.597</v>
-      </c>
-      <c r="E141" s="12" t="n">
-        <v>175.224</v>
-      </c>
-      <c r="G141" s="12" t="n">
-        <v>-398.881</v>
-      </c>
-      <c r="I141" s="12" t="n">
-        <v>-42.544</v>
-      </c>
-      <c r="K141" s="12" t="n">
-        <v>-298.285</v>
-      </c>
-      <c r="M141" s="12" t="n">
-        <v>-270.093</v>
-      </c>
-      <c r="O141" s="12" t="n">
-        <v>16.368</v>
-      </c>
-      <c r="P141" s="12" t="n">
-        <v>1197.788</v>
-      </c>
-      <c r="Q141" s="12" t="n">
-        <v>880.905</v>
-      </c>
-      <c r="R141" s="12" t="n">
-        <v>934.427</v>
-      </c>
-      <c r="S141" s="12" t="n">
-        <v>818.655</v>
-      </c>
-      <c r="T141" s="12" t="n">
-        <v>311.133</v>
-      </c>
-      <c r="U141" s="12" t="n">
-        <v>67.426</v>
-      </c>
-      <c r="V141" s="12" t="n">
-        <v>175.224</v>
-      </c>
-      <c r="W141" s="12" t="n">
-        <v>-42.544</v>
-      </c>
-      <c r="X141" s="12" t="n">
-        <v>-270.093</v>
+      <c r="A141" s="20" t="inlineStr">
+        <is>
+          <t>미지급·미수 소비세 등 증감액</t>
+        </is>
+      </c>
+      <c r="E141" s="22" t="n">
+        <v>78.678</v>
+      </c>
+      <c r="I141" s="22" t="n">
+        <v>25.042</v>
+      </c>
+      <c r="M141" s="22" t="n">
+        <v>-90.486</v>
+      </c>
+      <c r="S141" s="22" t="n">
+        <v>-152.579</v>
+      </c>
+      <c r="T141" s="22" t="n">
+        <v>7.094</v>
+      </c>
+      <c r="U141" s="22" t="n">
+        <v>-21.012</v>
+      </c>
+      <c r="V141" s="22" t="n">
+        <v>78.678</v>
+      </c>
+      <c r="W141" s="22" t="n">
+        <v>25.042</v>
+      </c>
+      <c r="X141" s="22" t="n">
+        <v>-90.486</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="20" t="inlineStr">
         <is>
-          <t>유가증권 매각·상환 수입</t>
-        </is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="C142" s="22" t="n">
+        <v>21.988</v>
       </c>
       <c r="E142" s="22" t="n">
-        <v>0</v>
+        <v>-49.188</v>
+      </c>
+      <c r="G142" s="22" t="n">
+        <v>-35.233</v>
+      </c>
+      <c r="I142" s="22" t="n">
+        <v>-45.974</v>
+      </c>
+      <c r="K142" s="22" t="n">
+        <v>63.836</v>
+      </c>
+      <c r="M142" s="22" t="n">
+        <v>22.763</v>
       </c>
       <c r="O142" s="22" t="n">
-        <v>121.592</v>
+        <v>286.011</v>
       </c>
       <c r="P142" s="22" t="n">
-        <v>177.344</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="Q142" s="22" t="n">
-        <v>2.613</v>
+        <v>-3.428</v>
       </c>
       <c r="R142" s="22" t="n">
-        <v>0</v>
+        <v>-3.084</v>
       </c>
       <c r="S142" s="22" t="n">
-        <v>0</v>
+        <v>-3.625</v>
       </c>
       <c r="T142" s="22" t="n">
-        <v>3.029</v>
+        <v>-53.921</v>
       </c>
       <c r="U142" s="22" t="n">
-        <v>10.813</v>
+        <v>13.43</v>
       </c>
       <c r="V142" s="22" t="n">
-        <v>0</v>
+        <v>-49.188</v>
+      </c>
+      <c r="W142" s="22" t="n">
+        <v>-45.974</v>
+      </c>
+      <c r="X142" s="22" t="n">
+        <v>22.763</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="20" t="inlineStr">
         <is>
-          <t>유형자산 취득(설비투자)</t>
-        </is>
+          <t>소계</t>
+        </is>
+      </c>
+      <c r="C143" s="22" t="n">
+        <v>465.48</v>
+      </c>
+      <c r="E143" s="22" t="n">
+        <v>643.256</v>
+      </c>
+      <c r="G143" s="22" t="n">
+        <v>-355.672</v>
+      </c>
+      <c r="I143" s="22" t="n">
+        <v>72.102</v>
+      </c>
+      <c r="K143" s="22" t="n">
+        <v>-68.98999999999999</v>
+      </c>
+      <c r="M143" s="22" t="n">
+        <v>123.943</v>
       </c>
       <c r="O143" s="22" t="n">
-        <v>-45.096</v>
+        <v>217.076</v>
       </c>
       <c r="P143" s="22" t="n">
-        <v>-16.263</v>
+        <v>1206.279</v>
+      </c>
+      <c r="Q143" s="22" t="n">
+        <v>979.542</v>
+      </c>
+      <c r="R143" s="22" t="n">
+        <v>975.633</v>
+      </c>
+      <c r="S143" s="22" t="n">
+        <v>1354.437</v>
+      </c>
+      <c r="T143" s="22" t="n">
+        <v>824.066</v>
+      </c>
+      <c r="U143" s="22" t="n">
+        <v>411.748</v>
+      </c>
+      <c r="V143" s="22" t="n">
+        <v>643.256</v>
+      </c>
+      <c r="W143" s="22" t="n">
+        <v>72.102</v>
+      </c>
+      <c r="X143" s="22" t="n">
+        <v>123.943</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 취득</t>
+          <t>이자·배당금 수취</t>
         </is>
       </c>
       <c r="C144" s="22" t="n">
-        <v>-2751.538</v>
+        <v>23.769</v>
       </c>
       <c r="E144" s="22" t="n">
-        <v>-4824.977</v>
+        <v>28.194</v>
       </c>
       <c r="G144" s="22" t="n">
-        <v>-4630.253</v>
+        <v>32.973</v>
       </c>
       <c r="I144" s="22" t="n">
-        <v>-9343.325999999999</v>
+        <v>116.91</v>
       </c>
       <c r="K144" s="22" t="n">
-        <v>-4302.783</v>
+        <v>17.429</v>
       </c>
       <c r="M144" s="22" t="n">
-        <v>-19829.995</v>
+        <v>45.005</v>
       </c>
       <c r="O144" s="22" t="n">
-        <v>-10951.549</v>
+        <v>79.813</v>
       </c>
       <c r="P144" s="22" t="n">
-        <v>-5795.559</v>
+        <v>191.725</v>
       </c>
       <c r="Q144" s="22" t="n">
-        <v>-1422.694</v>
+        <v>151.248</v>
       </c>
       <c r="R144" s="22" t="n">
-        <v>0</v>
+        <v>70.011</v>
       </c>
       <c r="S144" s="22" t="n">
-        <v>0</v>
+        <v>61.799</v>
       </c>
       <c r="T144" s="22" t="n">
-        <v>-561.431</v>
+        <v>19.351</v>
       </c>
       <c r="U144" s="22" t="n">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="V144" s="22" t="n">
-        <v>-4824.977</v>
+        <v>28.194</v>
       </c>
       <c r="W144" s="22" t="n">
-        <v>-9343.325999999999</v>
+        <v>116.91</v>
       </c>
       <c r="X144" s="22" t="n">
-        <v>-19829.995</v>
+        <v>45.005</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 매각·상환 수입</t>
+          <t>이자 지급</t>
         </is>
       </c>
       <c r="C145" s="22" t="n">
-        <v>2852.123</v>
+        <v>-0.015</v>
       </c>
       <c r="E145" s="22" t="n">
-        <v>3185.906</v>
+        <v>-0.081</v>
       </c>
       <c r="G145" s="22" t="n">
-        <v>2104.83</v>
+        <v>-0.103</v>
       </c>
       <c r="I145" s="22" t="n">
-        <v>10673.054</v>
+        <v>-0.186</v>
       </c>
       <c r="K145" s="22" t="n">
-        <v>3422.914</v>
+        <v>-0.063</v>
       </c>
       <c r="M145" s="22" t="n">
-        <v>14084.886</v>
+        <v>-0.106</v>
       </c>
       <c r="O145" s="22" t="n">
-        <v>5866.512</v>
+        <v>-0.041</v>
       </c>
       <c r="P145" s="22" t="n">
-        <v>8171.058</v>
+        <v>-0.101</v>
       </c>
       <c r="Q145" s="22" t="n">
-        <v>3146.043</v>
+        <v>-0.059</v>
       </c>
       <c r="R145" s="22" t="n">
-        <v>456.647</v>
+        <v>-0.048</v>
       </c>
       <c r="S145" s="22" t="n">
-        <v>0</v>
+        <v>-0.102</v>
       </c>
       <c r="T145" s="22" t="n">
-        <v>12.76</v>
+        <v>-0.057</v>
       </c>
       <c r="U145" s="22" t="n">
-        <v>3018.581</v>
+        <v>-0.057</v>
       </c>
       <c r="V145" s="22" t="n">
-        <v>3185.906</v>
+        <v>-0.081</v>
       </c>
       <c r="W145" s="22" t="n">
-        <v>10673.054</v>
+        <v>-0.186</v>
       </c>
       <c r="X145" s="22" t="n">
-        <v>14084.886</v>
+        <v>-0.106</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="20" t="inlineStr">
         <is>
-          <t>무형자산 취득</t>
-        </is>
+          <t>법인세 환급</t>
+        </is>
+      </c>
+      <c r="C146" s="22" t="n">
+        <v>2.544</v>
+      </c>
+      <c r="E146" s="22" t="n">
+        <v>2.544</v>
+      </c>
+      <c r="G146" s="22" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="I146" s="22" t="n">
+        <v>0.699</v>
+      </c>
+      <c r="K146" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O146" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P146" s="22" t="n">
+        <v>3.457</v>
+      </c>
+      <c r="Q146" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="R146" s="22" t="n">
-        <v>-10.687</v>
+        <v>0</v>
       </c>
       <c r="S146" s="22" t="n">
-        <v>-28.322</v>
+        <v>0.075</v>
+      </c>
+      <c r="T146" s="22" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="U146" s="22" t="n">
+        <v>1.208</v>
+      </c>
+      <c r="V146" s="22" t="n">
+        <v>2.544</v>
+      </c>
+      <c r="W146" s="22" t="n">
+        <v>0.699</v>
+      </c>
+      <c r="X146" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="20" t="inlineStr">
         <is>
-          <t>임차보증금·보증금 납입</t>
-        </is>
+          <t>법인세 납부</t>
+        </is>
+      </c>
+      <c r="C147" s="22" t="n">
+        <v>-277.182</v>
+      </c>
+      <c r="E147" s="22" t="n">
+        <v>-498.689</v>
+      </c>
+      <c r="G147" s="22" t="n">
+        <v>-76.54600000000001</v>
+      </c>
+      <c r="I147" s="22" t="n">
+        <v>-232.071</v>
+      </c>
+      <c r="K147" s="22" t="n">
+        <v>-246.661</v>
+      </c>
+      <c r="M147" s="22" t="n">
+        <v>-438.937</v>
+      </c>
+      <c r="O147" s="22" t="n">
+        <v>-280.481</v>
+      </c>
+      <c r="P147" s="22" t="n">
+        <v>-203.572</v>
+      </c>
+      <c r="Q147" s="22" t="n">
+        <v>-249.826</v>
       </c>
       <c r="R147" s="22" t="n">
-        <v>-19.127</v>
+        <v>-111.168</v>
       </c>
       <c r="S147" s="22" t="n">
-        <v>-64.971</v>
+        <v>-597.553</v>
+      </c>
+      <c r="T147" s="22" t="n">
+        <v>-532.301</v>
+      </c>
+      <c r="U147" s="22" t="n">
+        <v>-346.203</v>
+      </c>
+      <c r="V147" s="22" t="n">
+        <v>-498.689</v>
+      </c>
+      <c r="W147" s="22" t="n">
+        <v>-232.071</v>
+      </c>
+      <c r="X147" s="22" t="n">
+        <v>-438.937</v>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="20" t="inlineStr">
-        <is>
-          <t>Collection Of Short Term Loans Receivable Inv CF</t>
-        </is>
-      </c>
-      <c r="R148" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S148" s="22" t="n">
-        <v>40</v>
-      </c>
-      <c r="T148" s="22" t="n">
-        <v>0</v>
+      <c r="A148" s="9" t="inlineStr">
+        <is>
+          <t>영업활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="C148" s="12" t="n">
+        <v>214.597</v>
+      </c>
+      <c r="E148" s="12" t="n">
+        <v>175.224</v>
+      </c>
+      <c r="G148" s="12" t="n">
+        <v>-398.881</v>
+      </c>
+      <c r="I148" s="12" t="n">
+        <v>-42.544</v>
+      </c>
+      <c r="K148" s="12" t="n">
+        <v>-298.285</v>
+      </c>
+      <c r="M148" s="12" t="n">
+        <v>-270.093</v>
+      </c>
+      <c r="O148" s="12" t="n">
+        <v>16.368</v>
+      </c>
+      <c r="P148" s="12" t="n">
+        <v>1197.788</v>
+      </c>
+      <c r="Q148" s="12" t="n">
+        <v>880.905</v>
+      </c>
+      <c r="R148" s="12" t="n">
+        <v>934.427</v>
+      </c>
+      <c r="S148" s="12" t="n">
+        <v>818.655</v>
+      </c>
+      <c r="T148" s="12" t="n">
+        <v>311.133</v>
+      </c>
+      <c r="U148" s="12" t="n">
+        <v>67.426</v>
+      </c>
+      <c r="V148" s="12" t="n">
+        <v>175.224</v>
+      </c>
+      <c r="W148" s="12" t="n">
+        <v>-42.544</v>
+      </c>
+      <c r="X148" s="12" t="n">
+        <v>-270.093</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="20" t="inlineStr">
         <is>
-          <t>장기대여금 회수</t>
-        </is>
+          <t>유가증권 매각·상환 수입</t>
+        </is>
+      </c>
+      <c r="E149" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O149" s="22" t="n">
+        <v>121.592</v>
+      </c>
+      <c r="P149" s="22" t="n">
+        <v>177.344</v>
+      </c>
+      <c r="Q149" s="22" t="n">
+        <v>2.613</v>
       </c>
       <c r="R149" s="22" t="n">
         <v>0</v>
       </c>
       <c r="S149" s="22" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="T149" s="22" t="n">
+        <v>3.029</v>
+      </c>
+      <c r="U149" s="22" t="n">
+        <v>10.813</v>
+      </c>
+      <c r="V149" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="20" t="inlineStr">
         <is>
-          <t>Proceeds From Share Of Profits On Investments In Capital Inv CF</t>
-        </is>
-      </c>
-      <c r="C150" s="22" t="n">
-        <v>1.121</v>
-      </c>
-      <c r="E150" s="22" t="n">
-        <v>3.411</v>
-      </c>
-      <c r="G150" s="22" t="n">
-        <v>38.705</v>
-      </c>
-      <c r="I150" s="22" t="n">
-        <v>42.903</v>
-      </c>
-      <c r="K150" s="22" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="M150" s="22" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="R150" s="22" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="S150" s="22" t="n">
-        <v>67.38800000000001</v>
-      </c>
-      <c r="T150" s="22" t="n">
-        <v>2.016</v>
-      </c>
-      <c r="U150" s="22" t="n">
-        <v>61.465</v>
-      </c>
-      <c r="V150" s="22" t="n">
-        <v>3.411</v>
-      </c>
-      <c r="W150" s="22" t="n">
-        <v>42.903</v>
-      </c>
-      <c r="X150" s="22" t="n">
-        <v>2.16</v>
+          <t>유형자산 취득(설비투자)</t>
+        </is>
+      </c>
+      <c r="O150" s="22" t="n">
+        <v>-45.096</v>
+      </c>
+      <c r="P150" s="22" t="n">
+        <v>-16.263</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>투자유가증권 취득</t>
         </is>
       </c>
       <c r="C151" s="22" t="n">
-        <v>-21.745</v>
+        <v>-2751.538</v>
       </c>
       <c r="E151" s="22" t="n">
-        <v>-44.222</v>
+        <v>-4824.977</v>
       </c>
       <c r="G151" s="22" t="n">
-        <v>-3.04</v>
+        <v>-4630.253</v>
       </c>
       <c r="I151" s="22" t="n">
-        <v>-15.822</v>
+        <v>-9343.325999999999</v>
       </c>
       <c r="K151" s="22" t="n">
-        <v>-6.937</v>
+        <v>-4302.783</v>
       </c>
       <c r="M151" s="22" t="n">
-        <v>-14.043</v>
+        <v>-19829.995</v>
       </c>
       <c r="O151" s="22" t="n">
-        <v>-51.133</v>
+        <v>-10951.549</v>
       </c>
       <c r="P151" s="22" t="n">
-        <v>-63.383</v>
+        <v>-5795.559</v>
       </c>
       <c r="Q151" s="22" t="n">
-        <v>-19.547</v>
+        <v>-1422.694</v>
       </c>
       <c r="R151" s="22" t="n">
-        <v>-16.02</v>
+        <v>0</v>
       </c>
       <c r="S151" s="22" t="n">
-        <v>-30.244</v>
+        <v>0</v>
       </c>
       <c r="T151" s="22" t="n">
-        <v>-25.362</v>
+        <v>-561.431</v>
       </c>
       <c r="U151" s="22" t="n">
-        <v>-9.432</v>
+        <v>0</v>
       </c>
       <c r="V151" s="22" t="n">
-        <v>-44.222</v>
+        <v>-4824.977</v>
       </c>
       <c r="W151" s="22" t="n">
-        <v>-15.822</v>
+        <v>-9343.325999999999</v>
       </c>
       <c r="X151" s="22" t="n">
-        <v>-14.043</v>
+        <v>-19829.995</v>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="9" t="inlineStr">
-        <is>
-          <t>투자활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="C152" s="12" t="n">
-        <v>79.961</v>
-      </c>
-      <c r="E152" s="12" t="n">
-        <v>-1679.881</v>
-      </c>
-      <c r="G152" s="12" t="n">
-        <v>-2489.757</v>
-      </c>
-      <c r="I152" s="12" t="n">
-        <v>1356.809</v>
-      </c>
-      <c r="K152" s="12" t="n">
-        <v>-886.076</v>
-      </c>
-      <c r="M152" s="12" t="n">
-        <v>-5756.992</v>
-      </c>
-      <c r="O152" s="12" t="n">
-        <v>-5059.673</v>
-      </c>
-      <c r="P152" s="12" t="n">
-        <v>2489.46</v>
-      </c>
-      <c r="Q152" s="12" t="n">
-        <v>1706.416</v>
-      </c>
-      <c r="R152" s="12" t="n">
-        <v>410.821</v>
-      </c>
-      <c r="S152" s="12" t="n">
-        <v>104.755</v>
-      </c>
-      <c r="T152" s="12" t="n">
-        <v>-568.986</v>
-      </c>
-      <c r="U152" s="12" t="n">
-        <v>3081.428</v>
-      </c>
-      <c r="V152" s="12" t="n">
-        <v>-1679.881</v>
-      </c>
-      <c r="W152" s="12" t="n">
-        <v>1356.809</v>
-      </c>
-      <c r="X152" s="12" t="n">
-        <v>-5756.992</v>
+      <c r="A152" s="20" t="inlineStr">
+        <is>
+          <t>투자유가증권 매각·상환 수입</t>
+        </is>
+      </c>
+      <c r="C152" s="22" t="n">
+        <v>2852.123</v>
+      </c>
+      <c r="E152" s="22" t="n">
+        <v>3185.906</v>
+      </c>
+      <c r="G152" s="22" t="n">
+        <v>2104.83</v>
+      </c>
+      <c r="I152" s="22" t="n">
+        <v>10673.054</v>
+      </c>
+      <c r="K152" s="22" t="n">
+        <v>3422.914</v>
+      </c>
+      <c r="M152" s="22" t="n">
+        <v>14084.886</v>
+      </c>
+      <c r="O152" s="22" t="n">
+        <v>5866.512</v>
+      </c>
+      <c r="P152" s="22" t="n">
+        <v>8171.058</v>
+      </c>
+      <c r="Q152" s="22" t="n">
+        <v>3146.043</v>
+      </c>
+      <c r="R152" s="22" t="n">
+        <v>456.647</v>
+      </c>
+      <c r="S152" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T152" s="22" t="n">
+        <v>12.76</v>
+      </c>
+      <c r="U152" s="22" t="n">
+        <v>3018.581</v>
+      </c>
+      <c r="V152" s="22" t="n">
+        <v>3185.906</v>
+      </c>
+      <c r="W152" s="22" t="n">
+        <v>10673.054</v>
+      </c>
+      <c r="X152" s="22" t="n">
+        <v>14084.886</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="20" t="inlineStr">
         <is>
-          <t>배당금 지급</t>
-        </is>
-      </c>
-      <c r="C153" s="22" t="n">
-        <v>-152.78</v>
-      </c>
-      <c r="E153" s="22" t="n">
-        <v>-344.436</v>
-      </c>
-      <c r="G153" s="22" t="n">
-        <v>-238.683</v>
-      </c>
-      <c r="I153" s="22" t="n">
-        <v>-454.536</v>
-      </c>
-      <c r="K153" s="22" t="n">
-        <v>-311.449</v>
-      </c>
-      <c r="M153" s="22" t="n">
-        <v>-551.077</v>
-      </c>
-      <c r="O153" s="22" t="n">
-        <v>-304.745</v>
-      </c>
-      <c r="P153" s="22" t="n">
-        <v>-209.871</v>
-      </c>
-      <c r="Q153" s="22" t="n">
-        <v>-261.893</v>
+          <t>무형자산 취득</t>
+        </is>
       </c>
       <c r="R153" s="22" t="n">
-        <v>-261.587</v>
+        <v>-10.687</v>
       </c>
       <c r="S153" s="22" t="n">
-        <v>-285.963</v>
-      </c>
-      <c r="T153" s="22" t="n">
-        <v>-381.752</v>
-      </c>
-      <c r="U153" s="22" t="n">
-        <v>-315.412</v>
-      </c>
-      <c r="V153" s="22" t="n">
-        <v>-344.436</v>
-      </c>
-      <c r="W153" s="22" t="n">
-        <v>-454.536</v>
-      </c>
-      <c r="X153" s="22" t="n">
-        <v>-551.077</v>
+        <v>-28.322</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="20" t="inlineStr">
         <is>
-          <t>비지배주주 납입</t>
-        </is>
-      </c>
-      <c r="O154" s="22" t="n">
-        <v>50</v>
-      </c>
-      <c r="P154" s="22" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q154" s="22" t="n">
-        <v>0</v>
+          <t>임차보증금·보증금 납입</t>
+        </is>
+      </c>
+      <c r="R154" s="22" t="n">
+        <v>-19.127</v>
+      </c>
+      <c r="S154" s="22" t="n">
+        <v>-64.971</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="20" t="inlineStr">
         <is>
-          <t>비지배주주 환급</t>
+          <t>Collection Of Short Term Loans Receivable Inv CF</t>
         </is>
       </c>
       <c r="R155" s="22" t="n">
         <v>0</v>
       </c>
       <c r="S155" s="22" t="n">
-        <v>-145.05</v>
+        <v>40</v>
       </c>
       <c r="T155" s="22" t="n">
         <v>0</v>
@@ -9371,220 +9583,479 @@
     <row r="156">
       <c r="A156" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C156" s="22" t="n">
-        <v>-0.475</v>
-      </c>
-      <c r="E156" s="22" t="n">
-        <v>-2.203</v>
-      </c>
-      <c r="G156" s="22" t="n">
-        <v>-2.991</v>
-      </c>
-      <c r="I156" s="22" t="n">
-        <v>-6.003</v>
-      </c>
-      <c r="K156" s="22" t="n">
-        <v>-3.032</v>
-      </c>
-      <c r="M156" s="22" t="n">
-        <v>-6.085</v>
-      </c>
-      <c r="O156" s="22" t="n">
-        <v>9.574999999999999</v>
-      </c>
-      <c r="P156" s="22" t="n">
-        <v>-4.668</v>
-      </c>
-      <c r="Q156" s="22" t="n">
-        <v>-4.753</v>
+          <t>장기대여금 회수</t>
+        </is>
       </c>
       <c r="R156" s="22" t="n">
-        <v>-5.433</v>
+        <v>0</v>
       </c>
       <c r="S156" s="22" t="n">
-        <v>-5.245</v>
+        <v>95</v>
       </c>
       <c r="T156" s="22" t="n">
-        <v>-5.105</v>
-      </c>
-      <c r="U156" s="22" t="n">
-        <v>-4.96</v>
-      </c>
-      <c r="V156" s="22" t="n">
-        <v>-2.203</v>
-      </c>
-      <c r="W156" s="22" t="n">
-        <v>-6.003</v>
-      </c>
-      <c r="X156" s="22" t="n">
-        <v>-6.085</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="9" t="inlineStr">
-        <is>
-          <t>재무활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="C157" s="12" t="n">
-        <v>-153.255</v>
-      </c>
-      <c r="E157" s="12" t="n">
-        <v>-346.639</v>
-      </c>
-      <c r="G157" s="12" t="n">
-        <v>-241.675</v>
-      </c>
-      <c r="I157" s="12" t="n">
-        <v>-460.54</v>
-      </c>
-      <c r="K157" s="12" t="n">
-        <v>-314.482</v>
-      </c>
-      <c r="M157" s="12" t="n">
-        <v>-557.162</v>
-      </c>
-      <c r="O157" s="12" t="n">
-        <v>-245.17</v>
-      </c>
-      <c r="P157" s="12" t="n">
-        <v>-164.54</v>
-      </c>
-      <c r="Q157" s="12" t="n">
-        <v>-266.646</v>
-      </c>
-      <c r="R157" s="12" t="n">
-        <v>-267.02</v>
-      </c>
-      <c r="S157" s="12" t="n">
-        <v>-436.258</v>
-      </c>
-      <c r="T157" s="12" t="n">
-        <v>-386.858</v>
-      </c>
-      <c r="U157" s="12" t="n">
-        <v>-320.373</v>
-      </c>
-      <c r="V157" s="12" t="n">
-        <v>-346.639</v>
-      </c>
-      <c r="W157" s="12" t="n">
-        <v>-460.54</v>
-      </c>
-      <c r="X157" s="12" t="n">
-        <v>-557.162</v>
+      <c r="A157" s="20" t="inlineStr">
+        <is>
+          <t>Proceeds From Share Of Profits On Investments In Capital Inv CF</t>
+        </is>
+      </c>
+      <c r="C157" s="22" t="n">
+        <v>1.121</v>
+      </c>
+      <c r="E157" s="22" t="n">
+        <v>3.411</v>
+      </c>
+      <c r="G157" s="22" t="n">
+        <v>38.705</v>
+      </c>
+      <c r="I157" s="22" t="n">
+        <v>42.903</v>
+      </c>
+      <c r="K157" s="22" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="M157" s="22" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R157" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="S157" s="22" t="n">
+        <v>67.38800000000001</v>
+      </c>
+      <c r="T157" s="22" t="n">
+        <v>2.016</v>
+      </c>
+      <c r="U157" s="22" t="n">
+        <v>61.465</v>
+      </c>
+      <c r="V157" s="22" t="n">
+        <v>3.411</v>
+      </c>
+      <c r="W157" s="22" t="n">
+        <v>42.903</v>
+      </c>
+      <c r="X157" s="22" t="n">
+        <v>2.16</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="20" t="inlineStr">
         <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="C158" s="22" t="n">
+        <v>-21.745</v>
+      </c>
+      <c r="E158" s="22" t="n">
+        <v>-44.222</v>
+      </c>
+      <c r="G158" s="22" t="n">
+        <v>-3.04</v>
+      </c>
+      <c r="I158" s="22" t="n">
+        <v>-15.822</v>
+      </c>
+      <c r="K158" s="22" t="n">
+        <v>-6.937</v>
+      </c>
+      <c r="M158" s="22" t="n">
+        <v>-14.043</v>
+      </c>
+      <c r="O158" s="22" t="n">
+        <v>-51.133</v>
+      </c>
+      <c r="P158" s="22" t="n">
+        <v>-63.383</v>
+      </c>
+      <c r="Q158" s="22" t="n">
+        <v>-19.547</v>
+      </c>
+      <c r="R158" s="22" t="n">
+        <v>-16.02</v>
+      </c>
+      <c r="S158" s="22" t="n">
+        <v>-30.244</v>
+      </c>
+      <c r="T158" s="22" t="n">
+        <v>-25.362</v>
+      </c>
+      <c r="U158" s="22" t="n">
+        <v>-9.432</v>
+      </c>
+      <c r="V158" s="22" t="n">
+        <v>-44.222</v>
+      </c>
+      <c r="W158" s="22" t="n">
+        <v>-15.822</v>
+      </c>
+      <c r="X158" s="22" t="n">
+        <v>-14.043</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="9" t="inlineStr">
+        <is>
+          <t>투자활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="C159" s="12" t="n">
+        <v>79.961</v>
+      </c>
+      <c r="E159" s="12" t="n">
+        <v>-1679.881</v>
+      </c>
+      <c r="G159" s="12" t="n">
+        <v>-2489.757</v>
+      </c>
+      <c r="I159" s="12" t="n">
+        <v>1356.809</v>
+      </c>
+      <c r="K159" s="12" t="n">
+        <v>-886.076</v>
+      </c>
+      <c r="M159" s="12" t="n">
+        <v>-5756.992</v>
+      </c>
+      <c r="O159" s="12" t="n">
+        <v>-5059.673</v>
+      </c>
+      <c r="P159" s="12" t="n">
+        <v>2489.46</v>
+      </c>
+      <c r="Q159" s="12" t="n">
+        <v>1706.416</v>
+      </c>
+      <c r="R159" s="12" t="n">
+        <v>410.821</v>
+      </c>
+      <c r="S159" s="12" t="n">
+        <v>104.755</v>
+      </c>
+      <c r="T159" s="12" t="n">
+        <v>-568.986</v>
+      </c>
+      <c r="U159" s="12" t="n">
+        <v>3081.428</v>
+      </c>
+      <c r="V159" s="12" t="n">
+        <v>-1679.881</v>
+      </c>
+      <c r="W159" s="12" t="n">
+        <v>1356.809</v>
+      </c>
+      <c r="X159" s="12" t="n">
+        <v>-5756.992</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="20" t="inlineStr">
+        <is>
+          <t>배당금 지급</t>
+        </is>
+      </c>
+      <c r="C160" s="22" t="n">
+        <v>-152.78</v>
+      </c>
+      <c r="E160" s="22" t="n">
+        <v>-344.436</v>
+      </c>
+      <c r="G160" s="22" t="n">
+        <v>-238.683</v>
+      </c>
+      <c r="I160" s="22" t="n">
+        <v>-454.536</v>
+      </c>
+      <c r="K160" s="22" t="n">
+        <v>-311.449</v>
+      </c>
+      <c r="M160" s="22" t="n">
+        <v>-551.077</v>
+      </c>
+      <c r="O160" s="22" t="n">
+        <v>-304.745</v>
+      </c>
+      <c r="P160" s="22" t="n">
+        <v>-209.871</v>
+      </c>
+      <c r="Q160" s="22" t="n">
+        <v>-261.893</v>
+      </c>
+      <c r="R160" s="22" t="n">
+        <v>-261.587</v>
+      </c>
+      <c r="S160" s="22" t="n">
+        <v>-285.963</v>
+      </c>
+      <c r="T160" s="22" t="n">
+        <v>-381.752</v>
+      </c>
+      <c r="U160" s="22" t="n">
+        <v>-315.412</v>
+      </c>
+      <c r="V160" s="22" t="n">
+        <v>-344.436</v>
+      </c>
+      <c r="W160" s="22" t="n">
+        <v>-454.536</v>
+      </c>
+      <c r="X160" s="22" t="n">
+        <v>-551.077</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="20" t="inlineStr">
+        <is>
+          <t>비지배주주 납입</t>
+        </is>
+      </c>
+      <c r="O161" s="22" t="n">
+        <v>50</v>
+      </c>
+      <c r="P161" s="22" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q161" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="20" t="inlineStr">
+        <is>
+          <t>비지배주주 환급</t>
+        </is>
+      </c>
+      <c r="R162" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S162" s="22" t="n">
+        <v>-145.05</v>
+      </c>
+      <c r="T162" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="20" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="C163" s="22" t="n">
+        <v>-0.475</v>
+      </c>
+      <c r="E163" s="22" t="n">
+        <v>-2.203</v>
+      </c>
+      <c r="G163" s="22" t="n">
+        <v>-2.991</v>
+      </c>
+      <c r="I163" s="22" t="n">
+        <v>-6.003</v>
+      </c>
+      <c r="K163" s="22" t="n">
+        <v>-3.032</v>
+      </c>
+      <c r="M163" s="22" t="n">
+        <v>-6.085</v>
+      </c>
+      <c r="O163" s="22" t="n">
+        <v>9.574999999999999</v>
+      </c>
+      <c r="P163" s="22" t="n">
+        <v>-4.668</v>
+      </c>
+      <c r="Q163" s="22" t="n">
+        <v>-4.753</v>
+      </c>
+      <c r="R163" s="22" t="n">
+        <v>-5.433</v>
+      </c>
+      <c r="S163" s="22" t="n">
+        <v>-5.245</v>
+      </c>
+      <c r="T163" s="22" t="n">
+        <v>-5.105</v>
+      </c>
+      <c r="U163" s="22" t="n">
+        <v>-4.96</v>
+      </c>
+      <c r="V163" s="22" t="n">
+        <v>-2.203</v>
+      </c>
+      <c r="W163" s="22" t="n">
+        <v>-6.003</v>
+      </c>
+      <c r="X163" s="22" t="n">
+        <v>-6.085</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="9" t="inlineStr">
+        <is>
+          <t>재무활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="C164" s="12" t="n">
+        <v>-153.255</v>
+      </c>
+      <c r="E164" s="12" t="n">
+        <v>-346.639</v>
+      </c>
+      <c r="G164" s="12" t="n">
+        <v>-241.675</v>
+      </c>
+      <c r="I164" s="12" t="n">
+        <v>-460.54</v>
+      </c>
+      <c r="K164" s="12" t="n">
+        <v>-314.482</v>
+      </c>
+      <c r="M164" s="12" t="n">
+        <v>-557.162</v>
+      </c>
+      <c r="O164" s="12" t="n">
+        <v>-245.17</v>
+      </c>
+      <c r="P164" s="12" t="n">
+        <v>-164.54</v>
+      </c>
+      <c r="Q164" s="12" t="n">
+        <v>-266.646</v>
+      </c>
+      <c r="R164" s="12" t="n">
+        <v>-267.02</v>
+      </c>
+      <c r="S164" s="12" t="n">
+        <v>-436.258</v>
+      </c>
+      <c r="T164" s="12" t="n">
+        <v>-386.858</v>
+      </c>
+      <c r="U164" s="12" t="n">
+        <v>-320.373</v>
+      </c>
+      <c r="V164" s="12" t="n">
+        <v>-346.639</v>
+      </c>
+      <c r="W164" s="12" t="n">
+        <v>-460.54</v>
+      </c>
+      <c r="X164" s="12" t="n">
+        <v>-557.162</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="20" t="inlineStr">
+        <is>
           <t>현금성자산 환산차이</t>
         </is>
       </c>
-      <c r="C158" s="22" t="n">
+      <c r="C165" s="22" t="n">
         <v>12.511</v>
       </c>
-      <c r="E158" s="22" t="n">
+      <c r="E165" s="22" t="n">
         <v>13.345</v>
       </c>
-      <c r="G158" s="22" t="n">
+      <c r="G165" s="22" t="n">
         <v>3.371</v>
       </c>
-      <c r="I158" s="22" t="n">
+      <c r="I165" s="22" t="n">
         <v>8.218</v>
       </c>
-      <c r="K158" s="22" t="n">
+      <c r="K165" s="22" t="n">
         <v>2.125</v>
       </c>
-      <c r="M158" s="22" t="n">
+      <c r="M165" s="22" t="n">
         <v>17.813</v>
       </c>
-      <c r="O158" s="22" t="n">
+      <c r="O165" s="22" t="n">
         <v>-29.863</v>
       </c>
-      <c r="P158" s="22" t="n">
+      <c r="P165" s="22" t="n">
         <v>-18.766</v>
       </c>
-      <c r="Q158" s="22" t="n">
+      <c r="Q165" s="22" t="n">
         <v>-4.086</v>
       </c>
-      <c r="R158" s="22" t="n">
+      <c r="R165" s="22" t="n">
         <v>-6.511</v>
       </c>
-      <c r="S158" s="22" t="n">
+      <c r="S165" s="22" t="n">
         <v>-1.511</v>
       </c>
-      <c r="T158" s="22" t="n">
+      <c r="T165" s="22" t="n">
         <v>21.446</v>
       </c>
-      <c r="U158" s="22" t="n">
+      <c r="U165" s="22" t="n">
         <v>19.185</v>
       </c>
-      <c r="V158" s="22" t="n">
+      <c r="V165" s="22" t="n">
         <v>13.345</v>
       </c>
-      <c r="W158" s="22" t="n">
+      <c r="W165" s="22" t="n">
         <v>8.218</v>
       </c>
-      <c r="X158" s="22" t="n">
+      <c r="X165" s="22" t="n">
         <v>17.813</v>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="20" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="20" t="inlineStr">
         <is>
           <t>현금성자산 증감</t>
         </is>
       </c>
-      <c r="C159" s="22" t="n">
+      <c r="C166" s="22" t="n">
         <v>153.815</v>
       </c>
-      <c r="E159" s="22" t="n">
+      <c r="E166" s="22" t="n">
         <v>-1837.95</v>
       </c>
-      <c r="G159" s="22" t="n">
+      <c r="G166" s="22" t="n">
         <v>-3126.942</v>
       </c>
-      <c r="I159" s="22" t="n">
+      <c r="I166" s="22" t="n">
         <v>861.942</v>
       </c>
-      <c r="K159" s="22" t="n">
+      <c r="K166" s="22" t="n">
         <v>-1496.719</v>
       </c>
-      <c r="M159" s="22" t="n">
+      <c r="M166" s="22" t="n">
         <v>-6566.435</v>
       </c>
-      <c r="O159" s="22" t="n">
+      <c r="O166" s="22" t="n">
         <v>-5318.339</v>
       </c>
-      <c r="P159" s="22" t="n">
+      <c r="P166" s="22" t="n">
         <v>3503.942</v>
       </c>
-      <c r="Q159" s="22" t="n">
+      <c r="Q166" s="22" t="n">
         <v>2316.587</v>
       </c>
-      <c r="R159" s="22" t="n">
+      <c r="R166" s="22" t="n">
         <v>1071.717</v>
       </c>
-      <c r="S159" s="22" t="n">
+      <c r="S166" s="22" t="n">
         <v>485.64</v>
       </c>
-      <c r="T159" s="22" t="n">
+      <c r="T166" s="22" t="n">
         <v>-623.265</v>
       </c>
-      <c r="U159" s="22" t="n">
+      <c r="U166" s="22" t="n">
         <v>2847.668</v>
       </c>
-      <c r="V159" s="22" t="n">
+      <c r="V166" s="22" t="n">
         <v>-1837.95</v>
       </c>
-      <c r="W159" s="22" t="n">
+      <c r="W166" s="22" t="n">
         <v>861.942</v>
       </c>
-      <c r="X159" s="22" t="n">
+      <c r="X166" s="22" t="n">
         <v>-6566.435</v>
       </c>
     </row>
@@ -9625,7 +10096,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="45" t="inlineStr">
+      <c r="A2" s="46" t="inlineStr">
         <is>
           <t>재무비율은 기말 잔액 기준 · 분기 손익은 최근 4분기 합산(TTM)</t>
         </is>
@@ -11019,7 +11490,7 @@
       <c r="L42" s="25" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="46" t="inlineStr">
+      <c r="A43" s="47" t="inlineStr">
         <is>
           <t>부채비율</t>
         </is>
@@ -11071,7 +11542,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="46" t="inlineStr">
+      <c r="A44" s="47" t="inlineStr">
         <is>
           <t>순차입금비율</t>
         </is>
@@ -11123,7 +11594,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="46" t="inlineStr">
+      <c r="A45" s="47" t="inlineStr">
         <is>
           <t>자기자본비율</t>
         </is>
@@ -11175,7 +11646,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="46" t="inlineStr">
+      <c r="A46" s="47" t="inlineStr">
         <is>
           <t>유동비율</t>
         </is>
@@ -11227,7 +11698,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="46" t="inlineStr">
+      <c r="A47" s="47" t="inlineStr">
         <is>
           <t>당좌비율</t>
         </is>
@@ -11279,7 +11750,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="46" t="inlineStr">
+      <c r="A48" s="47" t="inlineStr">
         <is>
           <t>이자보상배율</t>
         </is>
@@ -11331,7 +11802,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="46" t="inlineStr">
+      <c r="A49" s="47" t="inlineStr">
         <is>
           <t>차입금 상환연수</t>
         </is>
@@ -11341,43 +11812,43 @@
           <t>4년↓ (버핏)</t>
         </is>
       </c>
-      <c r="C49" s="47">
+      <c r="C49" s="48">
         <f>IFERROR(IF((IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))&lt;=0,"적자",C28/(IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))),"")</f>
         <v/>
       </c>
-      <c r="D49" s="48">
+      <c r="D49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))&lt;=0,"적자",D28/(IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))),"")</f>
         <v/>
       </c>
-      <c r="E49" s="48">
+      <c r="E49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))&lt;=0,"적자",E28/(IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))),"")</f>
         <v/>
       </c>
-      <c r="F49" s="48">
+      <c r="F49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))&lt;=0,"적자",F28/(IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))),"")</f>
         <v/>
       </c>
-      <c r="G49" s="48">
+      <c r="G49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))&lt;=0,"적자",G28/(IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))),"")</f>
         <v/>
       </c>
-      <c r="H49" s="47">
+      <c r="H49" s="48">
         <f>IFERROR(IF(('연간'!T44)&lt;=0,"적자",H28/('연간'!T44)),"")</f>
         <v/>
       </c>
-      <c r="I49" s="48">
+      <c r="I49" s="49">
         <f>IFERROR(IF(('연간'!U44)&lt;=0,"적자",I28/('연간'!U44)),"")</f>
         <v/>
       </c>
-      <c r="J49" s="48">
+      <c r="J49" s="49">
         <f>IFERROR(IF(('연간'!V44)&lt;=0,"적자",J28/('연간'!V44)),"")</f>
         <v/>
       </c>
-      <c r="K49" s="48">
+      <c r="K49" s="49">
         <f>IFERROR(IF(('연간'!W44)&lt;=0,"적자",K28/('연간'!W44)),"")</f>
         <v/>
       </c>
-      <c r="L49" s="48">
+      <c r="L49" s="49">
         <f>IFERROR(IF(('연간'!X44)&lt;=0,"적자",L28/('연간'!X44)),"")</f>
         <v/>
       </c>
@@ -11401,7 +11872,7 @@
       <c r="L50" s="25" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="46" t="inlineStr">
+      <c r="A51" s="47" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
@@ -11453,7 +11924,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="46" t="inlineStr">
+      <c r="A52" s="47" t="inlineStr">
         <is>
           <t>ROA</t>
         </is>
@@ -11505,7 +11976,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="46" t="inlineStr">
+      <c r="A53" s="47" t="inlineStr">
         <is>
           <t>ROIC</t>
         </is>
@@ -11557,7 +12028,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="46" t="inlineStr">
+      <c r="A54" s="47" t="inlineStr">
         <is>
           <t>매출총이익률 (GPM)</t>
         </is>
@@ -11609,7 +12080,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="46" t="inlineStr">
+      <c r="A55" s="47" t="inlineStr">
         <is>
           <t>영업이익률 (OPM)</t>
         </is>
@@ -11661,7 +12132,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="46" t="inlineStr">
+      <c r="A56" s="47" t="inlineStr">
         <is>
           <t>순이익률</t>
         </is>
@@ -11731,7 +12202,7 @@
       <c r="L57" s="25" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="46" t="inlineStr">
+      <c r="A58" s="47" t="inlineStr">
         <is>
           <t>총자산회전율</t>
         </is>
@@ -11783,7 +12254,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="46" t="inlineStr">
+      <c r="A59" s="47" t="inlineStr">
         <is>
           <t>매출채권회전일수</t>
         </is>
@@ -11793,49 +12264,49 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C59" s="49">
+      <c r="C59" s="50">
         <f>IFERROR(C8/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4)))*365,"")</f>
         <v/>
       </c>
-      <c r="D59" s="50">
+      <c r="D59" s="51">
         <f>IFERROR(D8/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4)))*365,"")</f>
         <v/>
       </c>
-      <c r="E59" s="50">
+      <c r="E59" s="51">
         <f>IFERROR(E8/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4)))*365,"")</f>
         <v/>
       </c>
-      <c r="F59" s="50">
+      <c r="F59" s="51">
         <f>IFERROR(F8/(IF(COUNT('연간'!J4:M4)&lt;4,"",SUM('연간'!J4:M4)))*365,"")</f>
         <v/>
       </c>
-      <c r="G59" s="50">
+      <c r="G59" s="51">
         <f>IFERROR(G8/(IF(COUNT('연간'!K4:N4)&lt;4,"",SUM('연간'!K4:N4)))*365,"")</f>
         <v/>
       </c>
-      <c r="H59" s="49">
+      <c r="H59" s="50">
         <f>IFERROR(H8/('연간'!T4)*365,"")</f>
         <v/>
       </c>
-      <c r="I59" s="50">
+      <c r="I59" s="51">
         <f>IFERROR(I8/('연간'!U4)*365,"")</f>
         <v/>
       </c>
-      <c r="J59" s="50">
+      <c r="J59" s="51">
         <f>IFERROR(J8/('연간'!V4)*365,"")</f>
         <v/>
       </c>
-      <c r="K59" s="50">
+      <c r="K59" s="51">
         <f>IFERROR(K8/('연간'!W4)*365,"")</f>
         <v/>
       </c>
-      <c r="L59" s="50">
+      <c r="L59" s="51">
         <f>IFERROR(L8/('연간'!X4)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="46" t="inlineStr">
+      <c r="A60" s="47" t="inlineStr">
         <is>
           <t>재고자산회전일수</t>
         </is>
@@ -11845,49 +12316,49 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C60" s="49">
+      <c r="C60" s="50">
         <f>IFERROR(C9/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
-      <c r="D60" s="50">
+      <c r="D60" s="51">
         <f>IFERROR(D9/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
-      <c r="E60" s="50">
+      <c r="E60" s="51">
         <f>IFERROR(E9/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
-      <c r="F60" s="50">
+      <c r="F60" s="51">
         <f>IFERROR(F9/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
         <v/>
       </c>
-      <c r="G60" s="50">
+      <c r="G60" s="51">
         <f>IFERROR(G9/(IF(COUNT('연간'!K11:N11)&lt;4,"",SUM('연간'!K11:N11)))*365,"")</f>
         <v/>
       </c>
-      <c r="H60" s="49">
+      <c r="H60" s="50">
         <f>IFERROR(H9/('연간'!T11)*365,"")</f>
         <v/>
       </c>
-      <c r="I60" s="50">
+      <c r="I60" s="51">
         <f>IFERROR(I9/('연간'!U11)*365,"")</f>
         <v/>
       </c>
-      <c r="J60" s="50">
+      <c r="J60" s="51">
         <f>IFERROR(J9/('연간'!V11)*365,"")</f>
         <v/>
       </c>
-      <c r="K60" s="50">
+      <c r="K60" s="51">
         <f>IFERROR(K9/('연간'!W11)*365,"")</f>
         <v/>
       </c>
-      <c r="L60" s="50">
+      <c r="L60" s="51">
         <f>IFERROR(L9/('연간'!X11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="46" t="inlineStr">
+      <c r="A61" s="47" t="inlineStr">
         <is>
           <t>매입채무회전일수</t>
         </is>
@@ -11897,49 +12368,49 @@
           <t>길수록 유리</t>
         </is>
       </c>
-      <c r="C61" s="49">
+      <c r="C61" s="50">
         <f>IFERROR(C19/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
-      <c r="D61" s="50">
+      <c r="D61" s="51">
         <f>IFERROR(D19/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
-      <c r="E61" s="50">
+      <c r="E61" s="51">
         <f>IFERROR(E19/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
-      <c r="F61" s="50">
+      <c r="F61" s="51">
         <f>IFERROR(F19/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
         <v/>
       </c>
-      <c r="G61" s="50">
+      <c r="G61" s="51">
         <f>IFERROR(G19/(IF(COUNT('연간'!K11:N11)&lt;4,"",SUM('연간'!K11:N11)))*365,"")</f>
         <v/>
       </c>
-      <c r="H61" s="49">
+      <c r="H61" s="50">
         <f>IFERROR(H19/('연간'!T11)*365,"")</f>
         <v/>
       </c>
-      <c r="I61" s="50">
+      <c r="I61" s="51">
         <f>IFERROR(I19/('연간'!U11)*365,"")</f>
         <v/>
       </c>
-      <c r="J61" s="50">
+      <c r="J61" s="51">
         <f>IFERROR(J19/('연간'!V11)*365,"")</f>
         <v/>
       </c>
-      <c r="K61" s="50">
+      <c r="K61" s="51">
         <f>IFERROR(K19/('연간'!W11)*365,"")</f>
         <v/>
       </c>
-      <c r="L61" s="50">
+      <c r="L61" s="51">
         <f>IFERROR(L19/('연간'!X11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="46" t="inlineStr">
+      <c r="A62" s="47" t="inlineStr">
         <is>
           <t>현금전환주기 (CCC)</t>
         </is>
@@ -11949,43 +12420,43 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C62" s="49">
+      <c r="C62" s="50">
         <f>IF(OR(C59="",C60="",C61=""),"",IFERROR(C59+C60-C61,""))</f>
         <v/>
       </c>
-      <c r="D62" s="50">
+      <c r="D62" s="51">
         <f>IF(OR(D59="",D60="",D61=""),"",IFERROR(D59+D60-D61,""))</f>
         <v/>
       </c>
-      <c r="E62" s="50">
+      <c r="E62" s="51">
         <f>IF(OR(E59="",E60="",E61=""),"",IFERROR(E59+E60-E61,""))</f>
         <v/>
       </c>
-      <c r="F62" s="50">
+      <c r="F62" s="51">
         <f>IF(OR(F59="",F60="",F61=""),"",IFERROR(F59+F60-F61,""))</f>
         <v/>
       </c>
-      <c r="G62" s="50">
+      <c r="G62" s="51">
         <f>IF(OR(G59="",G60="",G61=""),"",IFERROR(G59+G60-G61,""))</f>
         <v/>
       </c>
-      <c r="H62" s="49">
+      <c r="H62" s="50">
         <f>IF(OR(H59="",H60="",H61=""),"",IFERROR(H59+H60-H61,""))</f>
         <v/>
       </c>
-      <c r="I62" s="50">
+      <c r="I62" s="51">
         <f>IF(OR(I59="",I60="",I61=""),"",IFERROR(I59+I60-I61,""))</f>
         <v/>
       </c>
-      <c r="J62" s="50">
+      <c r="J62" s="51">
         <f>IF(OR(J59="",J60="",J61=""),"",IFERROR(J59+J60-J61,""))</f>
         <v/>
       </c>
-      <c r="K62" s="50">
+      <c r="K62" s="51">
         <f>IF(OR(K59="",K60="",K61=""),"",IFERROR(K59+K60-K61,""))</f>
         <v/>
       </c>
-      <c r="L62" s="50">
+      <c r="L62" s="51">
         <f>IF(OR(L59="",L60="",L61=""),"",IFERROR(L59+L60-L61,""))</f>
         <v/>
       </c>
@@ -12009,7 +12480,7 @@
       <c r="L63" s="25" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="46" t="inlineStr">
+      <c r="A64" s="47" t="inlineStr">
         <is>
           <t>영업현금흐름 / 순이익</t>
         </is>
@@ -12061,7 +12532,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="46" t="inlineStr">
+      <c r="A65" s="47" t="inlineStr">
         <is>
           <t>FCF 마진</t>
         </is>
@@ -12113,7 +12584,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="46" t="inlineStr">
+      <c r="A66" s="47" t="inlineStr">
         <is>
           <t>CAPEX / 매출</t>
         </is>
@@ -12165,7 +12636,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="46" t="inlineStr">
+      <c r="A67" s="47" t="inlineStr">
         <is>
           <t>배당성향</t>
         </is>
@@ -13971,24 +14442,24 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>출처 · 쓴 결산단신</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="52" t="inlineStr">
+      <c r="A3" s="53" t="inlineStr">
         <is>
           <t>공시일</t>
         </is>
       </c>
-      <c r="B3" s="52" t="inlineStr">
+      <c r="B3" s="53" t="inlineStr">
         <is>
           <t>문서</t>
         </is>
       </c>
-      <c r="C3" s="52" t="inlineStr">
+      <c r="C3" s="53" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>

--- a/docs/data/jp/xlsx/4644.xlsx
+++ b/docs/data/jp/xlsx/4644.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="재무상태표" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="출처" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="섹터 데이터" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="출처" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'연간'!$3:$3</definedName>
@@ -21,14 +22,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="0.0%;-0.0%;&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0&quot;x&quot;;-0.0&quot;x&quot;;&quot;-&quot;"/>
     <numFmt numFmtId="167" formatCode="0.0&quot;년&quot;;-0.0&quot;년&quot;;&quot;-&quot;"/>
     <numFmt numFmtId="168" formatCode="0&quot;일&quot;;-0&quot;일&quot;;&quot;-&quot;"/>
+    <numFmt numFmtId="169" formatCode="#,##0.0;\(#,##0.0\);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -126,11 +128,31 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <color rgb="FFFF0000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="FF808080"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -155,6 +177,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF808080"/>
       </patternFill>
     </fill>
     <fill>
@@ -201,7 +228,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -345,7 +372,25 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -9639,7 +9684,7 @@
     <row r="146">
       <c r="A146" s="20" t="inlineStr">
         <is>
-          <t>Decrease Increase In Advance Expense Payments Other Ope CF</t>
+          <t>경비 선급금 증감액(△는 증가)</t>
         </is>
       </c>
       <c r="D146" s="22" t="n">
@@ -9774,7 +9819,7 @@
     <row r="149">
       <c r="A149" s="20" t="inlineStr">
         <is>
-          <t>Increase Decrease In Accounts Payable Ope CF</t>
+          <t>영업미지급금 증감액(△는 감소)</t>
         </is>
       </c>
       <c r="D149" s="22" t="n">
@@ -15416,6 +15461,2628 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G199"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="52" t="inlineStr">
+        <is>
+          <t>이마지니어 섹터·사업 데이터</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="53" t="inlineStr">
+        <is>
+          <t>2단계 보고서를 만들 때 모은 자료 · 월차 · 출처는 맨 오른쪽</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="54" t="inlineStr">
+        <is>
+          <t>bs annual</t>
+        </is>
+      </c>
+      <c r="B4" s="54" t="n"/>
+      <c r="C4" s="54" t="n"/>
+      <c r="D4" s="54" t="n"/>
+      <c r="E4" s="54" t="n"/>
+      <c r="F4" s="54" t="n"/>
+      <c r="G4" s="54" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B5" s="55" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C5" s="55" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D5" s="55" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E5" s="55" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F5" s="55" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G5" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="56" t="inlineStr">
+        <is>
+          <t>labels</t>
+        </is>
+      </c>
+      <c r="B6" s="57" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C6" s="57" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D6" s="57" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E6" s="57" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F6" s="57" t="n">
+        <v>2026</v>
+      </c>
+      <c r="G6" s="58" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="56" t="inlineStr">
+        <is>
+          <t>current assets</t>
+        </is>
+      </c>
+      <c r="B7" s="59" t="n">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="C7" s="59" t="n">
+        <v>123.6</v>
+      </c>
+      <c r="D7" s="59" t="n">
+        <v>108</v>
+      </c>
+      <c r="E7" s="59" t="n">
+        <v>117.6</v>
+      </c>
+      <c r="F7" s="59" t="n">
+        <v>51.9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="56" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="B8" s="59" t="n">
+        <v>73</v>
+      </c>
+      <c r="C8" s="59" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="D8" s="59" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="E8" s="59" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="F8" s="59" t="n">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="56" t="inlineStr">
+        <is>
+          <t>st fin</t>
+        </is>
+      </c>
+      <c r="B9" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="60" t="n"/>
+      <c r="D9" s="60" t="n"/>
+      <c r="E9" s="60" t="n"/>
+      <c r="F9" s="60" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="56" t="inlineStr">
+        <is>
+          <t>receivables</t>
+        </is>
+      </c>
+      <c r="B10" s="59" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="C10" s="59" t="n">
+        <v>18</v>
+      </c>
+      <c r="D10" s="59" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="E10" s="59" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="F10" s="59" t="n">
+        <v>20.3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="56" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B11" s="59" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C11" s="59" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D11" s="59" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E11" s="59" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F11" s="59" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="56" t="inlineStr">
+        <is>
+          <t>noncurrent assets</t>
+        </is>
+      </c>
+      <c r="B12" s="59" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="C12" s="59" t="n">
+        <v>13</v>
+      </c>
+      <c r="D12" s="59" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="E12" s="59" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F12" s="59" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="56" t="inlineStr">
+        <is>
+          <t>ppe</t>
+        </is>
+      </c>
+      <c r="B13" s="59" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C13" s="59" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D13" s="59" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E13" s="59" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F13" s="59" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="56" t="inlineStr">
+        <is>
+          <t>intangibles</t>
+        </is>
+      </c>
+      <c r="B14" s="59" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C14" s="59" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D14" s="59" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E14" s="59" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F14" s="59" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="56" t="inlineStr">
+        <is>
+          <t>inv property</t>
+        </is>
+      </c>
+      <c r="B15" s="60" t="n"/>
+      <c r="C15" s="60" t="n"/>
+      <c r="D15" s="60" t="n"/>
+      <c r="E15" s="60" t="n"/>
+      <c r="F15" s="60" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="56" t="inlineStr">
+        <is>
+          <t>합계 assets</t>
+        </is>
+      </c>
+      <c r="B16" s="59" t="n">
+        <v>126.6</v>
+      </c>
+      <c r="C16" s="59" t="n">
+        <v>136.6</v>
+      </c>
+      <c r="D16" s="59" t="n">
+        <v>134.5</v>
+      </c>
+      <c r="E16" s="59" t="n">
+        <v>134.8</v>
+      </c>
+      <c r="F16" s="59" t="n">
+        <v>129.9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="56" t="inlineStr">
+        <is>
+          <t>current liab</t>
+        </is>
+      </c>
+      <c r="B17" s="59" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="C17" s="59" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="D17" s="59" t="n">
+        <v>14</v>
+      </c>
+      <c r="E17" s="59" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="F17" s="59" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="56" t="inlineStr">
+        <is>
+          <t>payables</t>
+        </is>
+      </c>
+      <c r="B18" s="59" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C18" s="59" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D18" s="59" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E18" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="59" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="56" t="inlineStr">
+        <is>
+          <t>st debt</t>
+        </is>
+      </c>
+      <c r="B19" s="60" t="n"/>
+      <c r="C19" s="60" t="n"/>
+      <c r="D19" s="60" t="n"/>
+      <c r="E19" s="60" t="n"/>
+      <c r="F19" s="60" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="56" t="inlineStr">
+        <is>
+          <t>noncurrent liab</t>
+        </is>
+      </c>
+      <c r="B20" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="59" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E20" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="56" t="inlineStr">
+        <is>
+          <t>lt debt</t>
+        </is>
+      </c>
+      <c r="B21" s="60" t="n"/>
+      <c r="C21" s="60" t="n"/>
+      <c r="D21" s="60" t="n"/>
+      <c r="E21" s="60" t="n"/>
+      <c r="F21" s="60" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="56" t="inlineStr">
+        <is>
+          <t>bonds</t>
+        </is>
+      </c>
+      <c r="B22" s="60" t="n"/>
+      <c r="C22" s="60" t="n"/>
+      <c r="D22" s="60" t="n"/>
+      <c r="E22" s="60" t="n"/>
+      <c r="F22" s="60" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="56" t="inlineStr">
+        <is>
+          <t>합계 liab</t>
+        </is>
+      </c>
+      <c r="B23" s="59" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="C23" s="59" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="D23" s="59" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="E23" s="59" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="F23" s="59" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="56" t="inlineStr">
+        <is>
+          <t>capital stock</t>
+        </is>
+      </c>
+      <c r="B24" s="59" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="C24" s="59" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="D24" s="59" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="E24" s="59" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="F24" s="59" t="n">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="56" t="inlineStr">
+        <is>
+          <t>retained</t>
+        </is>
+      </c>
+      <c r="B25" s="59" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="C25" s="59" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="D25" s="59" t="n">
+        <v>74</v>
+      </c>
+      <c r="E25" s="59" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="F25" s="59" t="n">
+        <v>77.40000000000001</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="56" t="inlineStr">
+        <is>
+          <t>nci</t>
+        </is>
+      </c>
+      <c r="B26" s="59" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C26" s="59" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D26" s="59" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E26" s="59" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="59" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="56" t="inlineStr">
+        <is>
+          <t>합계 equity</t>
+        </is>
+      </c>
+      <c r="B27" s="59" t="n">
+        <v>116.9</v>
+      </c>
+      <c r="C27" s="59" t="n">
+        <v>119.2</v>
+      </c>
+      <c r="D27" s="59" t="n">
+        <v>120.4</v>
+      </c>
+      <c r="E27" s="59" t="n">
+        <v>121.7</v>
+      </c>
+      <c r="F27" s="59" t="n">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="56" t="inlineStr">
+        <is>
+          <t>current ltd</t>
+        </is>
+      </c>
+      <c r="B28" s="60" t="n"/>
+      <c r="C28" s="60" t="n"/>
+      <c r="D28" s="60" t="n"/>
+      <c r="E28" s="60" t="n"/>
+      <c r="F28" s="60" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="56" t="inlineStr">
+        <is>
+          <t>equity owner</t>
+        </is>
+      </c>
+      <c r="B29" s="59" t="n">
+        <v>116.3</v>
+      </c>
+      <c r="C29" s="59" t="n">
+        <v>118.4</v>
+      </c>
+      <c r="D29" s="59" t="n">
+        <v>119.7</v>
+      </c>
+      <c r="E29" s="59" t="n">
+        <v>120.6</v>
+      </c>
+      <c r="F29" s="59" t="n">
+        <v>119.6</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="54" t="inlineStr">
+        <is>
+          <t>cf annual</t>
+        </is>
+      </c>
+      <c r="B31" s="54" t="n"/>
+      <c r="C31" s="54" t="n"/>
+      <c r="D31" s="54" t="n"/>
+      <c r="E31" s="54" t="n"/>
+      <c r="F31" s="54" t="n"/>
+      <c r="G31" s="54" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B32" s="55" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C32" s="55" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D32" s="55" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E32" s="55" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F32" s="55" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G32" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="56" t="inlineStr">
+        <is>
+          <t>labels</t>
+        </is>
+      </c>
+      <c r="B33" s="57" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C33" s="57" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D33" s="57" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E33" s="57" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F33" s="57" t="n">
+        <v>2026</v>
+      </c>
+      <c r="G33" s="58" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="56" t="inlineStr">
+        <is>
+          <t>ocf</t>
+        </is>
+      </c>
+      <c r="B34" s="59" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C34" s="59" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D34" s="59" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E34" s="59" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="F34" s="59" t="n">
+        <v>-2.7</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="56" t="inlineStr">
+        <is>
+          <t>설비투자</t>
+        </is>
+      </c>
+      <c r="B35" s="60" t="n"/>
+      <c r="C35" s="60" t="n"/>
+      <c r="D35" s="60" t="n"/>
+      <c r="E35" s="60" t="n"/>
+      <c r="F35" s="60" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="56" t="inlineStr">
+        <is>
+          <t>dividends</t>
+        </is>
+      </c>
+      <c r="B36" s="59" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="C36" s="59" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D36" s="59" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E36" s="59" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F36" s="59" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="54" t="inlineStr">
+        <is>
+          <t>company 예상</t>
+        </is>
+      </c>
+      <c r="B38" s="54" t="n"/>
+      <c r="C38" s="54" t="n"/>
+      <c r="D38" s="54" t="n"/>
+      <c r="E38" s="54" t="n"/>
+      <c r="F38" s="54" t="n"/>
+      <c r="G38" s="54" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B39" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="G39" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="56" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B40" s="59" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="G40" s="58" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="56" t="inlineStr">
+        <is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="B41" s="59" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="56" t="inlineStr">
+        <is>
+          <t>경상이익</t>
+        </is>
+      </c>
+      <c r="B42" s="59" t="n">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="56" t="inlineStr">
+        <is>
+          <t>순이익</t>
+        </is>
+      </c>
+      <c r="B43" s="59" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="56" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="B44" s="59" t="n">
+        <v>51.9</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="54" t="inlineStr">
+        <is>
+          <t>this quarter</t>
+        </is>
+      </c>
+      <c r="B46" s="54" t="n"/>
+      <c r="C46" s="54" t="n"/>
+      <c r="D46" s="54" t="n"/>
+      <c r="E46" s="54" t="n"/>
+      <c r="F46" s="54" t="n"/>
+      <c r="G46" s="54" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B47" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="G47" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="56" t="inlineStr">
+        <is>
+          <t>mcap ex treasury oku</t>
+        </is>
+      </c>
+      <c r="B48" s="59" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="G48" s="58" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="56" t="inlineStr">
+        <is>
+          <t>PER guide</t>
+        </is>
+      </c>
+      <c r="B49" s="59" t="n">
+        <v>20.2</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="56" t="inlineStr">
+        <is>
+          <t>div yield %</t>
+        </is>
+      </c>
+      <c r="B50" s="59" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="54" t="inlineStr">
+        <is>
+          <t>this quarter · 상반기 cum oku</t>
+        </is>
+      </c>
+      <c r="B52" s="54" t="n"/>
+      <c r="C52" s="54" t="n"/>
+      <c r="D52" s="54" t="n"/>
+      <c r="E52" s="54" t="n"/>
+      <c r="F52" s="54" t="n"/>
+      <c r="G52" s="54" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B53" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="G53" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="56" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B54" s="59" t="n">
+        <v>29.71</v>
+      </c>
+      <c r="G54" s="58" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="56" t="inlineStr">
+        <is>
+          <t>cogs</t>
+        </is>
+      </c>
+      <c r="B55" s="59" t="n">
+        <v>10.49</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="56" t="inlineStr">
+        <is>
+          <t>gp</t>
+        </is>
+      </c>
+      <c r="B56" s="59" t="n">
+        <v>19.22</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="56" t="inlineStr">
+        <is>
+          <t>sga</t>
+        </is>
+      </c>
+      <c r="B57" s="59" t="n">
+        <v>17.02</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="56" t="inlineStr">
+        <is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="B58" s="59" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="56" t="inlineStr">
+        <is>
+          <t>nonop inc</t>
+        </is>
+      </c>
+      <c r="B59" s="59" t="n">
+        <v>7.92</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="56" t="inlineStr">
+        <is>
+          <t>sec gain</t>
+        </is>
+      </c>
+      <c r="B60" s="59" t="n">
+        <v>7.67</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="56" t="inlineStr">
+        <is>
+          <t>nonop inc other</t>
+        </is>
+      </c>
+      <c r="B61" s="59" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="56" t="inlineStr">
+        <is>
+          <t>nonop exp</t>
+        </is>
+      </c>
+      <c r="B62" s="59" t="n">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="56" t="inlineStr">
+        <is>
+          <t>환율 loss</t>
+        </is>
+      </c>
+      <c r="B63" s="59" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="56" t="inlineStr">
+        <is>
+          <t>sec loss</t>
+        </is>
+      </c>
+      <c r="B64" s="59" t="n">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="56" t="inlineStr">
+        <is>
+          <t>nonop exp other</t>
+        </is>
+      </c>
+      <c r="B65" s="59" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="56" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="B66" s="59" t="n">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="56" t="inlineStr">
+        <is>
+          <t>special</t>
+        </is>
+      </c>
+      <c r="B67" s="57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="56" t="inlineStr">
+        <is>
+          <t>pbt</t>
+        </is>
+      </c>
+      <c r="B68" s="59" t="n">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="56" t="inlineStr">
+        <is>
+          <t>tax</t>
+        </is>
+      </c>
+      <c r="B69" s="59" t="n">
+        <v>2.87</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="56" t="inlineStr">
+        <is>
+          <t>순이익</t>
+        </is>
+      </c>
+      <c r="B70" s="59" t="n">
+        <v>6.12</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="56" t="inlineStr">
+        <is>
+          <t>nci</t>
+        </is>
+      </c>
+      <c r="B71" s="59" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="56" t="inlineStr">
+        <is>
+          <t>순이익 owner</t>
+        </is>
+      </c>
+      <c r="B72" s="59" t="n">
+        <v>5.85</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="56" t="inlineStr">
+        <is>
+          <t>EPS yen</t>
+        </is>
+      </c>
+      <c r="B73" s="59" t="n">
+        <v>60.65</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="56" t="inlineStr">
+        <is>
+          <t>comprehensive</t>
+        </is>
+      </c>
+      <c r="B74" s="59" t="n">
+        <v>9.52</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="54" t="inlineStr">
+        <is>
+          <t>this quarter · 상반기 prior oku</t>
+        </is>
+      </c>
+      <c r="B76" s="54" t="n"/>
+      <c r="C76" s="54" t="n"/>
+      <c r="D76" s="54" t="n"/>
+      <c r="E76" s="54" t="n"/>
+      <c r="F76" s="54" t="n"/>
+      <c r="G76" s="54" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B77" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="G77" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="56" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B78" s="59" t="n">
+        <v>26.27</v>
+      </c>
+      <c r="G78" s="58" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="56" t="inlineStr">
+        <is>
+          <t>cogs</t>
+        </is>
+      </c>
+      <c r="B79" s="59" t="n">
+        <v>10.09</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="56" t="inlineStr">
+        <is>
+          <t>gp</t>
+        </is>
+      </c>
+      <c r="B80" s="59" t="n">
+        <v>16.18</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="56" t="inlineStr">
+        <is>
+          <t>sga</t>
+        </is>
+      </c>
+      <c r="B81" s="59" t="n">
+        <v>17.48</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="56" t="inlineStr">
+        <is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="B82" s="59" t="n">
+        <v>-1.3</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="56" t="inlineStr">
+        <is>
+          <t>nonop inc</t>
+        </is>
+      </c>
+      <c r="B83" s="59" t="n">
+        <v>2.66</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="56" t="inlineStr">
+        <is>
+          <t>sec gain</t>
+        </is>
+      </c>
+      <c r="B84" s="59" t="n">
+        <v>2.24</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="56" t="inlineStr">
+        <is>
+          <t>nonop exp</t>
+        </is>
+      </c>
+      <c r="B85" s="59" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="56" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="B86" s="59" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="56" t="inlineStr">
+        <is>
+          <t>tax</t>
+        </is>
+      </c>
+      <c r="B87" s="59" t="n">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="56" t="inlineStr">
+        <is>
+          <t>순이익 owner</t>
+        </is>
+      </c>
+      <c r="B88" s="59" t="n">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="56" t="inlineStr">
+        <is>
+          <t>EPS yen</t>
+        </is>
+      </c>
+      <c r="B89" s="59" t="n">
+        <v>8.58</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="54" t="inlineStr">
+        <is>
+          <t>this_quarter · q2_standalone_oku(계산=중간누계-1Q)</t>
+        </is>
+      </c>
+      <c r="B91" s="54" t="n"/>
+      <c r="C91" s="54" t="n"/>
+      <c r="D91" s="54" t="n"/>
+      <c r="E91" s="54" t="n"/>
+      <c r="F91" s="54" t="n"/>
+      <c r="G91" s="54" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B92" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="G92" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="56" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B93" s="59" t="n">
+        <v>16.06</v>
+      </c>
+      <c r="G93" s="58" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="56" t="inlineStr">
+        <is>
+          <t>cogs</t>
+        </is>
+      </c>
+      <c r="B94" s="59" t="n">
+        <v>5.74</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="56" t="inlineStr">
+        <is>
+          <t>gp</t>
+        </is>
+      </c>
+      <c r="B95" s="59" t="n">
+        <v>10.32</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="56" t="inlineStr">
+        <is>
+          <t>매출총이익률 %</t>
+        </is>
+      </c>
+      <c r="B96" s="59" t="n">
+        <v>64.2</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="56" t="inlineStr">
+        <is>
+          <t>sga</t>
+        </is>
+      </c>
+      <c r="B97" s="59" t="n">
+        <v>9.859999999999999</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="56" t="inlineStr">
+        <is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="B98" s="59" t="n">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="56" t="inlineStr">
+        <is>
+          <t>영업이익률 %</t>
+        </is>
+      </c>
+      <c r="B99" s="59" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="56" t="inlineStr">
+        <is>
+          <t>nonop inc</t>
+        </is>
+      </c>
+      <c r="B100" s="59" t="n">
+        <v>4.72</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="56" t="inlineStr">
+        <is>
+          <t>sec_gain_q2_공시</t>
+        </is>
+      </c>
+      <c r="B101" s="59" t="n">
+        <v>4.88</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="56" t="inlineStr">
+        <is>
+          <t>nonop exp</t>
+        </is>
+      </c>
+      <c r="B102" s="59" t="n">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="56" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="B103" s="59" t="n">
+        <v>4.06</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="56" t="inlineStr">
+        <is>
+          <t>tax</t>
+        </is>
+      </c>
+      <c r="B104" s="59" t="n">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="56" t="inlineStr">
+        <is>
+          <t>순이익 owner</t>
+        </is>
+      </c>
+      <c r="B105" s="59" t="n">
+        <v>2.67</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="54" t="inlineStr">
+        <is>
+          <t>this quarter · 2Q prior year oku</t>
+        </is>
+      </c>
+      <c r="B107" s="54" t="n"/>
+      <c r="C107" s="54" t="n"/>
+      <c r="D107" s="54" t="n"/>
+      <c r="E107" s="54" t="n"/>
+      <c r="F107" s="54" t="n"/>
+      <c r="G107" s="54" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B108" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="G108" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="56" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B109" s="59" t="n">
+        <v>13.22</v>
+      </c>
+      <c r="G109" s="58" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="56" t="inlineStr">
+        <is>
+          <t>gp</t>
+        </is>
+      </c>
+      <c r="B110" s="59" t="n">
+        <v>8.27</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="56" t="inlineStr">
+        <is>
+          <t>sga</t>
+        </is>
+      </c>
+      <c r="B111" s="59" t="n">
+        <v>9.210000000000001</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="56" t="inlineStr">
+        <is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="B112" s="59" t="n">
+        <v>-0.93</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="56" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="B113" s="59" t="n">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="56" t="inlineStr">
+        <is>
+          <t>순이익 owner</t>
+        </is>
+      </c>
+      <c r="B114" s="59" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="54" t="inlineStr">
+        <is>
+          <t>this quarter · 가이던스 FY3 27 unchanged</t>
+        </is>
+      </c>
+      <c r="B116" s="54" t="n"/>
+      <c r="C116" s="54" t="n"/>
+      <c r="D116" s="54" t="n"/>
+      <c r="E116" s="54" t="n"/>
+      <c r="F116" s="54" t="n"/>
+      <c r="G116" s="54" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B117" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="G117" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="56" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B118" s="59" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="G118" s="58" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="56" t="inlineStr">
+        <is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="B119" s="59" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="56" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="B120" s="59" t="n">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="56" t="inlineStr">
+        <is>
+          <t>순이익 owner</t>
+        </is>
+      </c>
+      <c r="B121" s="59" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="56" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="B122" s="59" t="n">
+        <v>51.87</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="56" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B123" s="57" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="54" t="inlineStr">
+        <is>
+          <t>this_quarter · implied_H2(계산=연간예상-중간)</t>
+        </is>
+      </c>
+      <c r="B125" s="54" t="n"/>
+      <c r="C125" s="54" t="n"/>
+      <c r="D125" s="54" t="n"/>
+      <c r="E125" s="54" t="n"/>
+      <c r="F125" s="54" t="n"/>
+      <c r="G125" s="54" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B126" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="G126" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="56" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B127" s="59" t="n">
+        <v>28.09</v>
+      </c>
+      <c r="G127" s="58" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="56" t="inlineStr">
+        <is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="B128" s="59" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="56" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="B129" s="59" t="n">
+        <v>-1.39</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="56" t="inlineStr">
+        <is>
+          <t>순이익 owner</t>
+        </is>
+      </c>
+      <c r="B130" s="59" t="n">
+        <v>-0.85</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="54" t="inlineStr">
+        <is>
+          <t>this quarter · bs 2026 09 end oku</t>
+        </is>
+      </c>
+      <c r="B132" s="54" t="n"/>
+      <c r="C132" s="54" t="n"/>
+      <c r="D132" s="54" t="n"/>
+      <c r="E132" s="54" t="n"/>
+      <c r="F132" s="54" t="n"/>
+      <c r="G132" s="54" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B133" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="G133" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="56" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="B134" s="59" t="n">
+        <v>16.64</v>
+      </c>
+      <c r="G134" s="58" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="56" t="inlineStr">
+        <is>
+          <t>deposits_預け金</t>
+        </is>
+      </c>
+      <c r="B135" s="59" t="n">
+        <v>87.28</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="56" t="inlineStr">
+        <is>
+          <t>inv securities</t>
+        </is>
+      </c>
+      <c r="B136" s="59" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="56" t="inlineStr">
+        <is>
+          <t>receivables</t>
+        </is>
+      </c>
+      <c r="B137" s="59" t="n">
+        <v>20.38</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="56" t="inlineStr">
+        <is>
+          <t>합계 assets</t>
+        </is>
+      </c>
+      <c r="B138" s="59" t="n">
+        <v>137.93</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="56" t="inlineStr">
+        <is>
+          <t>합계 liab</t>
+        </is>
+      </c>
+      <c r="B139" s="59" t="n">
+        <v>10.76</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="56" t="inlineStr">
+        <is>
+          <t>equity</t>
+        </is>
+      </c>
+      <c r="B140" s="59" t="n">
+        <v>127.16</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="56" t="inlineStr">
+        <is>
+          <t>equity owner</t>
+        </is>
+      </c>
+      <c r="B141" s="59" t="n">
+        <v>125.5</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="56" t="inlineStr">
+        <is>
+          <t>equity ratio %</t>
+        </is>
+      </c>
+      <c r="B142" s="59" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="56" t="inlineStr">
+        <is>
+          <t>fin assets 합계</t>
+        </is>
+      </c>
+      <c r="B143" s="59" t="n">
+        <v>105.52</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="56" t="inlineStr">
+        <is>
+          <t>net fin assets</t>
+        </is>
+      </c>
+      <c r="B144" s="59" t="n">
+        <v>94.76000000000001</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="56" t="inlineStr">
+        <is>
+          <t>treasury shares</t>
+        </is>
+      </c>
+      <c r="B145" s="57" t="n">
+        <v>1000249</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="56" t="inlineStr">
+        <is>
+          <t>shares ex treasury</t>
+        </is>
+      </c>
+      <c r="B146" s="57" t="n">
+        <v>9648751</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="56" t="inlineStr">
+        <is>
+          <t>net fin PER 비중 yen</t>
+        </is>
+      </c>
+      <c r="B147" s="57" t="n">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="56" t="inlineStr">
+        <is>
+          <t>bps yen</t>
+        </is>
+      </c>
+      <c r="B148" s="57" t="n">
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="54" t="inlineStr">
+        <is>
+          <t>this quarter · bs 2026 03 end oku</t>
+        </is>
+      </c>
+      <c r="B150" s="54" t="n"/>
+      <c r="C150" s="54" t="n"/>
+      <c r="D150" s="54" t="n"/>
+      <c r="E150" s="54" t="n"/>
+      <c r="F150" s="54" t="n"/>
+      <c r="G150" s="54" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B151" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="G151" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="56" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="B152" s="59" t="n">
+        <v>16.77</v>
+      </c>
+      <c r="G152" s="58" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="56" t="inlineStr">
+        <is>
+          <t>deposits</t>
+        </is>
+      </c>
+      <c r="B153" s="59" t="n">
+        <v>9.289999999999999</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="56" t="inlineStr">
+        <is>
+          <t>inv securities</t>
+        </is>
+      </c>
+      <c r="B154" s="59" t="n">
+        <v>67.93000000000001</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="56" t="inlineStr">
+        <is>
+          <t>합계 liab</t>
+        </is>
+      </c>
+      <c r="B155" s="59" t="n">
+        <v>8.949999999999999</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="56" t="inlineStr">
+        <is>
+          <t>equity owner</t>
+        </is>
+      </c>
+      <c r="B156" s="59" t="n">
+        <v>119.59</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="54" t="inlineStr">
+        <is>
+          <t>this quarter · cf 상반기 oku</t>
+        </is>
+      </c>
+      <c r="B158" s="54" t="n"/>
+      <c r="C158" s="54" t="n"/>
+      <c r="D158" s="54" t="n"/>
+      <c r="E158" s="54" t="n"/>
+      <c r="F158" s="54" t="n"/>
+      <c r="G158" s="54" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B159" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="G159" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="56" t="inlineStr">
+        <is>
+          <t>ocf</t>
+        </is>
+      </c>
+      <c r="B160" s="59" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="G160" s="58" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="56" t="inlineStr">
+        <is>
+          <t>icf</t>
+        </is>
+      </c>
+      <c r="B161" s="59" t="n">
+        <v>78.05</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="56" t="inlineStr">
+        <is>
+          <t>sec buy</t>
+        </is>
+      </c>
+      <c r="B162" s="59" t="n">
+        <v>-109.97</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="56" t="inlineStr">
+        <is>
+          <t>sec sell</t>
+        </is>
+      </c>
+      <c r="B163" s="59" t="n">
+        <v>188.04</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="56" t="inlineStr">
+        <is>
+          <t>fcf div</t>
+        </is>
+      </c>
+      <c r="B164" s="59" t="n">
+        <v>-3.42</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="56" t="inlineStr">
+        <is>
+          <t>cash eq end</t>
+        </is>
+      </c>
+      <c r="B165" s="59" t="n">
+        <v>103.92</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="54" t="inlineStr">
+        <is>
+          <t>filings</t>
+        </is>
+      </c>
+      <c r="B167" s="54" t="n"/>
+      <c r="C167" s="54" t="n"/>
+      <c r="D167" s="54" t="n"/>
+      <c r="E167" s="54" t="n"/>
+      <c r="F167" s="54" t="n"/>
+      <c r="G167" s="54" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B168" s="55" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C168" s="55" t="inlineStr">
+        <is>
+          <t>doc</t>
+        </is>
+      </c>
+      <c r="G168" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="56" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B169" s="60" t="inlineStr">
+        <is>
+          <t>2027年3月期第2四半期（中間期）決算短信〔日本基準〕（連結）</t>
+        </is>
+      </c>
+      <c r="C169" s="60" t="inlineStr">
+        <is>
+          <t>140120261020553344</t>
+        </is>
+      </c>
+      <c r="G169" s="58" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="56" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B170" s="60" t="inlineStr">
+        <is>
+          <t>2027年3月期第1四半期決算短信〔日本基準〕（連結）</t>
+        </is>
+      </c>
+      <c r="C170" s="60" t="inlineStr">
+        <is>
+          <t>140120260717595817</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="56" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B171" s="60" t="inlineStr">
+        <is>
+          <t>2026年3月期決算短信〔日本基準〕（連結）</t>
+        </is>
+      </c>
+      <c r="C171" s="60" t="inlineStr">
+        <is>
+          <t>140120260424510291</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="56" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="B172" s="60" t="inlineStr">
+        <is>
+          <t>2026年3月期第3四半期決算短信〔日本基準〕（連結）</t>
+        </is>
+      </c>
+      <c r="C172" s="60" t="inlineStr">
+        <is>
+          <t>140120260122536910</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="56" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="B173" s="60" t="inlineStr">
+        <is>
+          <t>2026年3月期第2四半期（中間期）決算短信〔日本基準〕（連結）</t>
+        </is>
+      </c>
+      <c r="C173" s="60" t="inlineStr">
+        <is>
+          <t>140120251021576319</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="56" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="B174" s="60" t="inlineStr">
+        <is>
+          <t>2026年3月期第1四半期決算短信〔日本基準〕（連結）</t>
+        </is>
+      </c>
+      <c r="C174" s="60" t="inlineStr">
+        <is>
+          <t>140120250718516595</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="56" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="B175" s="60" t="inlineStr">
+        <is>
+          <t>2025年3月期決算短信〔日本基準〕（連結）</t>
+        </is>
+      </c>
+      <c r="C175" s="60" t="inlineStr">
+        <is>
+          <t>140120250428525315</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="56" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="B176" s="60" t="inlineStr">
+        <is>
+          <t>2025年3月期第3四半期決算短信〔日本基準〕（連結）</t>
+        </is>
+      </c>
+      <c r="C176" s="60" t="inlineStr">
+        <is>
+          <t>140120250121553372</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="56" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+      <c r="B177" s="60" t="inlineStr">
+        <is>
+          <t>2025年3月期第2四半期決算短信〔日本基準〕（連結）</t>
+        </is>
+      </c>
+      <c r="C177" s="60" t="inlineStr">
+        <is>
+          <t>140120241021500573</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="56" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="B178" s="60" t="inlineStr">
+        <is>
+          <t>2025年3月期第1四半期決算短信〔日本基準〕（連結）</t>
+        </is>
+      </c>
+      <c r="C178" s="60" t="inlineStr">
+        <is>
+          <t>140120240718551074</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="56" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="B179" s="60" t="inlineStr">
+        <is>
+          <t>2024年3月期 決算短信〔日本基準〕（連結）</t>
+        </is>
+      </c>
+      <c r="C179" s="60" t="inlineStr">
+        <is>
+          <t>140120240424575847</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="56" t="inlineStr">
+        <is>
+          <t>2024-01-31</t>
+        </is>
+      </c>
+      <c r="B180" s="60" t="inlineStr">
+        <is>
+          <t>2024年3月期 第3四半期決算短信〔日本基準〕（連結）</t>
+        </is>
+      </c>
+      <c r="C180" s="60" t="inlineStr">
+        <is>
+          <t>140120240125519125</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="56" t="inlineStr">
+        <is>
+          <t>2023-10-31</t>
+        </is>
+      </c>
+      <c r="B181" s="60" t="inlineStr">
+        <is>
+          <t>2024年3月期第2四半期決算短信〔日本基準〕（連結）</t>
+        </is>
+      </c>
+      <c r="C181" s="60" t="inlineStr">
+        <is>
+          <t>140120231023570147</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="56" t="inlineStr">
+        <is>
+          <t>2023-07-31</t>
+        </is>
+      </c>
+      <c r="B182" s="60" t="inlineStr">
+        <is>
+          <t>2024年3月期 第1四半期決算短信〔日本基準〕（連結）</t>
+        </is>
+      </c>
+      <c r="C182" s="60" t="inlineStr">
+        <is>
+          <t>140120230720524475</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="56" t="inlineStr">
+        <is>
+          <t>2023-05-15</t>
+        </is>
+      </c>
+      <c r="B183" s="60" t="inlineStr">
+        <is>
+          <t>2023年3月期 決算短信〔日本基準〕（連結）</t>
+        </is>
+      </c>
+      <c r="C183" s="60" t="inlineStr">
+        <is>
+          <t>140120230427554287</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="56" t="inlineStr">
+        <is>
+          <t>2023-01-31</t>
+        </is>
+      </c>
+      <c r="B184" s="60" t="inlineStr">
+        <is>
+          <t>2023年3月期 第3四半期決算短信〔日本基準〕（連結）</t>
+        </is>
+      </c>
+      <c r="C184" s="60" t="inlineStr">
+        <is>
+          <t>140120230124592901</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="56" t="inlineStr">
+        <is>
+          <t>2022-05-16</t>
+        </is>
+      </c>
+      <c r="B185" s="60" t="inlineStr">
+        <is>
+          <t>2022年3月期 決算短信〔日本基準〕（連結）</t>
+        </is>
+      </c>
+      <c r="C185" s="60" t="inlineStr">
+        <is>
+          <t>140120220426527935</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="56" t="inlineStr">
+        <is>
+          <t>2021-05-14</t>
+        </is>
+      </c>
+      <c r="B186" s="60" t="inlineStr">
+        <is>
+          <t>2021年3月期決算短信〔日本基準〕（連結）</t>
+        </is>
+      </c>
+      <c r="C186" s="60" t="inlineStr">
+        <is>
+          <t>140120210426400105</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="56" t="inlineStr">
+        <is>
+          <t>2020-05-15</t>
+        </is>
+      </c>
+      <c r="B187" s="60" t="inlineStr">
+        <is>
+          <t>2020年3月期決算短信〔日本基準〕（連結）</t>
+        </is>
+      </c>
+      <c r="C187" s="60" t="inlineStr">
+        <is>
+          <t>140120200430403327</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="56" t="inlineStr">
+        <is>
+          <t>2019-05-15</t>
+        </is>
+      </c>
+      <c r="B188" s="60" t="inlineStr">
+        <is>
+          <t>2019年3月期決算短信〔日本基準〕（連結）</t>
+        </is>
+      </c>
+      <c r="C188" s="60" t="inlineStr">
+        <is>
+          <t>140120190507415941</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="56" t="inlineStr">
+        <is>
+          <t>2018-05-15</t>
+        </is>
+      </c>
+      <c r="B189" s="60" t="inlineStr">
+        <is>
+          <t>平成30年3月期 決算短信〔日本基準〕（連結）</t>
+        </is>
+      </c>
+      <c r="C189" s="60" t="inlineStr">
+        <is>
+          <t>140120180425419501</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="54" t="inlineStr">
+        <is>
+          <t>reactions</t>
+        </is>
+      </c>
+      <c r="B191" s="54" t="n"/>
+      <c r="C191" s="54" t="n"/>
+      <c r="D191" s="54" t="n"/>
+      <c r="E191" s="54" t="n"/>
+      <c r="F191" s="54" t="n"/>
+      <c r="G191" s="54" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B192" s="55" t="inlineStr">
+        <is>
+          <t>기준일</t>
+        </is>
+      </c>
+      <c r="C192" s="55" t="inlineStr">
+        <is>
+          <t>다음날</t>
+        </is>
+      </c>
+      <c r="D192" s="55" t="inlineStr">
+        <is>
+          <t>등락%</t>
+        </is>
+      </c>
+      <c r="G192" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="56" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="B193" s="60" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="C193" s="60" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="D193" s="59" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="G193" s="58" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="56" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="B194" s="60" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="C194" s="60" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="D194" s="59" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="56" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="B195" s="60" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="C195" s="60" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="D195" s="59" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="56" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="B196" s="60" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="C196" s="60" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="D196" s="59" t="n">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="56" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="B197" s="60" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="C197" s="60" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="D197" s="59" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="56" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B198" s="60" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C198" s="60" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="D198" s="59" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="56" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B199" s="60" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="C199" s="60" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D199" s="59" t="n">
+        <v>-0.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -15432,17 +18099,17 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="53" t="inlineStr">
+      <c r="A3" s="61" t="inlineStr">
         <is>
           <t>공시일</t>
         </is>
       </c>
-      <c r="B3" s="53" t="inlineStr">
+      <c r="B3" s="61" t="inlineStr">
         <is>
           <t>문서</t>
         </is>
       </c>
-      <c r="C3" s="53" t="inlineStr">
+      <c r="C3" s="61" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
